--- a/research/traditional_assets/database/data/morocco/morocco_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_paper_forest_products.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="cbse_mdp" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0537</v>
+        <v>0.0649</v>
+      </c>
+      <c r="E2">
+        <v>0.187</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.01651376146788991</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.01651376146788991</v>
       </c>
       <c r="I2">
-        <v>-0.008474576271186441</v>
+        <v>0.06009174311926606</v>
       </c>
       <c r="J2">
-        <v>-0.008474576271186441</v>
+        <v>0.05830615989515073</v>
       </c>
       <c r="K2">
-        <v>-0.488</v>
+        <v>1.7</v>
       </c>
       <c r="L2">
-        <v>-0.06362451108213819</v>
+        <v>0.1559633027522936</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,73 +629,73 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.017</v>
+        <v>0.164</v>
       </c>
       <c r="V2">
-        <v>0.002800658978583196</v>
+        <v>0.01312</v>
       </c>
       <c r="W2">
-        <v>0.1025210084033613</v>
+        <v>-0.3003533568904593</v>
       </c>
       <c r="X2">
-        <v>0.2145471252522514</v>
+        <v>0.1949281319457252</v>
       </c>
       <c r="Y2">
-        <v>-0.1120261168488901</v>
+        <v>-0.4952814888361845</v>
       </c>
       <c r="Z2">
-        <v>0.7900700453234447</v>
+        <v>1.292541207162339</v>
       </c>
       <c r="AA2">
-        <v>-0.00669550885867326</v>
+        <v>0.07536311429587844</v>
       </c>
       <c r="AB2">
-        <v>0.07123959743463504</v>
+        <v>0.1140379404340876</v>
       </c>
       <c r="AC2">
-        <v>-0.0779351062933083</v>
+        <v>-0.03867482613820919</v>
       </c>
       <c r="AD2">
-        <v>21.5</v>
+        <v>18.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>21.5</v>
+        <v>18.4</v>
       </c>
       <c r="AG2">
-        <v>21.483</v>
+        <v>18.236</v>
       </c>
       <c r="AH2">
-        <v>0.7798331519767864</v>
+        <v>0.5954692556634305</v>
       </c>
       <c r="AI2">
-        <v>1.357323232323232</v>
+        <v>1.218543046357616</v>
       </c>
       <c r="AJ2">
-        <v>0.7796973106376801</v>
+        <v>0.5933107756376886</v>
       </c>
       <c r="AK2">
-        <v>1.357707135182961</v>
+        <v>1.220942688805571</v>
       </c>
       <c r="AL2">
-        <v>0.303</v>
+        <v>0.279</v>
       </c>
       <c r="AM2">
-        <v>0.303</v>
+        <v>0.279</v>
       </c>
       <c r="AO2">
-        <v>-0.2145214521452145</v>
+        <v>2.347670250896057</v>
       </c>
       <c r="AQ2">
-        <v>-0.2145214521452145</v>
+        <v>2.347670250896057</v>
       </c>
     </row>
     <row r="3">
@@ -710,25 +715,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0537</v>
+        <v>0.0649</v>
+      </c>
+      <c r="E3">
+        <v>0.187</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.01651376146788991</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.01651376146788991</v>
       </c>
       <c r="I3">
-        <v>-0.008474576271186441</v>
+        <v>0.06009174311926606</v>
       </c>
       <c r="J3">
-        <v>-0.008474576271186441</v>
+        <v>0.05830615989515073</v>
       </c>
       <c r="K3">
-        <v>-0.488</v>
+        <v>1.7</v>
       </c>
       <c r="L3">
-        <v>-0.06362451108213819</v>
+        <v>0.1559633027522936</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,73 +754,8782 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.017</v>
+        <v>0.164</v>
       </c>
       <c r="V3">
-        <v>0.002800658978583196</v>
+        <v>0.01312</v>
       </c>
       <c r="W3">
-        <v>0.1025210084033613</v>
+        <v>-0.3003533568904593</v>
       </c>
       <c r="X3">
-        <v>0.2145471252522514</v>
+        <v>0.1949281319457252</v>
       </c>
       <c r="Y3">
-        <v>-0.1120261168488901</v>
+        <v>-0.4952814888361845</v>
       </c>
       <c r="Z3">
-        <v>0.7900700453234447</v>
+        <v>1.292541207162339</v>
       </c>
       <c r="AA3">
-        <v>-0.00669550885867326</v>
+        <v>0.07536311429587844</v>
       </c>
       <c r="AB3">
-        <v>0.07123959743463504</v>
+        <v>0.1140379404340876</v>
       </c>
       <c r="AC3">
-        <v>-0.0779351062933083</v>
+        <v>-0.03867482613820919</v>
       </c>
       <c r="AD3">
-        <v>21.5</v>
+        <v>18.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>21.5</v>
+        <v>18.4</v>
       </c>
       <c r="AG3">
-        <v>21.483</v>
+        <v>18.236</v>
       </c>
       <c r="AH3">
-        <v>0.7798331519767864</v>
+        <v>0.5954692556634305</v>
       </c>
       <c r="AI3">
-        <v>1.357323232323232</v>
+        <v>1.218543046357616</v>
       </c>
       <c r="AJ3">
-        <v>0.7796973106376801</v>
+        <v>0.5933107756376886</v>
       </c>
       <c r="AK3">
-        <v>1.357707135182961</v>
+        <v>1.220942688805571</v>
       </c>
       <c r="AL3">
-        <v>0.303</v>
+        <v>0.279</v>
       </c>
       <c r="AM3">
-        <v>0.303</v>
+        <v>0.279</v>
       </c>
       <c r="AO3">
-        <v>-0.2145214521452145</v>
+        <v>2.347670250896057</v>
       </c>
       <c r="AQ3">
-        <v>-0.2145214521452145</v>
+        <v>2.347670250896057</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Med Paper S.A. (CBSE:MDP)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CBSE:MDP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Paper/Forest Products</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.59546925566343</v>
+      </c>
+      <c r="F2">
+        <v>0.09</v>
+      </c>
+      <c r="G2">
+        <v>12.5</v>
+      </c>
+      <c r="H2">
+        <v>28.0304851058727</v>
+      </c>
+      <c r="I2">
+        <v>30.736</v>
+      </c>
+      <c r="J2">
+        <v>30.6474851058727</v>
+      </c>
+      <c r="K2">
+        <v>18.4</v>
+      </c>
+      <c r="L2">
+        <v>2.781</v>
+      </c>
+      <c r="M2">
+        <v>0.114037940434088</v>
+      </c>
+      <c r="N2">
+        <v>0.114255239775579</v>
+      </c>
+      <c r="O2">
+        <v>0.0590853646788991</v>
+      </c>
+      <c r="P2">
+        <v>0.040572</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.194928131945725</v>
+      </c>
+      <c r="T2">
+        <v>0.121542593159977</v>
+      </c>
+      <c r="U2">
+        <v>1.52541584222679</v>
+      </c>
+      <c r="V2">
+        <v>0.808418450026879</v>
+      </c>
+      <c r="W2">
+        <v>4.005557634776313</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>12.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.1023511934410034</v>
+      </c>
+      <c r="AC2">
+        <v>0.0856309633027523</v>
+      </c>
+      <c r="AD2">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>-0.655</v>
+      </c>
+      <c r="AI2">
+        <v>-0.16</v>
+      </c>
+      <c r="AJ2">
+        <v>18.4</v>
+      </c>
+      <c r="AK2">
+        <v>18.4</v>
+      </c>
+      <c r="AL2">
+        <v>0.279</v>
+      </c>
+      <c r="AN2">
+        <v>0.164</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1162568046246057</v>
+      </c>
+      <c r="C2">
+        <v>30.019522034374</v>
+      </c>
+      <c r="D2">
+        <v>29.855522034374</v>
+      </c>
+      <c r="E2">
+        <v>-18.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.164</v>
+      </c>
+      <c r="H2">
+        <v>12.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>-0.655</v>
+      </c>
+      <c r="L2">
+        <v>0.655</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.655</v>
+      </c>
+      <c r="O2">
+        <v>0.20305</v>
+      </c>
+      <c r="P2">
+        <v>0.45195</v>
+      </c>
+      <c r="Q2">
+        <v>-0.2030500000000001</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1162568046246057</v>
+      </c>
+      <c r="T2">
+        <v>0.7567748066294202</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W2">
+        <v>0.031533</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1159440185302694</v>
+      </c>
+      <c r="C3">
+        <v>29.83157344327666</v>
+      </c>
+      <c r="D3">
+        <v>29.97657344327666</v>
+      </c>
+      <c r="E3">
+        <v>-18.091</v>
+      </c>
+      <c r="F3">
+        <v>0.309</v>
+      </c>
+      <c r="G3">
+        <v>0.164</v>
+      </c>
+      <c r="H3">
+        <v>12.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>-0.655</v>
+      </c>
+      <c r="L3">
+        <v>0.655</v>
+      </c>
+      <c r="M3">
+        <v>0.0141213</v>
+      </c>
+      <c r="N3">
+        <v>0.6408787</v>
+      </c>
+      <c r="O3">
+        <v>0.198672397</v>
+      </c>
+      <c r="P3">
+        <v>0.442206303</v>
+      </c>
+      <c r="Q3">
+        <v>-0.2127936970000001</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1167966550810802</v>
+      </c>
+      <c r="T3">
+        <v>0.7620492977059283</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W3">
+        <v>0.031533</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>46.38383151692832</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1156312324359332</v>
+      </c>
+      <c r="C4">
+        <v>29.6446104721207</v>
+      </c>
+      <c r="D4">
+        <v>30.0986104721207</v>
+      </c>
+      <c r="E4">
+        <v>-17.782</v>
+      </c>
+      <c r="F4">
+        <v>0.618</v>
+      </c>
+      <c r="G4">
+        <v>0.164</v>
+      </c>
+      <c r="H4">
+        <v>12.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>-0.655</v>
+      </c>
+      <c r="L4">
+        <v>0.655</v>
+      </c>
+      <c r="M4">
+        <v>0.0282426</v>
+      </c>
+      <c r="N4">
+        <v>0.6267574</v>
+      </c>
+      <c r="O4">
+        <v>0.194294794</v>
+      </c>
+      <c r="P4">
+        <v>0.432462606</v>
+      </c>
+      <c r="Q4">
+        <v>-0.2225373940000001</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1173475228938093</v>
+      </c>
+      <c r="T4">
+        <v>0.7674314314574672</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W4">
+        <v>0.031533</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>23.19191575846416</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1153184463415969</v>
+      </c>
+      <c r="C5">
+        <v>29.45864520772545</v>
+      </c>
+      <c r="D5">
+        <v>30.22164520772545</v>
+      </c>
+      <c r="E5">
+        <v>-17.473</v>
+      </c>
+      <c r="F5">
+        <v>0.9269999999999999</v>
+      </c>
+      <c r="G5">
+        <v>0.164</v>
+      </c>
+      <c r="H5">
+        <v>12.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>-0.655</v>
+      </c>
+      <c r="L5">
+        <v>0.655</v>
+      </c>
+      <c r="M5">
+        <v>0.0423639</v>
+      </c>
+      <c r="N5">
+        <v>0.6126361</v>
+      </c>
+      <c r="O5">
+        <v>0.189917191</v>
+      </c>
+      <c r="P5">
+        <v>0.422718909</v>
+      </c>
+      <c r="Q5">
+        <v>-0.2322810910000001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.11790974880577</v>
+      </c>
+      <c r="T5">
+        <v>0.7729245370389346</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W5">
+        <v>0.031533</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>15.46127717230944</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1150498202472606</v>
+      </c>
+      <c r="C6">
+        <v>29.2561152622153</v>
+      </c>
+      <c r="D6">
+        <v>30.3281152622153</v>
+      </c>
+      <c r="E6">
+        <v>-17.164</v>
+      </c>
+      <c r="F6">
+        <v>1.236</v>
+      </c>
+      <c r="G6">
+        <v>0.164</v>
+      </c>
+      <c r="H6">
+        <v>12.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>-0.655</v>
+      </c>
+      <c r="L6">
+        <v>0.655</v>
+      </c>
+      <c r="M6">
+        <v>0.0584628</v>
+      </c>
+      <c r="N6">
+        <v>0.5965372</v>
+      </c>
+      <c r="O6">
+        <v>0.184926532</v>
+      </c>
+      <c r="P6">
+        <v>0.411610668</v>
+      </c>
+      <c r="Q6">
+        <v>-0.2433893320000001</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1184836877575631</v>
+      </c>
+      <c r="T6">
+        <v>0.778532082320016</v>
+      </c>
+      <c r="U6">
+        <v>0.0473</v>
+      </c>
+      <c r="V6">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W6">
+        <v>0.032637</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>11.20370560424749</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1148791741529243</v>
+      </c>
+      <c r="C7">
+        <v>29.01514142674326</v>
+      </c>
+      <c r="D7">
+        <v>30.39614142674326</v>
+      </c>
+      <c r="E7">
+        <v>-16.855</v>
+      </c>
+      <c r="F7">
+        <v>1.545</v>
+      </c>
+      <c r="G7">
+        <v>0.164</v>
+      </c>
+      <c r="H7">
+        <v>12.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>-0.655</v>
+      </c>
+      <c r="L7">
+        <v>0.655</v>
+      </c>
+      <c r="M7">
+        <v>0.07894949999999999</v>
+      </c>
+      <c r="N7">
+        <v>0.5760505</v>
+      </c>
+      <c r="O7">
+        <v>0.178575655</v>
+      </c>
+      <c r="P7">
+        <v>0.397474845</v>
+      </c>
+      <c r="Q7">
+        <v>-0.2575251550000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1190697096346572</v>
+      </c>
+      <c r="T7">
+        <v>0.7842576811859624</v>
+      </c>
+      <c r="U7">
+        <v>0.0511</v>
+      </c>
+      <c r="V7">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W7">
+        <v>0.035259</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>8.296442662714774</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.114682308058588</v>
+      </c>
+      <c r="C8">
+        <v>28.78499998809535</v>
+      </c>
+      <c r="D8">
+        <v>30.47499998809534</v>
+      </c>
+      <c r="E8">
+        <v>-16.546</v>
+      </c>
+      <c r="F8">
+        <v>1.854</v>
+      </c>
+      <c r="G8">
+        <v>0.164</v>
+      </c>
+      <c r="H8">
+        <v>12.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>-0.655</v>
+      </c>
+      <c r="L8">
+        <v>0.655</v>
+      </c>
+      <c r="M8">
+        <v>0.098262</v>
+      </c>
+      <c r="N8">
+        <v>0.5567380000000001</v>
+      </c>
+      <c r="O8">
+        <v>0.1725887800000001</v>
+      </c>
+      <c r="P8">
+        <v>0.38414922</v>
+      </c>
+      <c r="Q8">
+        <v>-0.27085078</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1196682000623277</v>
+      </c>
+      <c r="T8">
+        <v>0.7901051013043756</v>
+      </c>
+      <c r="U8">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V8">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W8">
+        <v>0.03657</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>6.665852516740959</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1145164919642517</v>
+      </c>
+      <c r="C9">
+        <v>28.54273902132089</v>
+      </c>
+      <c r="D9">
+        <v>30.54173902132089</v>
+      </c>
+      <c r="E9">
+        <v>-16.237</v>
+      </c>
+      <c r="F9">
+        <v>2.163</v>
+      </c>
+      <c r="G9">
+        <v>0.164</v>
+      </c>
+      <c r="H9">
+        <v>12.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>-0.655</v>
+      </c>
+      <c r="L9">
+        <v>0.655</v>
+      </c>
+      <c r="M9">
+        <v>0.118965</v>
+      </c>
+      <c r="N9">
+        <v>0.536035</v>
+      </c>
+      <c r="O9">
+        <v>0.16617085</v>
+      </c>
+      <c r="P9">
+        <v>0.36986415</v>
+      </c>
+      <c r="Q9">
+        <v>-0.28513585</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1202795612518836</v>
+      </c>
+      <c r="T9">
+        <v>0.7960782723930773</v>
+      </c>
+      <c r="U9">
+        <v>0.055</v>
+      </c>
+      <c r="V9">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W9">
+        <v>0.03795</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>5.505821039801623</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1142678758699155</v>
+      </c>
+      <c r="C10">
+        <v>28.33435359119174</v>
+      </c>
+      <c r="D10">
+        <v>30.64235359119174</v>
+      </c>
+      <c r="E10">
+        <v>-15.928</v>
+      </c>
+      <c r="F10">
+        <v>2.472</v>
+      </c>
+      <c r="G10">
+        <v>0.164</v>
+      </c>
+      <c r="H10">
+        <v>12.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>-0.655</v>
+      </c>
+      <c r="L10">
+        <v>0.655</v>
+      </c>
+      <c r="M10">
+        <v>0.13596</v>
+      </c>
+      <c r="N10">
+        <v>0.5190400000000001</v>
+      </c>
+      <c r="O10">
+        <v>0.1609024000000001</v>
+      </c>
+      <c r="P10">
+        <v>0.3581376</v>
+      </c>
+      <c r="Q10">
+        <v>-0.2968624</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.120904212902082</v>
+      </c>
+      <c r="T10">
+        <v>0.8021812950271855</v>
+      </c>
+      <c r="U10">
+        <v>0.055</v>
+      </c>
+      <c r="V10">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W10">
+        <v>0.03795</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>4.81759340982642</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1142552397755792</v>
+      </c>
+      <c r="C11">
+        <v>28.03048510587271</v>
+      </c>
+      <c r="D11">
+        <v>30.6474851058727</v>
+      </c>
+      <c r="E11">
+        <v>-15.619</v>
+      </c>
+      <c r="F11">
+        <v>2.781</v>
+      </c>
+      <c r="G11">
+        <v>0.164</v>
+      </c>
+      <c r="H11">
+        <v>12.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>-0.655</v>
+      </c>
+      <c r="L11">
+        <v>0.655</v>
+      </c>
+      <c r="M11">
+        <v>0.1635228</v>
+      </c>
+      <c r="N11">
+        <v>0.4914772000000001</v>
+      </c>
+      <c r="O11">
+        <v>0.1523579320000001</v>
+      </c>
+      <c r="P11">
+        <v>0.339119268</v>
+      </c>
+      <c r="Q11">
+        <v>-0.315880732</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1215425931599771</v>
+      </c>
+      <c r="T11">
+        <v>0.8084184500268785</v>
+      </c>
+      <c r="U11">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V11">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W11">
+        <v>0.040572</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>4.005557634776313</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1148125436812429</v>
+      </c>
+      <c r="C12">
+        <v>27.49678583492213</v>
+      </c>
+      <c r="D12">
+        <v>30.42278583492213</v>
+      </c>
+      <c r="E12">
+        <v>-15.31</v>
+      </c>
+      <c r="F12">
+        <v>3.09</v>
+      </c>
+      <c r="G12">
+        <v>0.164</v>
+      </c>
+      <c r="H12">
+        <v>12.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>-0.655</v>
+      </c>
+      <c r="L12">
+        <v>0.655</v>
+      </c>
+      <c r="M12">
+        <v>0.216609</v>
+      </c>
+      <c r="N12">
+        <v>0.4383910000000001</v>
+      </c>
+      <c r="O12">
+        <v>0.1359012100000001</v>
+      </c>
+      <c r="P12">
+        <v>0.30248979</v>
+      </c>
+      <c r="Q12">
+        <v>-0.35251021</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1221951596458255</v>
+      </c>
+      <c r="T12">
+        <v>0.814794208471009</v>
+      </c>
+      <c r="U12">
+        <v>0.0701</v>
+      </c>
+      <c r="V12">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W12">
+        <v>0.048369</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>3.023881740832561</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1162847875869066</v>
+      </c>
+      <c r="C13">
+        <v>26.60973997026076</v>
+      </c>
+      <c r="D13">
+        <v>29.84473997026076</v>
+      </c>
+      <c r="E13">
+        <v>-15.001</v>
+      </c>
+      <c r="F13">
+        <v>3.399</v>
+      </c>
+      <c r="G13">
+        <v>0.164</v>
+      </c>
+      <c r="H13">
+        <v>12.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>-0.655</v>
+      </c>
+      <c r="L13">
+        <v>0.655</v>
+      </c>
+      <c r="M13">
+        <v>0.3106686</v>
+      </c>
+      <c r="N13">
+        <v>0.3443314</v>
+      </c>
+      <c r="O13">
+        <v>0.106742734</v>
+      </c>
+      <c r="P13">
+        <v>0.237588666</v>
+      </c>
+      <c r="Q13">
+        <v>-0.417411334</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1228623905470861</v>
+      </c>
+      <c r="T13">
+        <v>0.8213132423857943</v>
+      </c>
+      <c r="U13">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V13">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W13">
+        <v>0.063066</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>2.108355978042197</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1180344114925704</v>
+      </c>
+      <c r="C14">
+        <v>25.64171986111056</v>
+      </c>
+      <c r="D14">
+        <v>29.18571986111056</v>
+      </c>
+      <c r="E14">
+        <v>-14.692</v>
+      </c>
+      <c r="F14">
+        <v>3.708</v>
+      </c>
+      <c r="G14">
+        <v>0.164</v>
+      </c>
+      <c r="H14">
+        <v>12.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>-0.655</v>
+      </c>
+      <c r="L14">
+        <v>0.655</v>
+      </c>
+      <c r="M14">
+        <v>0.41715</v>
+      </c>
+      <c r="N14">
+        <v>0.2378500000000001</v>
+      </c>
+      <c r="O14">
+        <v>0.07373350000000004</v>
+      </c>
+      <c r="P14">
+        <v>0.1641165</v>
+      </c>
+      <c r="Q14">
+        <v>-0.4908835</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1235447857870118</v>
+      </c>
+      <c r="T14">
+        <v>0.8279804361622792</v>
+      </c>
+      <c r="U14">
+        <v>0.1125</v>
+      </c>
+      <c r="V14">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="W14">
+        <v>0.077625</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>1.570178592832315</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1276106756062078</v>
+      </c>
+      <c r="C15">
+        <v>22.18568646868479</v>
+      </c>
+      <c r="D15">
+        <v>26.03868646868479</v>
+      </c>
+      <c r="E15">
+        <v>-14.383</v>
+      </c>
+      <c r="F15">
+        <v>4.017</v>
+      </c>
+      <c r="G15">
+        <v>0.164</v>
+      </c>
+      <c r="H15">
+        <v>12.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>-0.655</v>
+      </c>
+      <c r="L15">
+        <v>0.655</v>
+      </c>
+      <c r="M15">
+        <v>0.7897422000000001</v>
+      </c>
+      <c r="N15">
+        <v>-0.1347422</v>
+      </c>
+      <c r="O15">
+        <v>-0.04177008200000002</v>
+      </c>
+      <c r="P15">
+        <v>-0.09297211800000002</v>
+      </c>
+      <c r="Q15">
+        <v>-0.7479721180000001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1248550264565644</v>
+      </c>
+      <c r="T15">
+        <v>0.8407818566978187</v>
+      </c>
+      <c r="U15">
+        <v>0.1966</v>
+      </c>
+      <c r="V15">
+        <v>0.2571092186792096</v>
+      </c>
+      <c r="W15">
+        <v>0.1460523276076674</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.8293845763845467</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1318049526111058</v>
+      </c>
+      <c r="C16">
+        <v>20.70241068199607</v>
+      </c>
+      <c r="D16">
+        <v>24.86441068199607</v>
+      </c>
+      <c r="E16">
+        <v>-14.074</v>
+      </c>
+      <c r="F16">
+        <v>4.326000000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.164</v>
+      </c>
+      <c r="H16">
+        <v>12.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>-0.655</v>
+      </c>
+      <c r="L16">
+        <v>0.655</v>
+      </c>
+      <c r="M16">
+        <v>0.9248988</v>
+      </c>
+      <c r="N16">
+        <v>-0.2698988</v>
+      </c>
+      <c r="O16">
+        <v>-0.08366862800000001</v>
+      </c>
+      <c r="P16">
+        <v>-0.186230172</v>
+      </c>
+      <c r="Q16">
+        <v>-0.8412301719999999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1260978488629175</v>
+      </c>
+      <c r="T16">
+        <v>0.8529245818050685</v>
+      </c>
+      <c r="U16">
+        <v>0.2138</v>
+      </c>
+      <c r="V16">
+        <v>0.2195375321062153</v>
+      </c>
+      <c r="W16">
+        <v>0.1668628756356912</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.7081855874394042</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1335549526111058</v>
+      </c>
+      <c r="C17">
+        <v>19.93419754859842</v>
+      </c>
+      <c r="D17">
+        <v>24.40519754859842</v>
+      </c>
+      <c r="E17">
+        <v>-13.765</v>
+      </c>
+      <c r="F17">
+        <v>4.635</v>
+      </c>
+      <c r="G17">
+        <v>0.164</v>
+      </c>
+      <c r="H17">
+        <v>12.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>-0.655</v>
+      </c>
+      <c r="L17">
+        <v>0.655</v>
+      </c>
+      <c r="M17">
+        <v>0.9909629999999999</v>
+      </c>
+      <c r="N17">
+        <v>-0.3359629999999999</v>
+      </c>
+      <c r="O17">
+        <v>-0.10414853</v>
+      </c>
+      <c r="P17">
+        <v>-0.2318144699999999</v>
+      </c>
+      <c r="Q17">
+        <v>-0.8868144699999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1271248823789518</v>
+      </c>
+      <c r="T17">
+        <v>0.8629589886498339</v>
+      </c>
+      <c r="U17">
+        <v>0.2138</v>
+      </c>
+      <c r="V17">
+        <v>0.2049016966324677</v>
+      </c>
+      <c r="W17">
+        <v>0.1699920172599784</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.660973214943444</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1353049526111058</v>
+      </c>
+      <c r="C18">
+        <v>19.18263895907032</v>
+      </c>
+      <c r="D18">
+        <v>23.96263895907031</v>
+      </c>
+      <c r="E18">
+        <v>-13.456</v>
+      </c>
+      <c r="F18">
+        <v>4.944</v>
+      </c>
+      <c r="G18">
+        <v>0.164</v>
+      </c>
+      <c r="H18">
+        <v>12.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>-0.655</v>
+      </c>
+      <c r="L18">
+        <v>0.655</v>
+      </c>
+      <c r="M18">
+        <v>1.0570272</v>
+      </c>
+      <c r="N18">
+        <v>-0.4020271999999998</v>
+      </c>
+      <c r="O18">
+        <v>-0.124628432</v>
+      </c>
+      <c r="P18">
+        <v>-0.2773987679999999</v>
+      </c>
+      <c r="Q18">
+        <v>-0.9323987679999999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1281763690739393</v>
+      </c>
+      <c r="T18">
+        <v>0.8732323099432843</v>
+      </c>
+      <c r="U18">
+        <v>0.2138</v>
+      </c>
+      <c r="V18">
+        <v>0.1920953405929385</v>
+      </c>
+      <c r="W18">
+        <v>0.1727300161812298</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.6196623890094788</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1370549526111058</v>
+      </c>
+      <c r="C19">
+        <v>18.44684502081103</v>
+      </c>
+      <c r="D19">
+        <v>23.53584502081103</v>
+      </c>
+      <c r="E19">
+        <v>-13.147</v>
+      </c>
+      <c r="F19">
+        <v>5.253</v>
+      </c>
+      <c r="G19">
+        <v>0.164</v>
+      </c>
+      <c r="H19">
+        <v>12.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>-0.655</v>
+      </c>
+      <c r="L19">
+        <v>0.655</v>
+      </c>
+      <c r="M19">
+        <v>1.1230914</v>
+      </c>
+      <c r="N19">
+        <v>-0.4680914</v>
+      </c>
+      <c r="O19">
+        <v>-0.145108334</v>
+      </c>
+      <c r="P19">
+        <v>-0.322983066</v>
+      </c>
+      <c r="Q19">
+        <v>-0.9779830660000001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1292531927977217</v>
+      </c>
+      <c r="T19">
+        <v>0.8837531811474203</v>
+      </c>
+      <c r="U19">
+        <v>0.2138</v>
+      </c>
+      <c r="V19">
+        <v>0.1807956146757068</v>
+      </c>
+      <c r="W19">
+        <v>0.1751458975823339</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.5832116602442152</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1388049526111058</v>
+      </c>
+      <c r="C20">
+        <v>17.72598813061693</v>
+      </c>
+      <c r="D20">
+        <v>23.12398813061692</v>
+      </c>
+      <c r="E20">
+        <v>-12.838</v>
+      </c>
+      <c r="F20">
+        <v>5.561999999999999</v>
+      </c>
+      <c r="G20">
+        <v>0.164</v>
+      </c>
+      <c r="H20">
+        <v>12.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>-0.655</v>
+      </c>
+      <c r="L20">
+        <v>0.655</v>
+      </c>
+      <c r="M20">
+        <v>1.1891556</v>
+      </c>
+      <c r="N20">
+        <v>-0.5341555999999998</v>
+      </c>
+      <c r="O20">
+        <v>-0.165588236</v>
+      </c>
+      <c r="P20">
+        <v>-0.3685673639999999</v>
+      </c>
+      <c r="Q20">
+        <v>-1.023567364</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1303562805147671</v>
+      </c>
+      <c r="T20">
+        <v>0.8945306589662914</v>
+      </c>
+      <c r="U20">
+        <v>0.2138</v>
+      </c>
+      <c r="V20">
+        <v>0.1707514138603897</v>
+      </c>
+      <c r="W20">
+        <v>0.1772933477166487</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.55081101245287</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1405549526111058</v>
+      </c>
+      <c r="C21">
+        <v>17.0192976183601</v>
+      </c>
+      <c r="D21">
+        <v>22.72629761836009</v>
+      </c>
+      <c r="E21">
+        <v>-12.529</v>
+      </c>
+      <c r="F21">
+        <v>5.871</v>
+      </c>
+      <c r="G21">
+        <v>0.164</v>
+      </c>
+      <c r="H21">
+        <v>12.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>-0.655</v>
+      </c>
+      <c r="L21">
+        <v>0.655</v>
+      </c>
+      <c r="M21">
+        <v>1.2552198</v>
+      </c>
+      <c r="N21">
+        <v>-0.6002197999999999</v>
+      </c>
+      <c r="O21">
+        <v>-0.186068138</v>
+      </c>
+      <c r="P21">
+        <v>-0.4141516619999999</v>
+      </c>
+      <c r="Q21">
+        <v>-1.069151662</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1314866049655667</v>
+      </c>
+      <c r="T21">
+        <v>0.9055742473485912</v>
+      </c>
+      <c r="U21">
+        <v>0.2138</v>
+      </c>
+      <c r="V21">
+        <v>0.1617644973414218</v>
+      </c>
+      <c r="W21">
+        <v>0.179214750468404</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.5218209591658769</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1475541836205799</v>
+      </c>
+      <c r="C22">
+        <v>15.24767244178837</v>
+      </c>
+      <c r="D22">
+        <v>21.26367244178837</v>
+      </c>
+      <c r="E22">
+        <v>-12.22</v>
+      </c>
+      <c r="F22">
+        <v>6.18</v>
+      </c>
+      <c r="G22">
+        <v>0.164</v>
+      </c>
+      <c r="H22">
+        <v>12.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>-0.655</v>
+      </c>
+      <c r="L22">
+        <v>0.655</v>
+      </c>
+      <c r="M22">
+        <v>1.475784</v>
+      </c>
+      <c r="N22">
+        <v>-0.820784</v>
+      </c>
+      <c r="O22">
+        <v>-0.25444304</v>
+      </c>
+      <c r="P22">
+        <v>-0.56634096</v>
+      </c>
+      <c r="Q22">
+        <v>-1.22134096</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1329567262894789</v>
+      </c>
+      <c r="T22">
+        <v>0.9199377469277106</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.1375878854900175</v>
+      </c>
+      <c r="W22">
+        <v>0.2059440129449838</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.4438318886774758</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1495541836205798</v>
+      </c>
+      <c r="C23">
+        <v>14.55469286202581</v>
+      </c>
+      <c r="D23">
+        <v>20.87969286202581</v>
+      </c>
+      <c r="E23">
+        <v>-11.911</v>
+      </c>
+      <c r="F23">
+        <v>6.489</v>
+      </c>
+      <c r="G23">
+        <v>0.164</v>
+      </c>
+      <c r="H23">
+        <v>12.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>-0.655</v>
+      </c>
+      <c r="L23">
+        <v>0.655</v>
+      </c>
+      <c r="M23">
+        <v>1.5495732</v>
+      </c>
+      <c r="N23">
+        <v>-0.8945732</v>
+      </c>
+      <c r="O23">
+        <v>-0.2773176920000001</v>
+      </c>
+      <c r="P23">
+        <v>-0.617255508</v>
+      </c>
+      <c r="Q23">
+        <v>-1.272255508</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1341485835842824</v>
+      </c>
+      <c r="T23">
+        <v>0.9315825285343903</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.1310360814190643</v>
+      </c>
+      <c r="W23">
+        <v>0.2075085837571274</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.4226970368356913</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1515541836205799</v>
+      </c>
+      <c r="C24">
+        <v>13.87533511224534</v>
+      </c>
+      <c r="D24">
+        <v>20.50933511224534</v>
+      </c>
+      <c r="E24">
+        <v>-11.602</v>
+      </c>
+      <c r="F24">
+        <v>6.798</v>
+      </c>
+      <c r="G24">
+        <v>0.164</v>
+      </c>
+      <c r="H24">
+        <v>12.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>-0.655</v>
+      </c>
+      <c r="L24">
+        <v>0.655</v>
+      </c>
+      <c r="M24">
+        <v>1.6233624</v>
+      </c>
+      <c r="N24">
+        <v>-0.9683624</v>
+      </c>
+      <c r="O24">
+        <v>-0.3001923440000001</v>
+      </c>
+      <c r="P24">
+        <v>-0.6681700559999999</v>
+      </c>
+      <c r="Q24">
+        <v>-1.323170056</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1353710013225425</v>
+      </c>
+      <c r="T24">
+        <v>0.9435258942848314</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.1250798959000159</v>
+      </c>
+      <c r="W24">
+        <v>0.2089309208590762</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.4034835351613417</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1535541836205799</v>
+      </c>
+      <c r="C25">
+        <v>13.20888696586566</v>
+      </c>
+      <c r="D25">
+        <v>20.15188696586565</v>
+      </c>
+      <c r="E25">
+        <v>-11.293</v>
+      </c>
+      <c r="F25">
+        <v>7.107</v>
+      </c>
+      <c r="G25">
+        <v>0.164</v>
+      </c>
+      <c r="H25">
+        <v>12.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>-0.655</v>
+      </c>
+      <c r="L25">
+        <v>0.655</v>
+      </c>
+      <c r="M25">
+        <v>1.6971516</v>
+      </c>
+      <c r="N25">
+        <v>-1.0421516</v>
+      </c>
+      <c r="O25">
+        <v>-0.3230669960000001</v>
+      </c>
+      <c r="P25">
+        <v>-0.7190846040000001</v>
+      </c>
+      <c r="Q25">
+        <v>-1.374084604</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1366251701708872</v>
+      </c>
+      <c r="T25">
+        <v>0.9557794773274915</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.119641639556537</v>
+      </c>
+      <c r="W25">
+        <v>0.210229576473899</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.3859407727630224</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1555541836205799</v>
+      </c>
+      <c r="C26">
+        <v>12.55468499809114</v>
+      </c>
+      <c r="D26">
+        <v>19.80668499809114</v>
+      </c>
+      <c r="E26">
+        <v>-10.984</v>
+      </c>
+      <c r="F26">
+        <v>7.415999999999999</v>
+      </c>
+      <c r="G26">
+        <v>0.164</v>
+      </c>
+      <c r="H26">
+        <v>12.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>-0.655</v>
+      </c>
+      <c r="L26">
+        <v>0.655</v>
+      </c>
+      <c r="M26">
+        <v>1.7709408</v>
+      </c>
+      <c r="N26">
+        <v>-1.1159408</v>
+      </c>
+      <c r="O26">
+        <v>-0.345941648</v>
+      </c>
+      <c r="P26">
+        <v>-0.7699991519999999</v>
+      </c>
+      <c r="Q26">
+        <v>-1.424999152</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1379123434626093</v>
+      </c>
+      <c r="T26">
+        <v>0.9683555230818005</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.1146565712416813</v>
+      </c>
+      <c r="W26">
+        <v>0.2114200107874865</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.3698599072312299</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1575541836205799</v>
+      </c>
+      <c r="C27">
+        <v>11.91211047643262</v>
+      </c>
+      <c r="D27">
+        <v>19.47311047643262</v>
+      </c>
+      <c r="E27">
+        <v>-10.675</v>
+      </c>
+      <c r="F27">
+        <v>7.725</v>
+      </c>
+      <c r="G27">
+        <v>0.164</v>
+      </c>
+      <c r="H27">
+        <v>12.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>-0.655</v>
+      </c>
+      <c r="L27">
+        <v>0.655</v>
+      </c>
+      <c r="M27">
+        <v>1.84473</v>
+      </c>
+      <c r="N27">
+        <v>-1.18973</v>
+      </c>
+      <c r="O27">
+        <v>-0.3688163</v>
+      </c>
+      <c r="P27">
+        <v>-0.8209137</v>
+      </c>
+      <c r="Q27">
+        <v>-1.4759137</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1392338413754441</v>
+      </c>
+      <c r="T27">
+        <v>0.9812669300562245</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.110070308392014</v>
+      </c>
+      <c r="W27">
+        <v>0.2125152103559871</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.3550655109419807</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1595541836205799</v>
+      </c>
+      <c r="C28">
+        <v>11.2805856596094</v>
+      </c>
+      <c r="D28">
+        <v>19.1505856596094</v>
+      </c>
+      <c r="E28">
+        <v>-10.366</v>
+      </c>
+      <c r="F28">
+        <v>8.034000000000001</v>
+      </c>
+      <c r="G28">
+        <v>0.164</v>
+      </c>
+      <c r="H28">
+        <v>12.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>-0.655</v>
+      </c>
+      <c r="L28">
+        <v>0.655</v>
+      </c>
+      <c r="M28">
+        <v>1.9185192</v>
+      </c>
+      <c r="N28">
+        <v>-1.2635192</v>
+      </c>
+      <c r="O28">
+        <v>-0.3916909520000001</v>
+      </c>
+      <c r="P28">
+        <v>-0.871828248</v>
+      </c>
+      <c r="Q28">
+        <v>-1.526828248</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1405910554480853</v>
+      </c>
+      <c r="T28">
+        <v>0.9945272939759033</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.1058368349923212</v>
+      </c>
+      <c r="W28">
+        <v>0.2135261638038337</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.3414091451365199</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1615541836205799</v>
+      </c>
+      <c r="C29">
+        <v>10.65957045825705</v>
+      </c>
+      <c r="D29">
+        <v>18.83857045825705</v>
+      </c>
+      <c r="E29">
+        <v>-10.057</v>
+      </c>
+      <c r="F29">
+        <v>8.343</v>
+      </c>
+      <c r="G29">
+        <v>0.164</v>
+      </c>
+      <c r="H29">
+        <v>12.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>-0.655</v>
+      </c>
+      <c r="L29">
+        <v>0.655</v>
+      </c>
+      <c r="M29">
+        <v>1.9923084</v>
+      </c>
+      <c r="N29">
+        <v>-1.3373084</v>
+      </c>
+      <c r="O29">
+        <v>-0.4145656040000001</v>
+      </c>
+      <c r="P29">
+        <v>-0.9227427960000001</v>
+      </c>
+      <c r="Q29">
+        <v>-1.577742796</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1419854534679221</v>
+      </c>
+      <c r="T29">
+        <v>1.008150955537217</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.1019169522148278</v>
+      </c>
+      <c r="W29">
+        <v>0.2144622318110991</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.3287643619833154</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1635541836205799</v>
+      </c>
+      <c r="C30">
+        <v>10.04855941683896</v>
+      </c>
+      <c r="D30">
+        <v>18.53655941683896</v>
+      </c>
+      <c r="E30">
+        <v>-9.747999999999998</v>
+      </c>
+      <c r="F30">
+        <v>8.652000000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.164</v>
+      </c>
+      <c r="H30">
+        <v>12.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>-0.655</v>
+      </c>
+      <c r="L30">
+        <v>0.655</v>
+      </c>
+      <c r="M30">
+        <v>2.0660976</v>
+      </c>
+      <c r="N30">
+        <v>-1.4110976</v>
+      </c>
+      <c r="O30">
+        <v>-0.4374402560000002</v>
+      </c>
+      <c r="P30">
+        <v>-0.9736573440000003</v>
+      </c>
+      <c r="Q30">
+        <v>-1.628657344</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1434185847660877</v>
+      </c>
+      <c r="T30">
+        <v>1.022153052141901</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.09827706106429822</v>
+      </c>
+      <c r="W30">
+        <v>0.2153314378178456</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.3170227776267684</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1655541836205799</v>
+      </c>
+      <c r="C31">
+        <v>9.447078981284658</v>
+      </c>
+      <c r="D31">
+        <v>18.24407898128466</v>
+      </c>
+      <c r="E31">
+        <v>-9.439</v>
+      </c>
+      <c r="F31">
+        <v>8.960999999999999</v>
+      </c>
+      <c r="G31">
+        <v>0.164</v>
+      </c>
+      <c r="H31">
+        <v>12.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>-0.655</v>
+      </c>
+      <c r="L31">
+        <v>0.655</v>
+      </c>
+      <c r="M31">
+        <v>2.1398868</v>
+      </c>
+      <c r="N31">
+        <v>-1.4848868</v>
+      </c>
+      <c r="O31">
+        <v>-0.460314908</v>
+      </c>
+      <c r="P31">
+        <v>-1.024571892</v>
+      </c>
+      <c r="Q31">
+        <v>-1.679571892</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1448920859599762</v>
+      </c>
+      <c r="T31">
+        <v>1.036549574003054</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.09488819688966728</v>
+      </c>
+      <c r="W31">
+        <v>0.2161406985827475</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.3060909577086041</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1675541836205799</v>
+      </c>
+      <c r="C32">
+        <v>8.854685021286475</v>
+      </c>
+      <c r="D32">
+        <v>17.96068502128647</v>
+      </c>
+      <c r="E32">
+        <v>-9.129999999999999</v>
+      </c>
+      <c r="F32">
+        <v>9.27</v>
+      </c>
+      <c r="G32">
+        <v>0.164</v>
+      </c>
+      <c r="H32">
+        <v>12.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>-0.655</v>
+      </c>
+      <c r="L32">
+        <v>0.655</v>
+      </c>
+      <c r="M32">
+        <v>2.213676</v>
+      </c>
+      <c r="N32">
+        <v>-1.558676</v>
+      </c>
+      <c r="O32">
+        <v>-0.4831895600000001</v>
+      </c>
+      <c r="P32">
+        <v>-1.07548644</v>
+      </c>
+      <c r="Q32">
+        <v>-1.73048644</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1464076871879759</v>
+      </c>
+      <c r="T32">
+        <v>1.051357425060241</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.09172525699334502</v>
+      </c>
+      <c r="W32">
+        <v>0.2168960086299892</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.2958879257849839</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1695541836205799</v>
+      </c>
+      <c r="C33">
+        <v>8.270960579988225</v>
+      </c>
+      <c r="D33">
+        <v>17.68596057998822</v>
+      </c>
+      <c r="E33">
+        <v>-8.821</v>
+      </c>
+      <c r="F33">
+        <v>9.578999999999999</v>
+      </c>
+      <c r="G33">
+        <v>0.164</v>
+      </c>
+      <c r="H33">
+        <v>12.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>-0.655</v>
+      </c>
+      <c r="L33">
+        <v>0.655</v>
+      </c>
+      <c r="M33">
+        <v>2.2874652</v>
+      </c>
+      <c r="N33">
+        <v>-1.6324652</v>
+      </c>
+      <c r="O33">
+        <v>-0.506064212</v>
+      </c>
+      <c r="P33">
+        <v>-1.126400988</v>
+      </c>
+      <c r="Q33">
+        <v>-1.781400988</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1479672188863523</v>
+      </c>
+      <c r="T33">
+        <v>1.066594489191548</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.0887663777354952</v>
+      </c>
+      <c r="W33">
+        <v>0.2176025889967637</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.2863431539854683</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1715541836205799</v>
+      </c>
+      <c r="C34">
+        <v>7.695513827085344</v>
+      </c>
+      <c r="D34">
+        <v>17.41951382708534</v>
+      </c>
+      <c r="E34">
+        <v>-8.511999999999999</v>
+      </c>
+      <c r="F34">
+        <v>9.888</v>
+      </c>
+      <c r="G34">
+        <v>0.164</v>
+      </c>
+      <c r="H34">
+        <v>12.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>-0.655</v>
+      </c>
+      <c r="L34">
+        <v>0.655</v>
+      </c>
+      <c r="M34">
+        <v>2.3612544</v>
+      </c>
+      <c r="N34">
+        <v>-1.7062544</v>
+      </c>
+      <c r="O34">
+        <v>-0.5289388640000001</v>
+      </c>
+      <c r="P34">
+        <v>-1.177315536</v>
+      </c>
+      <c r="Q34">
+        <v>-1.832315536</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1495726191640928</v>
+      </c>
+      <c r="T34">
+        <v>1.082279702267895</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.08599242843126095</v>
+      </c>
+      <c r="W34">
+        <v>0.2182650080906149</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2773949304234224</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1735541836205799</v>
+      </c>
+      <c r="C35">
+        <v>7.12797619420364</v>
+      </c>
+      <c r="D35">
+        <v>17.16097619420364</v>
+      </c>
+      <c r="E35">
+        <v>-8.202999999999999</v>
+      </c>
+      <c r="F35">
+        <v>10.197</v>
+      </c>
+      <c r="G35">
+        <v>0.164</v>
+      </c>
+      <c r="H35">
+        <v>12.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>-0.655</v>
+      </c>
+      <c r="L35">
+        <v>0.655</v>
+      </c>
+      <c r="M35">
+        <v>2.4350436</v>
+      </c>
+      <c r="N35">
+        <v>-1.7800436</v>
+      </c>
+      <c r="O35">
+        <v>-0.5518135160000001</v>
+      </c>
+      <c r="P35">
+        <v>-1.228230084</v>
+      </c>
+      <c r="Q35">
+        <v>-1.883230084</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1512259418381838</v>
+      </c>
+      <c r="T35">
+        <v>1.098433130659953</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.0833865972666773</v>
+      </c>
+      <c r="W35">
+        <v>0.2188872805727175</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2689890234408945</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1755541836205798</v>
+      </c>
+      <c r="C36">
+        <v>6.568000673896108</v>
+      </c>
+      <c r="D36">
+        <v>16.91000067389611</v>
+      </c>
+      <c r="E36">
+        <v>-7.893999999999998</v>
+      </c>
+      <c r="F36">
+        <v>10.506</v>
+      </c>
+      <c r="G36">
+        <v>0.164</v>
+      </c>
+      <c r="H36">
+        <v>12.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>-0.655</v>
+      </c>
+      <c r="L36">
+        <v>0.655</v>
+      </c>
+      <c r="M36">
+        <v>2.5088328</v>
+      </c>
+      <c r="N36">
+        <v>-1.8538328</v>
+      </c>
+      <c r="O36">
+        <v>-0.5746881680000001</v>
+      </c>
+      <c r="P36">
+        <v>-1.279144632</v>
+      </c>
+      <c r="Q36">
+        <v>-1.934144632</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1529293651993683</v>
+      </c>
+      <c r="T36">
+        <v>1.115076056882073</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.0809340502882456</v>
+      </c>
+      <c r="W36">
+        <v>0.219472948791167</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2610775815749858</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1775541836205799</v>
+      </c>
+      <c r="C37">
+        <v>6.015260265749038</v>
+      </c>
+      <c r="D37">
+        <v>16.66626026574904</v>
+      </c>
+      <c r="E37">
+        <v>-7.584999999999997</v>
+      </c>
+      <c r="F37">
+        <v>10.815</v>
+      </c>
+      <c r="G37">
+        <v>0.164</v>
+      </c>
+      <c r="H37">
+        <v>12.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>-0.655</v>
+      </c>
+      <c r="L37">
+        <v>0.655</v>
+      </c>
+      <c r="M37">
+        <v>2.582622000000001</v>
+      </c>
+      <c r="N37">
+        <v>-1.927622000000001</v>
+      </c>
+      <c r="O37">
+        <v>-0.5975628200000003</v>
+      </c>
+      <c r="P37">
+        <v>-1.33005918</v>
+      </c>
+      <c r="Q37">
+        <v>-1.98505918</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.154685201587051</v>
+      </c>
+      <c r="T37">
+        <v>1.132231073141798</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.07862164885143857</v>
+      </c>
+      <c r="W37">
+        <v>0.2200251502542765</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.2536182221014147</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1795541836205799</v>
+      </c>
+      <c r="C38">
+        <v>5.469446554965504</v>
+      </c>
+      <c r="D38">
+        <v>16.4294465549655</v>
+      </c>
+      <c r="E38">
+        <v>-7.276</v>
+      </c>
+      <c r="F38">
+        <v>11.124</v>
+      </c>
+      <c r="G38">
+        <v>0.164</v>
+      </c>
+      <c r="H38">
+        <v>12.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>-0.655</v>
+      </c>
+      <c r="L38">
+        <v>0.655</v>
+      </c>
+      <c r="M38">
+        <v>2.6564112</v>
+      </c>
+      <c r="N38">
+        <v>-2.0014112</v>
+      </c>
+      <c r="O38">
+        <v>-0.620437472</v>
+      </c>
+      <c r="P38">
+        <v>-1.380973728</v>
+      </c>
+      <c r="Q38">
+        <v>-2.035973728</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1564959078618486</v>
+      </c>
+      <c r="T38">
+        <v>1.149922183659638</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.07643771416112086</v>
+      </c>
+      <c r="W38">
+        <v>0.2205466738583244</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2465732714874866</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1815541836205799</v>
+      </c>
+      <c r="C39">
+        <v>4.93026841043374</v>
+      </c>
+      <c r="D39">
+        <v>16.19926841043374</v>
+      </c>
+      <c r="E39">
+        <v>-6.966999999999999</v>
+      </c>
+      <c r="F39">
+        <v>11.433</v>
+      </c>
+      <c r="G39">
+        <v>0.164</v>
+      </c>
+      <c r="H39">
+        <v>12.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>-0.655</v>
+      </c>
+      <c r="L39">
+        <v>0.655</v>
+      </c>
+      <c r="M39">
+        <v>2.7302004</v>
+      </c>
+      <c r="N39">
+        <v>-2.0752004</v>
+      </c>
+      <c r="O39">
+        <v>-0.643312124</v>
+      </c>
+      <c r="P39">
+        <v>-1.431888276</v>
+      </c>
+      <c r="Q39">
+        <v>-2.086888276</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1583640968755287</v>
+      </c>
+      <c r="T39">
+        <v>1.168174916733601</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.07437182999460407</v>
+      </c>
+      <c r="W39">
+        <v>0.2210400069972885</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2399091290148518</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1835541836205799</v>
+      </c>
+      <c r="C40">
+        <v>4.397450790724813</v>
+      </c>
+      <c r="D40">
+        <v>15.97545079072481</v>
+      </c>
+      <c r="E40">
+        <v>-6.657999999999999</v>
+      </c>
+      <c r="F40">
+        <v>11.742</v>
+      </c>
+      <c r="G40">
+        <v>0.164</v>
+      </c>
+      <c r="H40">
+        <v>12.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>-0.655</v>
+      </c>
+      <c r="L40">
+        <v>0.655</v>
+      </c>
+      <c r="M40">
+        <v>2.8039896</v>
+      </c>
+      <c r="N40">
+        <v>-2.1489896</v>
+      </c>
+      <c r="O40">
+        <v>-0.6661867760000002</v>
+      </c>
+      <c r="P40">
+        <v>-1.482802824</v>
+      </c>
+      <c r="Q40">
+        <v>-2.137802824</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1602925500509405</v>
+      </c>
+      <c r="T40">
+        <v>1.187016447648659</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.07241467657369344</v>
+      </c>
+      <c r="W40">
+        <v>0.221507375234202</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.233595730882882</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1855541836205799</v>
+      </c>
+      <c r="C41">
+        <v>3.870733647722906</v>
+      </c>
+      <c r="D41">
+        <v>15.75773364772291</v>
+      </c>
+      <c r="E41">
+        <v>-6.348999999999998</v>
+      </c>
+      <c r="F41">
+        <v>12.051</v>
+      </c>
+      <c r="G41">
+        <v>0.164</v>
+      </c>
+      <c r="H41">
+        <v>12.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>-0.655</v>
+      </c>
+      <c r="L41">
+        <v>0.655</v>
+      </c>
+      <c r="M41">
+        <v>2.8777788</v>
+      </c>
+      <c r="N41">
+        <v>-2.2227788</v>
+      </c>
+      <c r="O41">
+        <v>-0.6890614280000003</v>
+      </c>
+      <c r="P41">
+        <v>-1.533717372</v>
+      </c>
+      <c r="Q41">
+        <v>-2.188717372</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1622842311993166</v>
+      </c>
+      <c r="T41">
+        <v>1.206475733675686</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.07055788999488079</v>
+      </c>
+      <c r="W41">
+        <v>0.2219507758692225</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2276060967576798</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1875541836205799</v>
+      </c>
+      <c r="C42">
+        <v>3.349870918699896</v>
+      </c>
+      <c r="D42">
+        <v>15.5458709186999</v>
+      </c>
+      <c r="E42">
+        <v>-6.039999999999999</v>
+      </c>
+      <c r="F42">
+        <v>12.36</v>
+      </c>
+      <c r="G42">
+        <v>0.164</v>
+      </c>
+      <c r="H42">
+        <v>12.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>-0.655</v>
+      </c>
+      <c r="L42">
+        <v>0.655</v>
+      </c>
+      <c r="M42">
+        <v>2.951568</v>
+      </c>
+      <c r="N42">
+        <v>-2.296568</v>
+      </c>
+      <c r="O42">
+        <v>-0.7119360800000001</v>
+      </c>
+      <c r="P42">
+        <v>-1.58463192</v>
+      </c>
+      <c r="Q42">
+        <v>-2.23963192</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1643423017193052</v>
+      </c>
+      <c r="T42">
+        <v>1.226583662570281</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.06879394274500877</v>
+      </c>
+      <c r="W42">
+        <v>0.2223720064724919</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.221915944338738</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1895541836205799</v>
+      </c>
+      <c r="C43">
+        <v>2.834629598620502</v>
+      </c>
+      <c r="D43">
+        <v>15.3396295986205</v>
+      </c>
+      <c r="E43">
+        <v>-5.730999999999998</v>
+      </c>
+      <c r="F43">
+        <v>12.669</v>
+      </c>
+      <c r="G43">
+        <v>0.164</v>
+      </c>
+      <c r="H43">
+        <v>12.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>-0.655</v>
+      </c>
+      <c r="L43">
+        <v>0.655</v>
+      </c>
+      <c r="M43">
+        <v>3.0253572</v>
+      </c>
+      <c r="N43">
+        <v>-2.3703572</v>
+      </c>
+      <c r="O43">
+        <v>-0.7348107320000001</v>
+      </c>
+      <c r="P43">
+        <v>-1.635546468</v>
+      </c>
+      <c r="Q43">
+        <v>-2.290546468</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1664701373416663</v>
+      </c>
+      <c r="T43">
+        <v>1.247373216173167</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.06711604170244757</v>
+      </c>
+      <c r="W43">
+        <v>0.2227726892414555</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.2165033603304761</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1915541836205799</v>
+      </c>
+      <c r="C44">
+        <v>2.324788885324924</v>
+      </c>
+      <c r="D44">
+        <v>15.13878888532492</v>
+      </c>
+      <c r="E44">
+        <v>-5.421999999999999</v>
+      </c>
+      <c r="F44">
+        <v>12.978</v>
+      </c>
+      <c r="G44">
+        <v>0.164</v>
+      </c>
+      <c r="H44">
+        <v>12.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>-0.655</v>
+      </c>
+      <c r="L44">
+        <v>0.655</v>
+      </c>
+      <c r="M44">
+        <v>3.0991464</v>
+      </c>
+      <c r="N44">
+        <v>-2.4441464</v>
+      </c>
+      <c r="O44">
+        <v>-0.7576853840000002</v>
+      </c>
+      <c r="P44">
+        <v>-1.686461016</v>
+      </c>
+      <c r="Q44">
+        <v>-2.341461016</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1686713466061778</v>
+      </c>
+      <c r="T44">
+        <v>1.268879650934773</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.06551804070953217</v>
+      </c>
+      <c r="W44">
+        <v>0.2231542918785637</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.2113485184178455</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1935541836205799</v>
+      </c>
+      <c r="C45">
+        <v>1.820139390996014</v>
+      </c>
+      <c r="D45">
+        <v>14.94313939099601</v>
+      </c>
+      <c r="E45">
+        <v>-5.113</v>
+      </c>
+      <c r="F45">
+        <v>13.287</v>
+      </c>
+      <c r="G45">
+        <v>0.164</v>
+      </c>
+      <c r="H45">
+        <v>12.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>-0.655</v>
+      </c>
+      <c r="L45">
+        <v>0.655</v>
+      </c>
+      <c r="M45">
+        <v>3.1729356</v>
+      </c>
+      <c r="N45">
+        <v>-2.517935599999999</v>
+      </c>
+      <c r="O45">
+        <v>-0.780560036</v>
+      </c>
+      <c r="P45">
+        <v>-1.737375563999999</v>
+      </c>
+      <c r="Q45">
+        <v>-2.392375564</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1709497912834791</v>
+      </c>
+      <c r="T45">
+        <v>1.291140697442401</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.06399436534419421</v>
+      </c>
+      <c r="W45">
+        <v>0.2235181455558064</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.2064334365941749</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1955541836205799</v>
+      </c>
+      <c r="C46">
+        <v>1.320482413990973</v>
+      </c>
+      <c r="D46">
+        <v>14.75248241399097</v>
+      </c>
+      <c r="E46">
+        <v>-4.803999999999998</v>
+      </c>
+      <c r="F46">
+        <v>13.596</v>
+      </c>
+      <c r="G46">
+        <v>0.164</v>
+      </c>
+      <c r="H46">
+        <v>12.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>-0.655</v>
+      </c>
+      <c r="L46">
+        <v>0.655</v>
+      </c>
+      <c r="M46">
+        <v>3.2467248</v>
+      </c>
+      <c r="N46">
+        <v>-2.5917248</v>
+      </c>
+      <c r="O46">
+        <v>-0.8034346880000001</v>
+      </c>
+      <c r="P46">
+        <v>-1.788290112</v>
+      </c>
+      <c r="Q46">
+        <v>-2.443290112</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1733096089849699</v>
+      </c>
+      <c r="T46">
+        <v>1.314196781325301</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.06253994795000797</v>
+      </c>
+      <c r="W46">
+        <v>0.2238654604295381</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.2017417675806709</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1975541836205799</v>
+      </c>
+      <c r="C47">
+        <v>0.8256292657142765</v>
+      </c>
+      <c r="D47">
+        <v>14.56662926571428</v>
+      </c>
+      <c r="E47">
+        <v>-4.494999999999999</v>
+      </c>
+      <c r="F47">
+        <v>13.905</v>
+      </c>
+      <c r="G47">
+        <v>0.164</v>
+      </c>
+      <c r="H47">
+        <v>12.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>-0.655</v>
+      </c>
+      <c r="L47">
+        <v>0.655</v>
+      </c>
+      <c r="M47">
+        <v>3.320514</v>
+      </c>
+      <c r="N47">
+        <v>-2.665514</v>
+      </c>
+      <c r="O47">
+        <v>-0.8263093400000001</v>
+      </c>
+      <c r="P47">
+        <v>-1.83920466</v>
+      </c>
+      <c r="Q47">
+        <v>-2.49420466</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.175755238239242</v>
+      </c>
+      <c r="T47">
+        <v>1.338091268258488</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.06115017132889668</v>
+      </c>
+      <c r="W47">
+        <v>0.2241973390866595</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1972586171899893</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1995541836205799</v>
+      </c>
+      <c r="C48">
+        <v>0.3354006477382061</v>
+      </c>
+      <c r="D48">
+        <v>14.38540064773821</v>
+      </c>
+      <c r="E48">
+        <v>-4.185999999999998</v>
+      </c>
+      <c r="F48">
+        <v>14.214</v>
+      </c>
+      <c r="G48">
+        <v>0.164</v>
+      </c>
+      <c r="H48">
+        <v>12.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>-0.655</v>
+      </c>
+      <c r="L48">
+        <v>0.655</v>
+      </c>
+      <c r="M48">
+        <v>3.3943032</v>
+      </c>
+      <c r="N48">
+        <v>-2.7393032</v>
+      </c>
+      <c r="O48">
+        <v>-0.8491839920000002</v>
+      </c>
+      <c r="P48">
+        <v>-1.890119208</v>
+      </c>
+      <c r="Q48">
+        <v>-2.545119208</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1782914463547836</v>
+      </c>
+      <c r="T48">
+        <v>1.362870736189201</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.05982081977826848</v>
+      </c>
+      <c r="W48">
+        <v>0.2245147882369495</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1929703863815113</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2015541836205799</v>
+      </c>
+      <c r="C49">
+        <v>-0.1503739251510989</v>
+      </c>
+      <c r="D49">
+        <v>14.2086260748489</v>
+      </c>
+      <c r="E49">
+        <v>-3.876999999999999</v>
+      </c>
+      <c r="F49">
+        <v>14.523</v>
+      </c>
+      <c r="G49">
+        <v>0.164</v>
+      </c>
+      <c r="H49">
+        <v>12.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>-0.655</v>
+      </c>
+      <c r="L49">
+        <v>0.655</v>
+      </c>
+      <c r="M49">
+        <v>3.4680924</v>
+      </c>
+      <c r="N49">
+        <v>-2.8130924</v>
+      </c>
+      <c r="O49">
+        <v>-0.8720586440000002</v>
+      </c>
+      <c r="P49">
+        <v>-1.941033756</v>
+      </c>
+      <c r="Q49">
+        <v>-2.596033756</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1809233604369493</v>
+      </c>
+      <c r="T49">
+        <v>1.38858527838145</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.05854803637873086</v>
+      </c>
+      <c r="W49">
+        <v>0.2248187289127591</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1888646334797769</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2035541836205799</v>
+      </c>
+      <c r="C50">
+        <v>-0.6318566598848108</v>
+      </c>
+      <c r="D50">
+        <v>14.03614334011519</v>
+      </c>
+      <c r="E50">
+        <v>-3.568</v>
+      </c>
+      <c r="F50">
+        <v>14.832</v>
+      </c>
+      <c r="G50">
+        <v>0.164</v>
+      </c>
+      <c r="H50">
+        <v>12.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>-0.655</v>
+      </c>
+      <c r="L50">
+        <v>0.655</v>
+      </c>
+      <c r="M50">
+        <v>3.5418816</v>
+      </c>
+      <c r="N50">
+        <v>-2.8868816</v>
+      </c>
+      <c r="O50">
+        <v>-0.894933296</v>
+      </c>
+      <c r="P50">
+        <v>-1.991948304</v>
+      </c>
+      <c r="Q50">
+        <v>-2.646948303999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1836565019838137</v>
+      </c>
+      <c r="T50">
+        <v>1.415288841427247</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.05732828562084064</v>
+      </c>
+      <c r="W50">
+        <v>0.2251100053937433</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.184929953615615</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2055541836205799</v>
+      </c>
+      <c r="C51">
+        <v>-1.109201981547645</v>
+      </c>
+      <c r="D51">
+        <v>13.86779801845235</v>
+      </c>
+      <c r="E51">
+        <v>-3.259</v>
+      </c>
+      <c r="F51">
+        <v>15.141</v>
+      </c>
+      <c r="G51">
+        <v>0.164</v>
+      </c>
+      <c r="H51">
+        <v>12.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>-0.655</v>
+      </c>
+      <c r="L51">
+        <v>0.655</v>
+      </c>
+      <c r="M51">
+        <v>3.6156708</v>
+      </c>
+      <c r="N51">
+        <v>-2.9606708</v>
+      </c>
+      <c r="O51">
+        <v>-0.9178079480000001</v>
+      </c>
+      <c r="P51">
+        <v>-2.042862852</v>
+      </c>
+      <c r="Q51">
+        <v>-2.697862852</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1864968255521237</v>
+      </c>
+      <c r="T51">
+        <v>1.443039603023859</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.05615832060817043</v>
+      </c>
+      <c r="W51">
+        <v>0.2253893930387689</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1811558729295819</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2075541836205799</v>
+      </c>
+      <c r="C52">
+        <v>-1.582556994512922</v>
+      </c>
+      <c r="D52">
+        <v>13.70344300548708</v>
+      </c>
+      <c r="E52">
+        <v>-2.949999999999999</v>
+      </c>
+      <c r="F52">
+        <v>15.45</v>
+      </c>
+      <c r="G52">
+        <v>0.164</v>
+      </c>
+      <c r="H52">
+        <v>12.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>-0.655</v>
+      </c>
+      <c r="L52">
+        <v>0.655</v>
+      </c>
+      <c r="M52">
+        <v>3.68946</v>
+      </c>
+      <c r="N52">
+        <v>-3.03446</v>
+      </c>
+      <c r="O52">
+        <v>-0.9406826000000003</v>
+      </c>
+      <c r="P52">
+        <v>-2.0937774</v>
+      </c>
+      <c r="Q52">
+        <v>-2.7487774</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1894507620631662</v>
+      </c>
+      <c r="T52">
+        <v>1.471900395084337</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.05503515419600702</v>
+      </c>
+      <c r="W52">
+        <v>0.2256576051779935</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1775327554709902</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2095541836205799</v>
+      </c>
+      <c r="C53">
+        <v>-2.052061911170618</v>
+      </c>
+      <c r="D53">
+        <v>13.54293808882938</v>
+      </c>
+      <c r="E53">
+        <v>-2.640999999999998</v>
+      </c>
+      <c r="F53">
+        <v>15.759</v>
+      </c>
+      <c r="G53">
+        <v>0.164</v>
+      </c>
+      <c r="H53">
+        <v>12.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>-0.655</v>
+      </c>
+      <c r="L53">
+        <v>0.655</v>
+      </c>
+      <c r="M53">
+        <v>3.7632492</v>
+      </c>
+      <c r="N53">
+        <v>-3.1082492</v>
+      </c>
+      <c r="O53">
+        <v>-0.9635572520000003</v>
+      </c>
+      <c r="P53">
+        <v>-2.144691948</v>
+      </c>
+      <c r="Q53">
+        <v>-2.799691948</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1925252674113941</v>
+      </c>
+      <c r="T53">
+        <v>1.501939178657487</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.05395603352549708</v>
+      </c>
+      <c r="W53">
+        <v>0.2259152991941113</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1740517210499904</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2115541836205799</v>
+      </c>
+      <c r="C54">
+        <v>-2.517850450874807</v>
+      </c>
+      <c r="D54">
+        <v>13.38614954912519</v>
+      </c>
+      <c r="E54">
+        <v>-2.331999999999997</v>
+      </c>
+      <c r="F54">
+        <v>16.068</v>
+      </c>
+      <c r="G54">
+        <v>0.164</v>
+      </c>
+      <c r="H54">
+        <v>12.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>-0.655</v>
+      </c>
+      <c r="L54">
+        <v>0.655</v>
+      </c>
+      <c r="M54">
+        <v>3.8370384</v>
+      </c>
+      <c r="N54">
+        <v>-3.182038400000001</v>
+      </c>
+      <c r="O54">
+        <v>-0.9864319040000004</v>
+      </c>
+      <c r="P54">
+        <v>-2.195606496</v>
+      </c>
+      <c r="Q54">
+        <v>-2.850606496</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1957278771491315</v>
+      </c>
+      <c r="T54">
+        <v>1.533229578212851</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.05291841749616059</v>
+      </c>
+      <c r="W54">
+        <v>0.2261630819019169</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1707045725682599</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2135541836205799</v>
+      </c>
+      <c r="C55">
+        <v>-2.98005021149614</v>
+      </c>
+      <c r="D55">
+        <v>13.23294978850386</v>
+      </c>
+      <c r="E55">
+        <v>-2.023</v>
+      </c>
+      <c r="F55">
+        <v>16.377</v>
+      </c>
+      <c r="G55">
+        <v>0.164</v>
+      </c>
+      <c r="H55">
+        <v>12.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>-0.655</v>
+      </c>
+      <c r="L55">
+        <v>0.655</v>
+      </c>
+      <c r="M55">
+        <v>3.9108276</v>
+      </c>
+      <c r="N55">
+        <v>-3.2558276</v>
+      </c>
+      <c r="O55">
+        <v>-1.009306556</v>
+      </c>
+      <c r="P55">
+        <v>-2.246521044</v>
+      </c>
+      <c r="Q55">
+        <v>-2.901521044</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1990667681523045</v>
+      </c>
+      <c r="T55">
+        <v>1.565851484132273</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.05191995678868587</v>
+      </c>
+      <c r="W55">
+        <v>0.2264015143188618</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1674837315764059</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2155541836205799</v>
+      </c>
+      <c r="C56">
+        <v>-3.438783015749415</v>
+      </c>
+      <c r="D56">
+        <v>13.08321698425059</v>
+      </c>
+      <c r="E56">
+        <v>-1.713999999999999</v>
+      </c>
+      <c r="F56">
+        <v>16.686</v>
+      </c>
+      <c r="G56">
+        <v>0.164</v>
+      </c>
+      <c r="H56">
+        <v>12.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>-0.655</v>
+      </c>
+      <c r="L56">
+        <v>0.655</v>
+      </c>
+      <c r="M56">
+        <v>3.9846168</v>
+      </c>
+      <c r="N56">
+        <v>-3.3296168</v>
+      </c>
+      <c r="O56">
+        <v>-1.032181208</v>
+      </c>
+      <c r="P56">
+        <v>-2.297435592</v>
+      </c>
+      <c r="Q56">
+        <v>-2.952435592</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2025508283295285</v>
+      </c>
+      <c r="T56">
+        <v>1.599891733787323</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.0509584761074139</v>
+      </c>
+      <c r="W56">
+        <v>0.2266311159055496</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1643821809916578</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2175541836205799</v>
+      </c>
+      <c r="C57">
+        <v>-3.894165234271593</v>
+      </c>
+      <c r="D57">
+        <v>12.93683476572841</v>
+      </c>
+      <c r="E57">
+        <v>-1.404999999999998</v>
+      </c>
+      <c r="F57">
+        <v>16.995</v>
+      </c>
+      <c r="G57">
+        <v>0.164</v>
+      </c>
+      <c r="H57">
+        <v>12.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>-0.655</v>
+      </c>
+      <c r="L57">
+        <v>0.655</v>
+      </c>
+      <c r="M57">
+        <v>4.058406000000001</v>
+      </c>
+      <c r="N57">
+        <v>-3.403406</v>
+      </c>
+      <c r="O57">
+        <v>-1.05505586</v>
+      </c>
+      <c r="P57">
+        <v>-2.34835014</v>
+      </c>
+      <c r="Q57">
+        <v>-3.00335014</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2061897356257403</v>
+      </c>
+      <c r="T57">
+        <v>1.635444883427041</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.05003195836000637</v>
+      </c>
+      <c r="W57">
+        <v>0.2268523683436305</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1613934140645367</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2195541836205799</v>
+      </c>
+      <c r="C58">
+        <v>-4.346308087251243</v>
+      </c>
+      <c r="D58">
+        <v>12.79369191274876</v>
+      </c>
+      <c r="E58">
+        <v>-1.095999999999997</v>
+      </c>
+      <c r="F58">
+        <v>17.304</v>
+      </c>
+      <c r="G58">
+        <v>0.164</v>
+      </c>
+      <c r="H58">
+        <v>12.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>-0.655</v>
+      </c>
+      <c r="L58">
+        <v>0.655</v>
+      </c>
+      <c r="M58">
+        <v>4.132195200000001</v>
+      </c>
+      <c r="N58">
+        <v>-3.477195200000001</v>
+      </c>
+      <c r="O58">
+        <v>-1.077930512</v>
+      </c>
+      <c r="P58">
+        <v>-2.399264688</v>
+      </c>
+      <c r="Q58">
+        <v>-3.054264688</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2099940477990525</v>
+      </c>
+      <c r="T58">
+        <v>1.67261408532311</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.04913853053214911</v>
+      </c>
+      <c r="W58">
+        <v>0.2270657189089228</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1585113888133842</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2215541836205799</v>
+      </c>
+      <c r="C59">
+        <v>-4.795317926252356</v>
+      </c>
+      <c r="D59">
+        <v>12.65368207374764</v>
+      </c>
+      <c r="E59">
+        <v>-0.786999999999999</v>
+      </c>
+      <c r="F59">
+        <v>17.613</v>
+      </c>
+      <c r="G59">
+        <v>0.164</v>
+      </c>
+      <c r="H59">
+        <v>12.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>-0.655</v>
+      </c>
+      <c r="L59">
+        <v>0.655</v>
+      </c>
+      <c r="M59">
+        <v>4.2059844</v>
+      </c>
+      <c r="N59">
+        <v>-3.5509844</v>
+      </c>
+      <c r="O59">
+        <v>-1.100805164</v>
+      </c>
+      <c r="P59">
+        <v>-2.450179236</v>
+      </c>
+      <c r="Q59">
+        <v>-3.105179236</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.213975304724612</v>
+      </c>
+      <c r="T59">
+        <v>1.711512087307369</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.04827645104912896</v>
+      </c>
+      <c r="W59">
+        <v>0.227271583489468</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1557304872552547</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2235541836205799</v>
+      </c>
+      <c r="C60">
+        <v>-5.241296497733407</v>
+      </c>
+      <c r="D60">
+        <v>12.51670350226659</v>
+      </c>
+      <c r="E60">
+        <v>-0.4780000000000015</v>
+      </c>
+      <c r="F60">
+        <v>17.922</v>
+      </c>
+      <c r="G60">
+        <v>0.164</v>
+      </c>
+      <c r="H60">
+        <v>12.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>-0.655</v>
+      </c>
+      <c r="L60">
+        <v>0.655</v>
+      </c>
+      <c r="M60">
+        <v>4.2797736</v>
+      </c>
+      <c r="N60">
+        <v>-3.624773599999999</v>
+      </c>
+      <c r="O60">
+        <v>-1.123679816</v>
+      </c>
+      <c r="P60">
+        <v>-2.501093783999999</v>
+      </c>
+      <c r="Q60">
+        <v>-3.156093783999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2181461453132931</v>
+      </c>
+      <c r="T60">
+        <v>1.752262375100401</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.04744409844483364</v>
+      </c>
+      <c r="W60">
+        <v>0.2274703492913737</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1530454788543021</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2255541836205799</v>
+      </c>
+      <c r="C61">
+        <v>-5.684341189633818</v>
+      </c>
+      <c r="D61">
+        <v>12.38265881036618</v>
+      </c>
+      <c r="E61">
+        <v>-0.1690000000000005</v>
+      </c>
+      <c r="F61">
+        <v>18.231</v>
+      </c>
+      <c r="G61">
+        <v>0.164</v>
+      </c>
+      <c r="H61">
+        <v>12.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>-0.655</v>
+      </c>
+      <c r="L61">
+        <v>0.655</v>
+      </c>
+      <c r="M61">
+        <v>4.3535628</v>
+      </c>
+      <c r="N61">
+        <v>-3.698562799999999</v>
+      </c>
+      <c r="O61">
+        <v>-1.146554468</v>
+      </c>
+      <c r="P61">
+        <v>-2.552008332</v>
+      </c>
+      <c r="Q61">
+        <v>-3.207008332</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2225204415404466</v>
+      </c>
+      <c r="T61">
+        <v>1.795000481810167</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.04663996118305679</v>
+      </c>
+      <c r="W61">
+        <v>0.227662377269486</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.15045148768728</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2275541836205799</v>
+      </c>
+      <c r="C62">
+        <v>-6.124545262283746</v>
+      </c>
+      <c r="D62">
+        <v>12.25145473771625</v>
+      </c>
+      <c r="E62">
+        <v>0.1400000000000006</v>
+      </c>
+      <c r="F62">
+        <v>18.54</v>
+      </c>
+      <c r="G62">
+        <v>0.164</v>
+      </c>
+      <c r="H62">
+        <v>12.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>-0.655</v>
+      </c>
+      <c r="L62">
+        <v>0.655</v>
+      </c>
+      <c r="M62">
+        <v>4.427352</v>
+      </c>
+      <c r="N62">
+        <v>-3.772352</v>
+      </c>
+      <c r="O62">
+        <v>-1.16942912</v>
+      </c>
+      <c r="P62">
+        <v>-2.602922879999999</v>
+      </c>
+      <c r="Q62">
+        <v>-3.25792288</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2271134525789578</v>
+      </c>
+      <c r="T62">
+        <v>1.839875493855421</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.04586262849667251</v>
+      </c>
+      <c r="W62">
+        <v>0.2278480043149946</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.147943962892492</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2295541836205799</v>
+      </c>
+      <c r="C63">
+        <v>-6.56199806478778</v>
+      </c>
+      <c r="D63">
+        <v>12.12300193521222</v>
+      </c>
+      <c r="E63">
+        <v>0.4490000000000016</v>
+      </c>
+      <c r="F63">
+        <v>18.849</v>
+      </c>
+      <c r="G63">
+        <v>0.164</v>
+      </c>
+      <c r="H63">
+        <v>12.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>-0.655</v>
+      </c>
+      <c r="L63">
+        <v>0.655</v>
+      </c>
+      <c r="M63">
+        <v>4.5011412</v>
+      </c>
+      <c r="N63">
+        <v>-3.8461412</v>
+      </c>
+      <c r="O63">
+        <v>-1.192303772</v>
+      </c>
+      <c r="P63">
+        <v>-2.653837428</v>
+      </c>
+      <c r="Q63">
+        <v>-3.308837427999999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2319420026450849</v>
+      </c>
+      <c r="T63">
+        <v>1.887051788569663</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.04511078212787459</v>
+      </c>
+      <c r="W63">
+        <v>0.2280275452278636</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1455186520254019</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2315541836205799</v>
+      </c>
+      <c r="C64">
+        <v>-6.996785237937546</v>
+      </c>
+      <c r="D64">
+        <v>11.99721476206245</v>
+      </c>
+      <c r="E64">
+        <v>0.7579999999999991</v>
+      </c>
+      <c r="F64">
+        <v>19.158</v>
+      </c>
+      <c r="G64">
+        <v>0.164</v>
+      </c>
+      <c r="H64">
+        <v>12.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>-0.655</v>
+      </c>
+      <c r="L64">
+        <v>0.655</v>
+      </c>
+      <c r="M64">
+        <v>4.5749304</v>
+      </c>
+      <c r="N64">
+        <v>-3.919930399999999</v>
+      </c>
+      <c r="O64">
+        <v>-1.215178424</v>
+      </c>
+      <c r="P64">
+        <v>-2.704751975999999</v>
+      </c>
+      <c r="Q64">
+        <v>-3.359751975999999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2370246869252187</v>
+      </c>
+      <c r="T64">
+        <v>1.936711046163601</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.0443831888677476</v>
+      </c>
+      <c r="W64">
+        <v>0.2282012944983819</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1431715769927342</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2335541836205799</v>
+      </c>
+      <c r="C65">
+        <v>-7.428988904621653</v>
+      </c>
+      <c r="D65">
+        <v>11.87401109537835</v>
+      </c>
+      <c r="E65">
+        <v>1.067</v>
+      </c>
+      <c r="F65">
+        <v>19.467</v>
+      </c>
+      <c r="G65">
+        <v>0.164</v>
+      </c>
+      <c r="H65">
+        <v>12.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>-0.655</v>
+      </c>
+      <c r="L65">
+        <v>0.655</v>
+      </c>
+      <c r="M65">
+        <v>4.6487196</v>
+      </c>
+      <c r="N65">
+        <v>-3.993719599999999</v>
+      </c>
+      <c r="O65">
+        <v>-1.238053076</v>
+      </c>
+      <c r="P65">
+        <v>-2.755666524</v>
+      </c>
+      <c r="Q65">
+        <v>-3.410666524</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2423821108961706</v>
+      </c>
+      <c r="T65">
+        <v>1.989054587951807</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.04367869380635478</v>
+      </c>
+      <c r="W65">
+        <v>0.2283695279190425</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1408990122785638</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2355541836205799</v>
+      </c>
+      <c r="C66">
+        <v>-7.858687848622523</v>
+      </c>
+      <c r="D66">
+        <v>11.75331215137748</v>
+      </c>
+      <c r="E66">
+        <v>1.376000000000001</v>
+      </c>
+      <c r="F66">
+        <v>19.776</v>
+      </c>
+      <c r="G66">
+        <v>0.164</v>
+      </c>
+      <c r="H66">
+        <v>12.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>-0.655</v>
+      </c>
+      <c r="L66">
+        <v>0.655</v>
+      </c>
+      <c r="M66">
+        <v>4.7225088</v>
+      </c>
+      <c r="N66">
+        <v>-4.0675088</v>
+      </c>
+      <c r="O66">
+        <v>-1.260927728</v>
+      </c>
+      <c r="P66">
+        <v>-2.806581071999999</v>
+      </c>
+      <c r="Q66">
+        <v>-3.461581072</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2480371695321753</v>
+      </c>
+      <c r="T66">
+        <v>2.044306104283801</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.04299621421563048</v>
+      </c>
+      <c r="W66">
+        <v>0.2285325040453074</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1386974652117112</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2375541836205799</v>
+      </c>
+      <c r="C67">
+        <v>-8.285957682618212</v>
+      </c>
+      <c r="D67">
+        <v>11.63504231738179</v>
+      </c>
+      <c r="E67">
+        <v>1.685000000000002</v>
+      </c>
+      <c r="F67">
+        <v>20.085</v>
+      </c>
+      <c r="G67">
+        <v>0.164</v>
+      </c>
+      <c r="H67">
+        <v>12.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>-0.655</v>
+      </c>
+      <c r="L67">
+        <v>0.655</v>
+      </c>
+      <c r="M67">
+        <v>4.796298</v>
+      </c>
+      <c r="N67">
+        <v>-4.141298</v>
+      </c>
+      <c r="O67">
+        <v>-1.28380238</v>
+      </c>
+      <c r="P67">
+        <v>-2.85749562</v>
+      </c>
+      <c r="Q67">
+        <v>-3.51249562</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2540153743759518</v>
+      </c>
+      <c r="T67">
+        <v>2.102714850120481</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.04233473399692848</v>
+      </c>
+      <c r="W67">
+        <v>0.2286904655215335</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.136563658054608</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2395541836205799</v>
+      </c>
+      <c r="C68">
+        <v>-8.710871006141986</v>
+      </c>
+      <c r="D68">
+        <v>11.51912899385801</v>
+      </c>
+      <c r="E68">
+        <v>1.994</v>
+      </c>
+      <c r="F68">
+        <v>20.394</v>
+      </c>
+      <c r="G68">
+        <v>0.164</v>
+      </c>
+      <c r="H68">
+        <v>12.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>-0.655</v>
+      </c>
+      <c r="L68">
+        <v>0.655</v>
+      </c>
+      <c r="M68">
+        <v>4.8700872</v>
+      </c>
+      <c r="N68">
+        <v>-4.215087199999999</v>
+      </c>
+      <c r="O68">
+        <v>-1.306677032</v>
+      </c>
+      <c r="P68">
+        <v>-2.908410167999999</v>
+      </c>
+      <c r="Q68">
+        <v>-3.563410167999999</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2603452383281857</v>
+      </c>
+      <c r="T68">
+        <v>2.16455940453579</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.04169329863333865</v>
+      </c>
+      <c r="W68">
+        <v>0.2288436402863587</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1344945117204472</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2415541836205799</v>
+      </c>
+      <c r="C69">
+        <v>-9.133497554193042</v>
+      </c>
+      <c r="D69">
+        <v>11.40550244580696</v>
+      </c>
+      <c r="E69">
+        <v>2.303000000000001</v>
+      </c>
+      <c r="F69">
+        <v>20.703</v>
+      </c>
+      <c r="G69">
+        <v>0.164</v>
+      </c>
+      <c r="H69">
+        <v>12.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>-0.655</v>
+      </c>
+      <c r="L69">
+        <v>0.655</v>
+      </c>
+      <c r="M69">
+        <v>4.9438764</v>
+      </c>
+      <c r="N69">
+        <v>-4.288876399999999</v>
+      </c>
+      <c r="O69">
+        <v>-1.329551684</v>
+      </c>
+      <c r="P69">
+        <v>-2.959324715999999</v>
+      </c>
+      <c r="Q69">
+        <v>-3.614324716</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2670587303987367</v>
+      </c>
+      <c r="T69">
+        <v>2.230152113764147</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.04107101059403509</v>
+      </c>
+      <c r="W69">
+        <v>0.2289922426701445</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1324871309485003</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2435541836205799</v>
+      </c>
+      <c r="C70">
+        <v>-9.553904337137629</v>
+      </c>
+      <c r="D70">
+        <v>11.29409566286237</v>
+      </c>
+      <c r="E70">
+        <v>2.612000000000002</v>
+      </c>
+      <c r="F70">
+        <v>21.012</v>
+      </c>
+      <c r="G70">
+        <v>0.164</v>
+      </c>
+      <c r="H70">
+        <v>12.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>-0.655</v>
+      </c>
+      <c r="L70">
+        <v>0.655</v>
+      </c>
+      <c r="M70">
+        <v>5.0176656</v>
+      </c>
+      <c r="N70">
+        <v>-4.3626656</v>
+      </c>
+      <c r="O70">
+        <v>-1.352426336</v>
+      </c>
+      <c r="P70">
+        <v>-3.010239264</v>
+      </c>
+      <c r="Q70">
+        <v>-3.665239263999999</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2741918157236972</v>
+      </c>
+      <c r="T70">
+        <v>2.299844367319277</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.0404670251441228</v>
+      </c>
+      <c r="W70">
+        <v>0.2291364743955835</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.130538790787493</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2455541836205799</v>
+      </c>
+      <c r="C71">
+        <v>-9.972155772490332</v>
+      </c>
+      <c r="D71">
+        <v>11.18484422750967</v>
+      </c>
+      <c r="E71">
+        <v>2.921000000000003</v>
+      </c>
+      <c r="F71">
+        <v>21.321</v>
+      </c>
+      <c r="G71">
+        <v>0.164</v>
+      </c>
+      <c r="H71">
+        <v>12.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>-0.655</v>
+      </c>
+      <c r="L71">
+        <v>0.655</v>
+      </c>
+      <c r="M71">
+        <v>5.091454800000001</v>
+      </c>
+      <c r="N71">
+        <v>-4.436454800000001</v>
+      </c>
+      <c r="O71">
+        <v>-1.375300988</v>
+      </c>
+      <c r="P71">
+        <v>-3.061153812000001</v>
+      </c>
+      <c r="Q71">
+        <v>-3.716153812000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2817851001018811</v>
+      </c>
+      <c r="T71">
+        <v>2.374032895297318</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.03988054651884565</v>
+      </c>
+      <c r="W71">
+        <v>0.2292765254912997</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1286469242543409</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2475541836205799</v>
+      </c>
+      <c r="C72">
+        <v>-10.38831380912005</v>
+      </c>
+      <c r="D72">
+        <v>11.07768619087996</v>
+      </c>
+      <c r="E72">
+        <v>3.230000000000004</v>
+      </c>
+      <c r="F72">
+        <v>21.63</v>
+      </c>
+      <c r="G72">
+        <v>0.164</v>
+      </c>
+      <c r="H72">
+        <v>12.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>-0.655</v>
+      </c>
+      <c r="L72">
+        <v>0.655</v>
+      </c>
+      <c r="M72">
+        <v>5.165244000000001</v>
+      </c>
+      <c r="N72">
+        <v>-4.510244000000001</v>
+      </c>
+      <c r="O72">
+        <v>-1.39817564</v>
+      </c>
+      <c r="P72">
+        <v>-3.11206836</v>
+      </c>
+      <c r="Q72">
+        <v>-3.767068360000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2898846034386104</v>
+      </c>
+      <c r="T72">
+        <v>2.453167325140562</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.03931082442571929</v>
+      </c>
+      <c r="W72">
+        <v>0.2294125751271383</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1268091110507074</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2495541836205799</v>
+      </c>
+      <c r="C73">
+        <v>-10.80243804438384</v>
+      </c>
+      <c r="D73">
+        <v>10.97256195561616</v>
+      </c>
+      <c r="E73">
+        <v>3.538999999999998</v>
+      </c>
+      <c r="F73">
+        <v>21.939</v>
+      </c>
+      <c r="G73">
+        <v>0.164</v>
+      </c>
+      <c r="H73">
+        <v>12.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>-0.655</v>
+      </c>
+      <c r="L73">
+        <v>0.655</v>
+      </c>
+      <c r="M73">
+        <v>5.2390332</v>
+      </c>
+      <c r="N73">
+        <v>-4.584033199999999</v>
+      </c>
+      <c r="O73">
+        <v>-1.421050292</v>
+      </c>
+      <c r="P73">
+        <v>-3.162982907999999</v>
+      </c>
+      <c r="Q73">
+        <v>-3.817982907999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2985426932123555</v>
+      </c>
+      <c r="T73">
+        <v>2.537759301869546</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03875715084225846</v>
+      </c>
+      <c r="W73">
+        <v>0.2295447923788687</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1250230672330919</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2515541836205799</v>
+      </c>
+      <c r="C74">
+        <v>-11.21458583465418</v>
+      </c>
+      <c r="D74">
+        <v>10.86941416534582</v>
+      </c>
+      <c r="E74">
+        <v>3.847999999999999</v>
+      </c>
+      <c r="F74">
+        <v>22.248</v>
+      </c>
+      <c r="G74">
+        <v>0.164</v>
+      </c>
+      <c r="H74">
+        <v>12.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>-0.655</v>
+      </c>
+      <c r="L74">
+        <v>0.655</v>
+      </c>
+      <c r="M74">
+        <v>5.3128224</v>
+      </c>
+      <c r="N74">
+        <v>-4.6578224</v>
+      </c>
+      <c r="O74">
+        <v>-1.443924944</v>
+      </c>
+      <c r="P74">
+        <v>-3.213897456</v>
+      </c>
+      <c r="Q74">
+        <v>-3.868897456</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3078192179699397</v>
+      </c>
+      <c r="T74">
+        <v>2.628393562650602</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.03821885708056043</v>
+      </c>
+      <c r="W74">
+        <v>0.2296733369291622</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1232866357437433</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2535541836205799</v>
+      </c>
+      <c r="C75">
+        <v>-11.62481239967001</v>
+      </c>
+      <c r="D75">
+        <v>10.76818760032999</v>
+      </c>
+      <c r="E75">
+        <v>4.157</v>
+      </c>
+      <c r="F75">
+        <v>22.557</v>
+      </c>
+      <c r="G75">
+        <v>0.164</v>
+      </c>
+      <c r="H75">
+        <v>12.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>-0.655</v>
+      </c>
+      <c r="L75">
+        <v>0.655</v>
+      </c>
+      <c r="M75">
+        <v>5.3866116</v>
+      </c>
+      <c r="N75">
+        <v>-4.7316116</v>
+      </c>
+      <c r="O75">
+        <v>-1.466799596</v>
+      </c>
+      <c r="P75">
+        <v>-3.264812003999999</v>
+      </c>
+      <c r="Q75">
+        <v>-3.919812004</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.317782892709567</v>
+      </c>
+      <c r="T75">
+        <v>2.725741472378401</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.03769531109315549</v>
+      </c>
+      <c r="W75">
+        <v>0.2297983597109545</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1215977777198565</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2555541836205799</v>
+      </c>
+      <c r="C76">
+        <v>-12.03317092111087</v>
+      </c>
+      <c r="D76">
+        <v>10.66882907888913</v>
+      </c>
+      <c r="E76">
+        <v>4.466000000000001</v>
+      </c>
+      <c r="F76">
+        <v>22.866</v>
+      </c>
+      <c r="G76">
+        <v>0.164</v>
+      </c>
+      <c r="H76">
+        <v>12.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>-0.655</v>
+      </c>
+      <c r="L76">
+        <v>0.655</v>
+      </c>
+      <c r="M76">
+        <v>5.4604008</v>
+      </c>
+      <c r="N76">
+        <v>-4.8054008</v>
+      </c>
+      <c r="O76">
+        <v>-1.489674248</v>
+      </c>
+      <c r="P76">
+        <v>-3.315726552</v>
+      </c>
+      <c r="Q76">
+        <v>-3.970726552</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3285130039676273</v>
+      </c>
+      <c r="T76">
+        <v>2.830577682854494</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.03718591499730203</v>
+      </c>
+      <c r="W76">
+        <v>0.2299200034986443</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1199545645074259</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2575541836205799</v>
+      </c>
+      <c r="C77">
+        <v>-12.43971263576345</v>
+      </c>
+      <c r="D77">
+        <v>10.57128736423654</v>
+      </c>
+      <c r="E77">
+        <v>4.774999999999999</v>
+      </c>
+      <c r="F77">
+        <v>23.175</v>
+      </c>
+      <c r="G77">
+        <v>0.164</v>
+      </c>
+      <c r="H77">
+        <v>12.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>-0.655</v>
+      </c>
+      <c r="L77">
+        <v>0.655</v>
+      </c>
+      <c r="M77">
+        <v>5.53419</v>
+      </c>
+      <c r="N77">
+        <v>-4.879189999999999</v>
+      </c>
+      <c r="O77">
+        <v>-1.5125489</v>
+      </c>
+      <c r="P77">
+        <v>-3.366641099999999</v>
+      </c>
+      <c r="Q77">
+        <v>-4.021641099999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3401015241263324</v>
+      </c>
+      <c r="T77">
+        <v>2.943800790168674</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.03669010279733801</v>
+      </c>
+      <c r="W77">
+        <v>0.2300384034519957</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1183551703139936</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2595541836205799</v>
+      </c>
+      <c r="C78">
+        <v>-12.84448692362389</v>
+      </c>
+      <c r="D78">
+        <v>10.47551307637611</v>
+      </c>
+      <c r="E78">
+        <v>5.084</v>
+      </c>
+      <c r="F78">
+        <v>23.484</v>
+      </c>
+      <c r="G78">
+        <v>0.164</v>
+      </c>
+      <c r="H78">
+        <v>12.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>-0.655</v>
+      </c>
+      <c r="L78">
+        <v>0.655</v>
+      </c>
+      <c r="M78">
+        <v>5.6079792</v>
+      </c>
+      <c r="N78">
+        <v>-4.9529792</v>
+      </c>
+      <c r="O78">
+        <v>-1.535423552</v>
+      </c>
+      <c r="P78">
+        <v>-3.417555648</v>
+      </c>
+      <c r="Q78">
+        <v>-4.072555648</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3526557542982631</v>
+      </c>
+      <c r="T78">
+        <v>3.066459156425703</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03620733828684672</v>
+      </c>
+      <c r="W78">
+        <v>0.230153687617101</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1167978654414411</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2615541836205799</v>
+      </c>
+      <c r="C79">
+        <v>-13.24754139125372</v>
+      </c>
+      <c r="D79">
+        <v>10.38145860874628</v>
+      </c>
+      <c r="E79">
+        <v>5.393000000000001</v>
+      </c>
+      <c r="F79">
+        <v>23.793</v>
+      </c>
+      <c r="G79">
+        <v>0.164</v>
+      </c>
+      <c r="H79">
+        <v>12.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>-0.655</v>
+      </c>
+      <c r="L79">
+        <v>0.655</v>
+      </c>
+      <c r="M79">
+        <v>5.6817684</v>
+      </c>
+      <c r="N79">
+        <v>-5.0267684</v>
+      </c>
+      <c r="O79">
+        <v>-1.558298204</v>
+      </c>
+      <c r="P79">
+        <v>-3.468470196</v>
+      </c>
+      <c r="Q79">
+        <v>-4.123470196</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.366301656659057</v>
+      </c>
+      <c r="T79">
+        <v>3.199783467574645</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03573711311429027</v>
+      </c>
+      <c r="W79">
+        <v>0.2302659773883075</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1152810100460977</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2635541836205799</v>
+      </c>
+      <c r="C80">
+        <v>-13.64892195068547</v>
+      </c>
+      <c r="D80">
+        <v>10.28907804931453</v>
+      </c>
+      <c r="E80">
+        <v>5.702000000000002</v>
+      </c>
+      <c r="F80">
+        <v>24.102</v>
+      </c>
+      <c r="G80">
+        <v>0.164</v>
+      </c>
+      <c r="H80">
+        <v>12.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>-0.655</v>
+      </c>
+      <c r="L80">
+        <v>0.655</v>
+      </c>
+      <c r="M80">
+        <v>5.7555576</v>
+      </c>
+      <c r="N80">
+        <v>-5.1005576</v>
+      </c>
+      <c r="O80">
+        <v>-1.581172856</v>
+      </c>
+      <c r="P80">
+        <v>-3.519384744</v>
+      </c>
+      <c r="Q80">
+        <v>-4.174384744</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3811880955981051</v>
+      </c>
+      <c r="T80">
+        <v>3.34522817064622</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.03527894499744039</v>
+      </c>
+      <c r="W80">
+        <v>0.2303753879346112</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.11380304837884</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2655541836205799</v>
+      </c>
+      <c r="C81">
+        <v>-14.04867289415234</v>
+      </c>
+      <c r="D81">
+        <v>10.19832710584766</v>
+      </c>
+      <c r="E81">
+        <v>6.011000000000003</v>
+      </c>
+      <c r="F81">
+        <v>24.411</v>
+      </c>
+      <c r="G81">
+        <v>0.164</v>
+      </c>
+      <c r="H81">
+        <v>12.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>-0.655</v>
+      </c>
+      <c r="L81">
+        <v>0.655</v>
+      </c>
+      <c r="M81">
+        <v>5.829346800000001</v>
+      </c>
+      <c r="N81">
+        <v>-5.1743468</v>
+      </c>
+      <c r="O81">
+        <v>-1.604047508</v>
+      </c>
+      <c r="P81">
+        <v>-3.570299292</v>
+      </c>
+      <c r="Q81">
+        <v>-4.225299292</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3974922906265863</v>
+      </c>
+      <c r="T81">
+        <v>3.504524750200803</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.03483237607342216</v>
+      </c>
+      <c r="W81">
+        <v>0.2304820285936668</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1123625034626522</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2675541836205799</v>
+      </c>
+      <c r="C82">
+        <v>-14.44683696489793</v>
+      </c>
+      <c r="D82">
+        <v>10.10916303510207</v>
+      </c>
+      <c r="E82">
+        <v>6.32</v>
+      </c>
+      <c r="F82">
+        <v>24.72</v>
+      </c>
+      <c r="G82">
+        <v>0.164</v>
+      </c>
+      <c r="H82">
+        <v>12.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>-0.655</v>
+      </c>
+      <c r="L82">
+        <v>0.655</v>
+      </c>
+      <c r="M82">
+        <v>5.903136</v>
+      </c>
+      <c r="N82">
+        <v>-5.248136</v>
+      </c>
+      <c r="O82">
+        <v>-1.62692216</v>
+      </c>
+      <c r="P82">
+        <v>-3.621213839999999</v>
+      </c>
+      <c r="Q82">
+        <v>-4.27621384</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4154269051579156</v>
+      </c>
+      <c r="T82">
+        <v>3.679750987710842</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.03439697137250439</v>
+      </c>
+      <c r="W82">
+        <v>0.230586003236246</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.110957972169369</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2695541836205799</v>
+      </c>
+      <c r="C83">
+        <v>-14.84345542430341</v>
+      </c>
+      <c r="D83">
+        <v>10.02154457569659</v>
+      </c>
+      <c r="E83">
+        <v>6.629000000000001</v>
+      </c>
+      <c r="F83">
+        <v>25.029</v>
+      </c>
+      <c r="G83">
+        <v>0.164</v>
+      </c>
+      <c r="H83">
+        <v>12.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>-0.655</v>
+      </c>
+      <c r="L83">
+        <v>0.655</v>
+      </c>
+      <c r="M83">
+        <v>5.9769252</v>
+      </c>
+      <c r="N83">
+        <v>-5.3219252</v>
+      </c>
+      <c r="O83">
+        <v>-1.649796812</v>
+      </c>
+      <c r="P83">
+        <v>-3.672128388</v>
+      </c>
+      <c r="Q83">
+        <v>-4.327128388</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4352493738504375</v>
+      </c>
+      <c r="T83">
+        <v>3.873422092327203</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.0339723174049426</v>
+      </c>
+      <c r="W83">
+        <v>0.2306874106036997</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1095881206611052</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2715541836205799</v>
+      </c>
+      <c r="C84">
+        <v>-15.23856811555396</v>
+      </c>
+      <c r="D84">
+        <v>9.935431884446039</v>
+      </c>
+      <c r="E84">
+        <v>6.938000000000002</v>
+      </c>
+      <c r="F84">
+        <v>25.338</v>
+      </c>
+      <c r="G84">
+        <v>0.164</v>
+      </c>
+      <c r="H84">
+        <v>12.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>-0.655</v>
+      </c>
+      <c r="L84">
+        <v>0.655</v>
+      </c>
+      <c r="M84">
+        <v>6.0507144</v>
+      </c>
+      <c r="N84">
+        <v>-5.3957144</v>
+      </c>
+      <c r="O84">
+        <v>-1.672671464</v>
+      </c>
+      <c r="P84">
+        <v>-3.723042936</v>
+      </c>
+      <c r="Q84">
+        <v>-4.378042936</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4572743390643507</v>
+      </c>
+      <c r="T84">
+        <v>4.088612208567604</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.03355802085122379</v>
+      </c>
+      <c r="W84">
+        <v>0.2307863446207278</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.108251680165238</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2735541836205799</v>
+      </c>
+      <c r="C85">
+        <v>-15.63221352405075</v>
+      </c>
+      <c r="D85">
+        <v>9.850786475949254</v>
+      </c>
+      <c r="E85">
+        <v>7.247000000000003</v>
+      </c>
+      <c r="F85">
+        <v>25.647</v>
+      </c>
+      <c r="G85">
+        <v>0.164</v>
+      </c>
+      <c r="H85">
+        <v>12.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>-0.655</v>
+      </c>
+      <c r="L85">
+        <v>0.655</v>
+      </c>
+      <c r="M85">
+        <v>6.124503600000001</v>
+      </c>
+      <c r="N85">
+        <v>-5.4695036</v>
+      </c>
+      <c r="O85">
+        <v>-1.695546116</v>
+      </c>
+      <c r="P85">
+        <v>-3.773957484</v>
+      </c>
+      <c r="Q85">
+        <v>-4.428957484</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4818904766563714</v>
+      </c>
+      <c r="T85">
+        <v>4.329118809071581</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.03315370734699218</v>
+      </c>
+      <c r="W85">
+        <v>0.2308828946855383</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1069474430548135</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2755541836205799</v>
+      </c>
+      <c r="C86">
+        <v>-16.02442883476083</v>
+      </c>
+      <c r="D86">
+        <v>9.767571165239175</v>
+      </c>
+      <c r="E86">
+        <v>7.556000000000001</v>
+      </c>
+      <c r="F86">
+        <v>25.956</v>
+      </c>
+      <c r="G86">
+        <v>0.164</v>
+      </c>
+      <c r="H86">
+        <v>12.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>-0.655</v>
+      </c>
+      <c r="L86">
+        <v>0.655</v>
+      </c>
+      <c r="M86">
+        <v>6.1982928</v>
+      </c>
+      <c r="N86">
+        <v>-5.5432928</v>
+      </c>
+      <c r="O86">
+        <v>-1.718420768</v>
+      </c>
+      <c r="P86">
+        <v>-3.824872032</v>
+      </c>
+      <c r="Q86">
+        <v>-4.479872031999999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5095836314473944</v>
+      </c>
+      <c r="T86">
+        <v>4.599688734638552</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.03275902035476608</v>
+      </c>
+      <c r="W86">
+        <v>0.2309771459392819</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1056742592089228</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2775541836205799</v>
+      </c>
+      <c r="C87">
+        <v>-16.41524998668469</v>
+      </c>
+      <c r="D87">
+        <v>9.685750013315307</v>
+      </c>
+      <c r="E87">
+        <v>7.864999999999998</v>
+      </c>
+      <c r="F87">
+        <v>26.265</v>
+      </c>
+      <c r="G87">
+        <v>0.164</v>
+      </c>
+      <c r="H87">
+        <v>12.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>-0.655</v>
+      </c>
+      <c r="L87">
+        <v>0.655</v>
+      </c>
+      <c r="M87">
+        <v>6.272081999999999</v>
+      </c>
+      <c r="N87">
+        <v>-5.617081999999999</v>
+      </c>
+      <c r="O87">
+        <v>-1.74129542</v>
+      </c>
+      <c r="P87">
+        <v>-3.875786579999999</v>
+      </c>
+      <c r="Q87">
+        <v>-4.530786579999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5409692068772207</v>
+      </c>
+      <c r="T87">
+        <v>4.906334650281122</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.03237362011529825</v>
+      </c>
+      <c r="W87">
+        <v>0.2310691795164668</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1044310326299943</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2795541836205799</v>
+      </c>
+      <c r="C88">
+        <v>-16.80471172460888</v>
+      </c>
+      <c r="D88">
+        <v>9.60528827539112</v>
+      </c>
+      <c r="E88">
+        <v>8.173999999999999</v>
+      </c>
+      <c r="F88">
+        <v>26.574</v>
+      </c>
+      <c r="G88">
+        <v>0.164</v>
+      </c>
+      <c r="H88">
+        <v>12.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>-0.655</v>
+      </c>
+      <c r="L88">
+        <v>0.655</v>
+      </c>
+      <c r="M88">
+        <v>6.345871199999999</v>
+      </c>
+      <c r="N88">
+        <v>-5.690871199999999</v>
+      </c>
+      <c r="O88">
+        <v>-1.764170072</v>
+      </c>
+      <c r="P88">
+        <v>-3.926701127999999</v>
+      </c>
+      <c r="Q88">
+        <v>-4.581701128</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5768384359398795</v>
+      </c>
+      <c r="T88">
+        <v>5.256787125301203</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.03199718267209711</v>
+      </c>
+      <c r="W88">
+        <v>0.2311590727779032</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1032167182970875</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2815541836205799</v>
+      </c>
+      <c r="C89">
+        <v>-17.19284764830034</v>
+      </c>
+      <c r="D89">
+        <v>9.526152351699656</v>
+      </c>
+      <c r="E89">
+        <v>8.483000000000001</v>
+      </c>
+      <c r="F89">
+        <v>26.883</v>
+      </c>
+      <c r="G89">
+        <v>0.164</v>
+      </c>
+      <c r="H89">
+        <v>12.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>-0.655</v>
+      </c>
+      <c r="L89">
+        <v>0.655</v>
+      </c>
+      <c r="M89">
+        <v>6.4196604</v>
+      </c>
+      <c r="N89">
+        <v>-5.764660399999999</v>
+      </c>
+      <c r="O89">
+        <v>-1.787044724</v>
+      </c>
+      <c r="P89">
+        <v>-3.977615675999999</v>
+      </c>
+      <c r="Q89">
+        <v>-4.632615675999999</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6182260079352546</v>
+      </c>
+      <c r="T89">
+        <v>5.661155365708987</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.03162939896322242</v>
+      </c>
+      <c r="W89">
+        <v>0.2312468995275825</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1020303192362014</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2835541836205799</v>
+      </c>
+      <c r="C90">
+        <v>-17.5796902592889</v>
+      </c>
+      <c r="D90">
+        <v>9.448309740711096</v>
+      </c>
+      <c r="E90">
+        <v>8.792000000000002</v>
+      </c>
+      <c r="F90">
+        <v>27.192</v>
+      </c>
+      <c r="G90">
+        <v>0.164</v>
+      </c>
+      <c r="H90">
+        <v>12.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>-0.655</v>
+      </c>
+      <c r="L90">
+        <v>0.655</v>
+      </c>
+      <c r="M90">
+        <v>6.4934496</v>
+      </c>
+      <c r="N90">
+        <v>-5.8384496</v>
+      </c>
+      <c r="O90">
+        <v>-1.809919376</v>
+      </c>
+      <c r="P90">
+        <v>-4.028530223999999</v>
+      </c>
+      <c r="Q90">
+        <v>-4.683530223999999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6665115085965261</v>
+      </c>
+      <c r="T90">
+        <v>6.132918312851405</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.03126997397500399</v>
+      </c>
+      <c r="W90">
+        <v>0.2313327302147691</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1008708837903355</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2855541836205799</v>
+      </c>
+      <c r="C91">
+        <v>-17.96527100537456</v>
+      </c>
+      <c r="D91">
+        <v>9.371728994625434</v>
+      </c>
+      <c r="E91">
+        <v>9.100999999999999</v>
+      </c>
+      <c r="F91">
+        <v>27.501</v>
+      </c>
+      <c r="G91">
+        <v>0.164</v>
+      </c>
+      <c r="H91">
+        <v>12.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>-0.655</v>
+      </c>
+      <c r="L91">
+        <v>0.655</v>
+      </c>
+      <c r="M91">
+        <v>6.5672388</v>
+      </c>
+      <c r="N91">
+        <v>-5.9122388</v>
+      </c>
+      <c r="O91">
+        <v>-1.832794028</v>
+      </c>
+      <c r="P91">
+        <v>-4.079444772</v>
+      </c>
+      <c r="Q91">
+        <v>-4.734444772</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7235761911962102</v>
+      </c>
+      <c r="T91">
+        <v>6.690456341292441</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.03091862595281293</v>
+      </c>
+      <c r="W91">
+        <v>0.2314166321224683</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.09973750307359008</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2875541836205799</v>
+      </c>
+      <c r="C92">
+        <v>-18.34962032298781</v>
+      </c>
+      <c r="D92">
+        <v>9.29637967701219</v>
+      </c>
+      <c r="E92">
+        <v>9.41</v>
+      </c>
+      <c r="F92">
+        <v>27.81</v>
+      </c>
+      <c r="G92">
+        <v>0.164</v>
+      </c>
+      <c r="H92">
+        <v>12.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>-0.655</v>
+      </c>
+      <c r="L92">
+        <v>0.655</v>
+      </c>
+      <c r="M92">
+        <v>6.641028</v>
+      </c>
+      <c r="N92">
+        <v>-5.986028</v>
+      </c>
+      <c r="O92">
+        <v>-1.85566868</v>
+      </c>
+      <c r="P92">
+        <v>-4.13035932</v>
+      </c>
+      <c r="Q92">
+        <v>-4.78535932</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7920538103158312</v>
+      </c>
+      <c r="T92">
+        <v>7.359501975421686</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.03057508566444834</v>
+      </c>
+      <c r="W92">
+        <v>0.2314986695433298</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.09862930859499464</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2895541836205799</v>
+      </c>
+      <c r="C93">
+        <v>-18.73276767752271</v>
+      </c>
+      <c r="D93">
+        <v>9.222232322477289</v>
+      </c>
+      <c r="E93">
+        <v>9.719000000000001</v>
+      </c>
+      <c r="F93">
+        <v>28.119</v>
+      </c>
+      <c r="G93">
+        <v>0.164</v>
+      </c>
+      <c r="H93">
+        <v>12.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>-0.655</v>
+      </c>
+      <c r="L93">
+        <v>0.655</v>
+      </c>
+      <c r="M93">
+        <v>6.714817200000001</v>
+      </c>
+      <c r="N93">
+        <v>-6.0598172</v>
+      </c>
+      <c r="O93">
+        <v>-1.878543332</v>
+      </c>
+      <c r="P93">
+        <v>-4.181273868</v>
+      </c>
+      <c r="Q93">
+        <v>-4.836273868</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8757486781287014</v>
+      </c>
+      <c r="T93">
+        <v>8.177224417135207</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.03023909571209176</v>
+      </c>
+      <c r="W93">
+        <v>0.2315789039439525</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.09754547003900571</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2915541836205799</v>
+      </c>
+      <c r="C94">
+        <v>-19.11474160175513</v>
+      </c>
+      <c r="D94">
+        <v>9.149258398244873</v>
+      </c>
+      <c r="E94">
+        <v>10.028</v>
+      </c>
+      <c r="F94">
+        <v>28.428</v>
+      </c>
+      <c r="G94">
+        <v>0.164</v>
+      </c>
+      <c r="H94">
+        <v>12.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>-0.655</v>
+      </c>
+      <c r="L94">
+        <v>0.655</v>
+      </c>
+      <c r="M94">
+        <v>6.788606400000001</v>
+      </c>
+      <c r="N94">
+        <v>-6.133606400000001</v>
+      </c>
+      <c r="O94">
+        <v>-1.901417984000001</v>
+      </c>
+      <c r="P94">
+        <v>-4.232188416</v>
+      </c>
+      <c r="Q94">
+        <v>-4.887188416</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9803672628947893</v>
+      </c>
+      <c r="T94">
+        <v>9.19937746927711</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02991040988913424</v>
+      </c>
+      <c r="W94">
+        <v>0.2316573941184747</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.09648519319075566</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2935541836205799</v>
+      </c>
+      <c r="C95">
+        <v>-19.49556973245128</v>
+      </c>
+      <c r="D95">
+        <v>9.077430267548724</v>
+      </c>
+      <c r="E95">
+        <v>10.337</v>
+      </c>
+      <c r="F95">
+        <v>28.737</v>
+      </c>
+      <c r="G95">
+        <v>0.164</v>
+      </c>
+      <c r="H95">
+        <v>12.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>-0.655</v>
+      </c>
+      <c r="L95">
+        <v>0.655</v>
+      </c>
+      <c r="M95">
+        <v>6.862395600000001</v>
+      </c>
+      <c r="N95">
+        <v>-6.207395600000001</v>
+      </c>
+      <c r="O95">
+        <v>-1.924292636000001</v>
+      </c>
+      <c r="P95">
+        <v>-4.283102964</v>
+      </c>
+      <c r="Q95">
+        <v>-4.938102964</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.114876871879759</v>
+      </c>
+      <c r="T95">
+        <v>10.51357425060241</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02958879257849839</v>
+      </c>
+      <c r="W95">
+        <v>0.2317341963322546</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.09544771799515617</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2955541836205799</v>
+      </c>
+      <c r="C96">
+        <v>-19.87527884526529</v>
+      </c>
+      <c r="D96">
+        <v>9.006721154734713</v>
+      </c>
+      <c r="E96">
+        <v>10.646</v>
+      </c>
+      <c r="F96">
+        <v>29.046</v>
+      </c>
+      <c r="G96">
+        <v>0.164</v>
+      </c>
+      <c r="H96">
+        <v>12.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>-0.655</v>
+      </c>
+      <c r="L96">
+        <v>0.655</v>
+      </c>
+      <c r="M96">
+        <v>6.9361848</v>
+      </c>
+      <c r="N96">
+        <v>-6.2811848</v>
+      </c>
+      <c r="O96">
+        <v>-1.947167288</v>
+      </c>
+      <c r="P96">
+        <v>-4.334017512</v>
+      </c>
+      <c r="Q96">
+        <v>-4.989017512</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.294223017193053</v>
+      </c>
+      <c r="T96">
+        <v>12.26583662570282</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02927401818936543</v>
+      </c>
+      <c r="W96">
+        <v>0.2318093644563795</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.0944323167398885</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2975541836205799</v>
+      </c>
+      <c r="C97">
+        <v>-20.25389488801837</v>
+      </c>
+      <c r="D97">
+        <v>8.937105111981626</v>
+      </c>
+      <c r="E97">
+        <v>10.955</v>
+      </c>
+      <c r="F97">
+        <v>29.355</v>
+      </c>
+      <c r="G97">
+        <v>0.164</v>
+      </c>
+      <c r="H97">
+        <v>12.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>-0.655</v>
+      </c>
+      <c r="L97">
+        <v>0.655</v>
+      </c>
+      <c r="M97">
+        <v>7.009974000000001</v>
+      </c>
+      <c r="N97">
+        <v>-6.354974</v>
+      </c>
+      <c r="O97">
+        <v>-1.97004194</v>
+      </c>
+      <c r="P97">
+        <v>-4.38493206</v>
+      </c>
+      <c r="Q97">
+        <v>-5.03993206</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.545307620631664</v>
+      </c>
+      <c r="T97">
+        <v>14.71900395084339</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02896587062947737</v>
+      </c>
+      <c r="W97">
+        <v>0.2318829500936808</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.09343829235315282</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2995541836205799</v>
+      </c>
+      <c r="C98">
+        <v>-20.63144301244644</v>
+      </c>
+      <c r="D98">
+        <v>8.868556987553557</v>
+      </c>
+      <c r="E98">
+        <v>11.264</v>
+      </c>
+      <c r="F98">
+        <v>29.664</v>
+      </c>
+      <c r="G98">
+        <v>0.164</v>
+      </c>
+      <c r="H98">
+        <v>12.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>-0.655</v>
+      </c>
+      <c r="L98">
+        <v>0.655</v>
+      </c>
+      <c r="M98">
+        <v>7.0837632</v>
+      </c>
+      <c r="N98">
+        <v>-6.4287632</v>
+      </c>
+      <c r="O98">
+        <v>-1.992916592</v>
+      </c>
+      <c r="P98">
+        <v>-4.435846607999999</v>
+      </c>
+      <c r="Q98">
+        <v>-5.090846608</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.921934525789576</v>
+      </c>
+      <c r="T98">
+        <v>18.39875493855419</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02866414281042032</v>
+      </c>
+      <c r="W98">
+        <v>0.2319550026968716</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.09246497680780752</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3015541836205798</v>
+      </c>
+      <c r="C99">
+        <v>-21.00794760449784</v>
+      </c>
+      <c r="D99">
+        <v>8.801052395502156</v>
+      </c>
+      <c r="E99">
+        <v>11.573</v>
+      </c>
+      <c r="F99">
+        <v>29.973</v>
+      </c>
+      <c r="G99">
+        <v>0.164</v>
+      </c>
+      <c r="H99">
+        <v>12.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>-0.655</v>
+      </c>
+      <c r="L99">
+        <v>0.655</v>
+      </c>
+      <c r="M99">
+        <v>7.1575524</v>
+      </c>
+      <c r="N99">
+        <v>-6.5025524</v>
+      </c>
+      <c r="O99">
+        <v>-2.015791244</v>
+      </c>
+      <c r="P99">
+        <v>-4.486761156</v>
+      </c>
+      <c r="Q99">
+        <v>-5.141761156</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.549646034386102</v>
+      </c>
+      <c r="T99">
+        <v>24.53167325140559</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02836863618350877</v>
+      </c>
+      <c r="W99">
+        <v>0.2320255696793781</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.09151172962422183</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3035541836205799</v>
+      </c>
+      <c r="C100">
+        <v>-21.38343231325784</v>
+      </c>
+      <c r="D100">
+        <v>8.734567686742157</v>
+      </c>
+      <c r="E100">
+        <v>11.882</v>
+      </c>
+      <c r="F100">
+        <v>30.282</v>
+      </c>
+      <c r="G100">
+        <v>0.164</v>
+      </c>
+      <c r="H100">
+        <v>12.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>-0.655</v>
+      </c>
+      <c r="L100">
+        <v>0.655</v>
+      </c>
+      <c r="M100">
+        <v>7.231341599999999</v>
+      </c>
+      <c r="N100">
+        <v>-6.576341599999999</v>
+      </c>
+      <c r="O100">
+        <v>-2.038665896</v>
+      </c>
+      <c r="P100">
+        <v>-4.537675704</v>
+      </c>
+      <c r="Q100">
+        <v>-5.192675704</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.805069051579153</v>
+      </c>
+      <c r="T100">
+        <v>36.79750987710839</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.02807916030408521</v>
+      </c>
+      <c r="W100">
+        <v>0.2320946965193845</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.09057793646479106</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3055541836205798</v>
+      </c>
+      <c r="C101">
+        <v>-21.75792007857188</v>
+      </c>
+      <c r="D101">
+        <v>8.669079921428116</v>
+      </c>
+      <c r="E101">
+        <v>12.191</v>
+      </c>
+      <c r="F101">
+        <v>30.591</v>
+      </c>
+      <c r="G101">
+        <v>0.164</v>
+      </c>
+      <c r="H101">
+        <v>12.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>-0.655</v>
+      </c>
+      <c r="L101">
+        <v>0.655</v>
+      </c>
+      <c r="M101">
+        <v>7.3051308</v>
+      </c>
+      <c r="N101">
+        <v>-6.650130799999999</v>
+      </c>
+      <c r="O101">
+        <v>-2.061540548</v>
+      </c>
+      <c r="P101">
+        <v>-4.588590251999999</v>
+      </c>
+      <c r="Q101">
+        <v>-5.243590252</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.571338103158305</v>
+      </c>
+      <c r="T101">
+        <v>73.59501975421678</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02779553242222577</v>
+      </c>
+      <c r="W101">
+        <v>0.2321624268575725</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.08966300781363157</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/morocco/morocco_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_paper_forest_products.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09684382525883664</v>
+        <v>0.09656452501800838</v>
       </c>
       <c r="C2">
-        <v>26.63885344465605</v>
+        <v>26.47738513044577</v>
       </c>
       <c r="D2">
-        <v>26.61485344465605</v>
+        <v>26.76128513044577</v>
       </c>
       <c r="E2">
-        <v>-21.1</v>
+        <v>-20.7921</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3079</v>
       </c>
       <c r="G2">
         <v>0.024</v>
@@ -1439,28 +1439,28 @@
         <v>1.5125</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01548737</v>
       </c>
       <c r="N2">
-        <v>1.5125</v>
+        <v>1.49701263</v>
       </c>
       <c r="O2">
-        <v>0.4839999999999999</v>
+        <v>0.4790440415999999</v>
       </c>
       <c r="P2">
-        <v>1.0285</v>
+        <v>1.0179685884</v>
       </c>
       <c r="Q2">
-        <v>1.5785</v>
+        <v>1.5679685884</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09684382525883664</v>
+        <v>0.09719442931111957</v>
       </c>
       <c r="T2">
-        <v>0.6652721574126822</v>
+        <v>0.6698417035444058</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>97.66022249097166</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09656452501800838</v>
+        <v>0.0962852247771801</v>
       </c>
       <c r="C3">
-        <v>26.47738513044577</v>
+        <v>26.3175370290913</v>
       </c>
       <c r="D3">
-        <v>26.76128513044577</v>
+        <v>26.9093370290913</v>
       </c>
       <c r="E3">
-        <v>-20.7921</v>
+        <v>-20.4842</v>
       </c>
       <c r="F3">
-        <v>0.3079</v>
+        <v>0.6158</v>
       </c>
       <c r="G3">
         <v>0.024</v>
@@ -1521,28 +1521,28 @@
         <v>1.5125</v>
       </c>
       <c r="M3">
-        <v>0.01548737</v>
+        <v>0.03097474</v>
       </c>
       <c r="N3">
-        <v>1.49701263</v>
+        <v>1.48152526</v>
       </c>
       <c r="O3">
-        <v>0.4790440415999999</v>
+        <v>0.4740880831999999</v>
       </c>
       <c r="P3">
-        <v>1.0179685884</v>
+        <v>1.0074371768</v>
       </c>
       <c r="Q3">
-        <v>1.5679685884</v>
+        <v>1.5574371768</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09719442931111957</v>
+        <v>0.09755218854814296</v>
       </c>
       <c r="T3">
-        <v>0.6698417035444058</v>
+        <v>0.6745045057196337</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>97.66022249097166</v>
+        <v>48.83011124548583</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0962852247771801</v>
+        <v>0.09600592453635182</v>
       </c>
       <c r="C4">
-        <v>26.3175370290913</v>
+        <v>26.15933618077832</v>
       </c>
       <c r="D4">
-        <v>26.9093370290913</v>
+        <v>27.05903618077832</v>
       </c>
       <c r="E4">
-        <v>-20.4842</v>
+        <v>-20.1763</v>
       </c>
       <c r="F4">
-        <v>0.6158</v>
+        <v>0.9237</v>
       </c>
       <c r="G4">
         <v>0.024</v>
@@ -1603,28 +1603,28 @@
         <v>1.5125</v>
       </c>
       <c r="M4">
-        <v>0.03097474</v>
+        <v>0.04646210999999999</v>
       </c>
       <c r="N4">
-        <v>1.48152526</v>
+        <v>1.46603789</v>
       </c>
       <c r="O4">
-        <v>0.4740880831999999</v>
+        <v>0.4691321247999999</v>
       </c>
       <c r="P4">
-        <v>1.0074371768</v>
+        <v>0.9969057651999997</v>
       </c>
       <c r="Q4">
-        <v>1.5574371768</v>
+        <v>1.5469057652</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09755218854814296</v>
+        <v>0.09791732426428022</v>
       </c>
       <c r="T4">
-        <v>0.6745045057196337</v>
+        <v>0.6792634481458973</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>48.83011124548583</v>
+        <v>32.55340749699056</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09600592453635182</v>
+        <v>0.09572662429552352</v>
       </c>
       <c r="C5">
-        <v>26.15933618077832</v>
+        <v>26.00281023076693</v>
       </c>
       <c r="D5">
-        <v>27.05903618077832</v>
+        <v>27.21041023076693</v>
       </c>
       <c r="E5">
-        <v>-20.1763</v>
+        <v>-19.8684</v>
       </c>
       <c r="F5">
-        <v>0.9237</v>
+        <v>1.2316</v>
       </c>
       <c r="G5">
         <v>0.024</v>
@@ -1685,28 +1685,28 @@
         <v>1.5125</v>
       </c>
       <c r="M5">
-        <v>0.04646210999999999</v>
+        <v>0.06194948</v>
       </c>
       <c r="N5">
-        <v>1.46603789</v>
+        <v>1.45055052</v>
       </c>
       <c r="O5">
-        <v>0.4691321247999999</v>
+        <v>0.4641761663999999</v>
       </c>
       <c r="P5">
-        <v>0.9969057651999997</v>
+        <v>0.9863743535999998</v>
       </c>
       <c r="Q5">
-        <v>1.5469057652</v>
+        <v>1.5363743536</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09791732426428022</v>
+        <v>0.09829006697450368</v>
       </c>
       <c r="T5">
-        <v>0.6792634481458973</v>
+        <v>0.6841215352060415</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>32.55340749699056</v>
+        <v>24.41505562274292</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09572662429552352</v>
+        <v>0.09544732405469525</v>
       </c>
       <c r="C6">
-        <v>26.00281023076693</v>
+        <v>25.84798744641136</v>
       </c>
       <c r="D6">
-        <v>27.21041023076693</v>
+        <v>27.36348744641136</v>
       </c>
       <c r="E6">
-        <v>-19.8684</v>
+        <v>-19.5605</v>
       </c>
       <c r="F6">
-        <v>1.2316</v>
+        <v>1.5395</v>
       </c>
       <c r="G6">
         <v>0.024</v>
@@ -1767,28 +1767,28 @@
         <v>1.5125</v>
       </c>
       <c r="M6">
-        <v>0.06194948</v>
+        <v>0.07743685</v>
       </c>
       <c r="N6">
-        <v>1.45055052</v>
+        <v>1.43506315</v>
       </c>
       <c r="O6">
-        <v>0.4641761663999999</v>
+        <v>0.4592202079999999</v>
       </c>
       <c r="P6">
-        <v>0.9863743535999998</v>
+        <v>0.9758429419999999</v>
       </c>
       <c r="Q6">
-        <v>1.5363743536</v>
+        <v>1.525842942</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09829006697450368</v>
+        <v>0.09867065689967922</v>
       </c>
       <c r="T6">
-        <v>0.6841215352060415</v>
+        <v>0.6890818977832414</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>24.41505562274292</v>
+        <v>19.53204449819433</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09544732405469525</v>
+        <v>0.09516802381386696</v>
       </c>
       <c r="C7">
-        <v>25.84798744641136</v>
+        <v>25.69489673475758</v>
       </c>
       <c r="D7">
-        <v>27.36348744641136</v>
+        <v>27.51829673475758</v>
       </c>
       <c r="E7">
-        <v>-19.5605</v>
+        <v>-19.2526</v>
       </c>
       <c r="F7">
-        <v>1.5395</v>
+        <v>1.8474</v>
       </c>
       <c r="G7">
         <v>0.024</v>
@@ -1849,28 +1849,28 @@
         <v>1.5125</v>
       </c>
       <c r="M7">
-        <v>0.07743685</v>
+        <v>0.09292422</v>
       </c>
       <c r="N7">
-        <v>1.43506315</v>
+        <v>1.41957578</v>
       </c>
       <c r="O7">
-        <v>0.4592202079999999</v>
+        <v>0.4542642495999999</v>
       </c>
       <c r="P7">
-        <v>0.9758429419999999</v>
+        <v>0.9653115303999997</v>
       </c>
       <c r="Q7">
-        <v>1.525842942</v>
+        <v>1.5153115304</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09867065689967922</v>
+        <v>0.09905934448283721</v>
       </c>
       <c r="T7">
-        <v>0.6890818977832414</v>
+        <v>0.6941477999897433</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.53204449819433</v>
+        <v>16.27670374849528</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09516802381386696</v>
+        <v>0.09488872357303872</v>
       </c>
       <c r="C8">
-        <v>25.69489673475758</v>
+        <v>25.54356766074153</v>
       </c>
       <c r="D8">
-        <v>27.51829673475758</v>
+        <v>27.67486766074153</v>
       </c>
       <c r="E8">
-        <v>-19.2526</v>
+        <v>-18.9447</v>
       </c>
       <c r="F8">
-        <v>1.8474</v>
+        <v>2.1553</v>
       </c>
       <c r="G8">
         <v>0.024</v>
@@ -1931,28 +1931,28 @@
         <v>1.5125</v>
       </c>
       <c r="M8">
-        <v>0.09292421999999999</v>
+        <v>0.10841159</v>
       </c>
       <c r="N8">
-        <v>1.41957578</v>
+        <v>1.40408841</v>
       </c>
       <c r="O8">
-        <v>0.4542642495999999</v>
+        <v>0.4493082911999999</v>
       </c>
       <c r="P8">
-        <v>0.9653115303999997</v>
+        <v>0.9547801187999998</v>
       </c>
       <c r="Q8">
-        <v>1.5153115304</v>
+        <v>1.5047801188</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09905934448283721</v>
+        <v>0.0994563909387513</v>
       </c>
       <c r="T8">
-        <v>0.6941477999897433</v>
+        <v>0.6993226463297184</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.27670374849528</v>
+        <v>13.9514603558531</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09488872357303871</v>
+        <v>0.09469102333221044</v>
       </c>
       <c r="C9">
-        <v>25.54356766074154</v>
+        <v>25.34757630221631</v>
       </c>
       <c r="D9">
-        <v>27.67486766074154</v>
+        <v>27.78677630221631</v>
       </c>
       <c r="E9">
-        <v>-18.9447</v>
+        <v>-18.6368</v>
       </c>
       <c r="F9">
-        <v>2.1553</v>
+        <v>2.4632</v>
       </c>
       <c r="G9">
         <v>0.024</v>
@@ -2013,45 +2013,45 @@
         <v>1.5125</v>
       </c>
       <c r="M9">
-        <v>0.10841159</v>
+        <v>0.12759376</v>
       </c>
       <c r="N9">
-        <v>1.40408841</v>
+        <v>1.38490624</v>
       </c>
       <c r="O9">
-        <v>0.4493082911999999</v>
+        <v>0.4431699968</v>
       </c>
       <c r="P9">
-        <v>0.9547801187999998</v>
+        <v>0.9417362431999998</v>
       </c>
       <c r="Q9">
-        <v>1.5047801188</v>
+        <v>1.4917362432</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0994563909387513</v>
+        <v>0.09986206883935916</v>
       </c>
       <c r="T9">
-        <v>0.6993226463297184</v>
+        <v>0.7046099893292582</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.32</v>
       </c>
       <c r="W9">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.9514603558531</v>
+        <v>11.85402797127383</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09469102333221044</v>
+        <v>0.09442192309138216</v>
       </c>
       <c r="C10">
-        <v>25.34757630221631</v>
+        <v>25.19346347720556</v>
       </c>
       <c r="D10">
-        <v>27.78677630221631</v>
+        <v>27.94056347720556</v>
       </c>
       <c r="E10">
-        <v>-18.6368</v>
+        <v>-18.3289</v>
       </c>
       <c r="F10">
-        <v>2.4632</v>
+        <v>2.7711</v>
       </c>
       <c r="G10">
         <v>0.024</v>
@@ -2095,28 +2095,28 @@
         <v>1.5125</v>
       </c>
       <c r="M10">
-        <v>0.12759376</v>
+        <v>0.14354298</v>
       </c>
       <c r="N10">
-        <v>1.38490624</v>
+        <v>1.36895702</v>
       </c>
       <c r="O10">
-        <v>0.4431699968</v>
+        <v>0.4380662464</v>
       </c>
       <c r="P10">
-        <v>0.9417362431999998</v>
+        <v>0.9308907735999998</v>
       </c>
       <c r="Q10">
-        <v>1.4917362432</v>
+        <v>1.4808907736</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09986206883935916</v>
+        <v>0.1002766627377826</v>
       </c>
       <c r="T10">
-        <v>0.7046099893292582</v>
+        <v>0.7100135376694472</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.85402797127383</v>
+        <v>10.5369137522434</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09442192309138216</v>
+        <v>0.09426842285055388</v>
       </c>
       <c r="C11">
-        <v>25.19346347720556</v>
+        <v>24.97405167158838</v>
       </c>
       <c r="D11">
-        <v>27.94056347720556</v>
+        <v>28.02905167158838</v>
       </c>
       <c r="E11">
-        <v>-18.3289</v>
+        <v>-18.021</v>
       </c>
       <c r="F11">
-        <v>2.7711</v>
+        <v>3.079</v>
       </c>
       <c r="G11">
         <v>0.024</v>
@@ -2177,45 +2177,45 @@
         <v>1.5125</v>
       </c>
       <c r="M11">
-        <v>0.14354298</v>
+        <v>0.1647265</v>
       </c>
       <c r="N11">
-        <v>1.36895702</v>
+        <v>1.3477735</v>
       </c>
       <c r="O11">
-        <v>0.4380662464</v>
+        <v>0.4312875199999999</v>
       </c>
       <c r="P11">
-        <v>0.9308907735999998</v>
+        <v>0.9164859799999998</v>
       </c>
       <c r="Q11">
-        <v>1.4808907736</v>
+        <v>1.46648598</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1002766627377826</v>
+        <v>0.1007004698339488</v>
       </c>
       <c r="T11">
-        <v>0.7100135376694472</v>
+        <v>0.7155371648616404</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.32</v>
       </c>
       <c r="W11">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.5369137522434</v>
+        <v>9.181886338870795</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09426842285055388</v>
+        <v>0.09401088260972559</v>
       </c>
       <c r="C12">
-        <v>24.97405167158838</v>
+        <v>24.81588153188</v>
       </c>
       <c r="D12">
-        <v>28.02905167158838</v>
+        <v>28.17878153188</v>
       </c>
       <c r="E12">
-        <v>-18.021</v>
+        <v>-17.7131</v>
       </c>
       <c r="F12">
-        <v>3.079</v>
+        <v>3.3869</v>
       </c>
       <c r="G12">
         <v>0.024</v>
@@ -2259,28 +2259,28 @@
         <v>1.5125</v>
       </c>
       <c r="M12">
-        <v>0.1647265</v>
+        <v>0.18119915</v>
       </c>
       <c r="N12">
-        <v>1.3477735</v>
+        <v>1.33130085</v>
       </c>
       <c r="O12">
-        <v>0.4312875199999999</v>
+        <v>0.426016272</v>
       </c>
       <c r="P12">
-        <v>0.9164859799999998</v>
+        <v>0.9052845779999998</v>
       </c>
       <c r="Q12">
-        <v>1.46648598</v>
+        <v>1.455284578</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1007004698339488</v>
+        <v>0.1011338006850849</v>
       </c>
       <c r="T12">
-        <v>0.7155371648616404</v>
+        <v>0.7211849185075907</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.181886338870793</v>
+        <v>8.347169398973449</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09401088260972559</v>
+        <v>0.09375334236889733</v>
       </c>
       <c r="C13">
-        <v>24.81588153188</v>
+        <v>24.65931968316336</v>
       </c>
       <c r="D13">
-        <v>28.17878153188</v>
+        <v>28.33011968316336</v>
       </c>
       <c r="E13">
-        <v>-17.7131</v>
+        <v>-17.4052</v>
       </c>
       <c r="F13">
-        <v>3.3869</v>
+        <v>3.6948</v>
       </c>
       <c r="G13">
         <v>0.024</v>
@@ -2341,28 +2341,28 @@
         <v>1.5125</v>
       </c>
       <c r="M13">
-        <v>0.18119915</v>
+        <v>0.1976718</v>
       </c>
       <c r="N13">
-        <v>1.33130085</v>
+        <v>1.3148282</v>
       </c>
       <c r="O13">
-        <v>0.426016272</v>
+        <v>0.4207450239999999</v>
       </c>
       <c r="P13">
-        <v>0.9052845779999998</v>
+        <v>0.8940831759999999</v>
       </c>
       <c r="Q13">
-        <v>1.455284578</v>
+        <v>1.444083176</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1011338006850849</v>
+        <v>0.1015769799646561</v>
       </c>
       <c r="T13">
-        <v>0.7211849185075907</v>
+        <v>0.7269610301909492</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.347169398973449</v>
+        <v>7.651571949058996</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09375334236889733</v>
+        <v>0.09356652212806904</v>
       </c>
       <c r="C14">
-        <v>24.65931968316336</v>
+        <v>24.46222196782023</v>
       </c>
       <c r="D14">
-        <v>28.33011968316336</v>
+        <v>28.44092196782023</v>
       </c>
       <c r="E14">
-        <v>-17.4052</v>
+        <v>-17.0973</v>
       </c>
       <c r="F14">
-        <v>3.6948</v>
+        <v>4.0027</v>
       </c>
       <c r="G14">
         <v>0.024</v>
@@ -2423,45 +2423,45 @@
         <v>1.5125</v>
       </c>
       <c r="M14">
-        <v>0.1976718</v>
+        <v>0.21734661</v>
       </c>
       <c r="N14">
-        <v>1.3148282</v>
+        <v>1.29515339</v>
       </c>
       <c r="O14">
-        <v>0.4207450239999999</v>
+        <v>0.4144490848</v>
       </c>
       <c r="P14">
-        <v>0.8940831759999999</v>
+        <v>0.8807043051999999</v>
       </c>
       <c r="Q14">
-        <v>1.444083176</v>
+        <v>1.4307043052</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1015769799646561</v>
+        <v>0.1020303472736426</v>
       </c>
       <c r="T14">
-        <v>0.7269610301909492</v>
+        <v>0.7328699260509364</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.32</v>
       </c>
       <c r="W14">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>7.651571949058996</v>
+        <v>6.958930714401296</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09356652212806904</v>
+        <v>0.09331442188724076</v>
       </c>
       <c r="C15">
-        <v>24.46222196782023</v>
+        <v>24.30522274684015</v>
       </c>
       <c r="D15">
-        <v>28.44092196782023</v>
+        <v>28.59182274684015</v>
       </c>
       <c r="E15">
-        <v>-17.0973</v>
+        <v>-16.7894</v>
       </c>
       <c r="F15">
-        <v>4.0027</v>
+        <v>4.3106</v>
       </c>
       <c r="G15">
         <v>0.024</v>
@@ -2505,28 +2505,28 @@
         <v>1.5125</v>
       </c>
       <c r="M15">
-        <v>0.21734661</v>
+        <v>0.23406558</v>
       </c>
       <c r="N15">
-        <v>1.29515339</v>
+        <v>1.27843442</v>
       </c>
       <c r="O15">
-        <v>0.4144490848</v>
+        <v>0.4090990143999999</v>
       </c>
       <c r="P15">
-        <v>0.8807043051999999</v>
+        <v>0.8693354055999998</v>
       </c>
       <c r="Q15">
-        <v>1.4307043052</v>
+        <v>1.4193354056</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1020303472736426</v>
+        <v>0.1024942580084195</v>
       </c>
       <c r="T15">
-        <v>0.7328699260509364</v>
+        <v>0.738916238093714</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.958930714401296</v>
+        <v>6.461864234801203</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09331442188724076</v>
+        <v>0.09316432164641249</v>
       </c>
       <c r="C16">
-        <v>24.30522274684015</v>
+        <v>24.08793186633854</v>
       </c>
       <c r="D16">
-        <v>28.59182274684015</v>
+        <v>28.68243186633854</v>
       </c>
       <c r="E16">
-        <v>-16.7894</v>
+        <v>-16.4815</v>
       </c>
       <c r="F16">
-        <v>4.3106</v>
+        <v>4.618500000000001</v>
       </c>
       <c r="G16">
         <v>0.024</v>
@@ -2587,45 +2587,45 @@
         <v>1.5125</v>
       </c>
       <c r="M16">
-        <v>0.23406558</v>
+        <v>0.2554030500000001</v>
       </c>
       <c r="N16">
-        <v>1.27843442</v>
+        <v>1.25709695</v>
       </c>
       <c r="O16">
-        <v>0.4090990143999999</v>
+        <v>0.4022710239999999</v>
       </c>
       <c r="P16">
-        <v>0.8693354055999998</v>
+        <v>0.8548259259999998</v>
       </c>
       <c r="Q16">
-        <v>1.4193354056</v>
+        <v>1.404825926</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1024942580084195</v>
+        <v>0.1029690842898971</v>
       </c>
       <c r="T16">
-        <v>0.738916238093714</v>
+        <v>0.7451048163022042</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.32</v>
       </c>
       <c r="W16">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.461864234801203</v>
+        <v>5.922012286070975</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09316432164641249</v>
+        <v>0.09291902140558422</v>
       </c>
       <c r="C17">
-        <v>24.08793186633854</v>
+        <v>23.92935176379124</v>
       </c>
       <c r="D17">
-        <v>28.68243186633854</v>
+        <v>28.83175176379124</v>
       </c>
       <c r="E17">
-        <v>-16.4815</v>
+        <v>-16.1736</v>
       </c>
       <c r="F17">
-        <v>4.6185</v>
+        <v>4.9264</v>
       </c>
       <c r="G17">
         <v>0.024</v>
@@ -2669,28 +2669,28 @@
         <v>1.5125</v>
       </c>
       <c r="M17">
-        <v>0.25540305</v>
+        <v>0.27242992</v>
       </c>
       <c r="N17">
-        <v>1.25709695</v>
+        <v>1.24007008</v>
       </c>
       <c r="O17">
-        <v>0.4022710239999999</v>
+        <v>0.3968224255999999</v>
       </c>
       <c r="P17">
-        <v>0.8548259259999998</v>
+        <v>0.8432476543999998</v>
       </c>
       <c r="Q17">
-        <v>1.404825926</v>
+        <v>1.3932476544</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1029690842898971</v>
+        <v>0.1034552159590288</v>
       </c>
       <c r="T17">
-        <v>0.7451048163022042</v>
+        <v>0.7514407416108964</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.922012286070975</v>
+        <v>5.55188651819154</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09291902140558422</v>
+        <v>0.09267372116475592</v>
       </c>
       <c r="C18">
-        <v>23.92935176379124</v>
+        <v>23.77233450737161</v>
       </c>
       <c r="D18">
-        <v>28.83175176379124</v>
+        <v>28.98263450737161</v>
       </c>
       <c r="E18">
-        <v>-16.1736</v>
+        <v>-15.8657</v>
       </c>
       <c r="F18">
-        <v>4.9264</v>
+        <v>5.2343</v>
       </c>
       <c r="G18">
         <v>0.024</v>
@@ -2751,28 +2751,28 @@
         <v>1.5125</v>
       </c>
       <c r="M18">
-        <v>0.27242992</v>
+        <v>0.28945679</v>
       </c>
       <c r="N18">
-        <v>1.24007008</v>
+        <v>1.22304321</v>
       </c>
       <c r="O18">
-        <v>0.3968224255999999</v>
+        <v>0.3913738271999999</v>
       </c>
       <c r="P18">
-        <v>0.8432476543999998</v>
+        <v>0.8316693827999998</v>
       </c>
       <c r="Q18">
-        <v>1.3932476544</v>
+        <v>1.3816693828</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1034552159590288</v>
+        <v>0.1039530616442843</v>
       </c>
       <c r="T18">
-        <v>0.7514407416108964</v>
+        <v>0.7579293398185931</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.55188651819154</v>
+        <v>5.22530495829792</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09267372116475592</v>
+        <v>0.09242842092392765</v>
       </c>
       <c r="C19">
-        <v>23.77233450737161</v>
+        <v>23.61690476228534</v>
       </c>
       <c r="D19">
-        <v>28.98263450737161</v>
+        <v>29.13510476228534</v>
       </c>
       <c r="E19">
-        <v>-15.8657</v>
+        <v>-15.5578</v>
       </c>
       <c r="F19">
-        <v>5.2343</v>
+        <v>5.5422</v>
       </c>
       <c r="G19">
         <v>0.024</v>
@@ -2833,28 +2833,28 @@
         <v>1.5125</v>
       </c>
       <c r="M19">
-        <v>0.28945679</v>
+        <v>0.30648366</v>
       </c>
       <c r="N19">
-        <v>1.22304321</v>
+        <v>1.20601634</v>
       </c>
       <c r="O19">
-        <v>0.3913738271999999</v>
+        <v>0.3859252287999999</v>
       </c>
       <c r="P19">
-        <v>0.8316693827999998</v>
+        <v>0.8200911111999998</v>
       </c>
       <c r="Q19">
-        <v>1.3816693828</v>
+        <v>1.3700911112</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1039530616442843</v>
+        <v>0.1044630499072288</v>
       </c>
       <c r="T19">
-        <v>0.7579293398185931</v>
+        <v>0.7645761965191605</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.22530495829792</v>
+        <v>4.935010238392479</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09242842092392767</v>
+        <v>0.09218312068309938</v>
       </c>
       <c r="C20">
-        <v>23.61690476228533</v>
+        <v>23.46308771551254</v>
       </c>
       <c r="D20">
-        <v>29.13510476228533</v>
+        <v>29.28918771551254</v>
       </c>
       <c r="E20">
-        <v>-15.5578</v>
+        <v>-15.2499</v>
       </c>
       <c r="F20">
-        <v>5.542199999999999</v>
+        <v>5.8501</v>
       </c>
       <c r="G20">
         <v>0.024</v>
@@ -2915,28 +2915,28 @@
         <v>1.5125</v>
       </c>
       <c r="M20">
-        <v>0.30648366</v>
+        <v>0.32351053</v>
       </c>
       <c r="N20">
-        <v>1.20601634</v>
+        <v>1.18898947</v>
       </c>
       <c r="O20">
-        <v>0.3859252287999999</v>
+        <v>0.3804766303999999</v>
       </c>
       <c r="P20">
-        <v>0.8200911111999998</v>
+        <v>0.8085128395999998</v>
       </c>
       <c r="Q20">
-        <v>1.3700911112</v>
+        <v>1.358512839599999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1044630499072288</v>
+        <v>0.1049856304729622</v>
       </c>
       <c r="T20">
-        <v>0.7645761965191605</v>
+        <v>0.7713871731382607</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.935010238392479</v>
+        <v>4.675272857424455</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09218312068309938</v>
+        <v>0.09227782044227112</v>
       </c>
       <c r="C21">
-        <v>23.46308771551254</v>
+        <v>23.09551023931849</v>
       </c>
       <c r="D21">
-        <v>29.28918771551254</v>
+        <v>29.22951023931849</v>
       </c>
       <c r="E21">
-        <v>-15.2499</v>
+        <v>-14.942</v>
       </c>
       <c r="F21">
-        <v>5.8501</v>
+        <v>6.158</v>
       </c>
       <c r="G21">
         <v>0.024</v>
@@ -2997,45 +2997,45 @@
         <v>1.5125</v>
       </c>
       <c r="M21">
-        <v>0.32351053</v>
+        <v>0.3559324</v>
       </c>
       <c r="N21">
-        <v>1.18898947</v>
+        <v>1.1565676</v>
       </c>
       <c r="O21">
-        <v>0.3804766303999999</v>
+        <v>0.370101632</v>
       </c>
       <c r="P21">
-        <v>0.8085128395999998</v>
+        <v>0.7864659679999999</v>
       </c>
       <c r="Q21">
-        <v>1.358512839599999</v>
+        <v>1.336465968</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1049856304729622</v>
+        <v>0.1055212755528389</v>
       </c>
       <c r="T21">
-        <v>0.7713871731382607</v>
+        <v>0.7783684241728381</v>
       </c>
       <c r="U21">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V21">
         <v>0.32</v>
       </c>
       <c r="W21">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.675272857424455</v>
+        <v>4.249402414615808</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09227782044227112</v>
+        <v>0.09204952020144283</v>
       </c>
       <c r="C22">
-        <v>23.09551023931849</v>
+        <v>22.93189507076894</v>
       </c>
       <c r="D22">
-        <v>29.22951023931849</v>
+        <v>29.37379507076894</v>
       </c>
       <c r="E22">
-        <v>-14.942</v>
+        <v>-14.6341</v>
       </c>
       <c r="F22">
-        <v>6.158</v>
+        <v>6.4659</v>
       </c>
       <c r="G22">
         <v>0.024</v>
@@ -3079,28 +3079,28 @@
         <v>1.5125</v>
       </c>
       <c r="M22">
-        <v>0.3559324</v>
+        <v>0.3737290200000001</v>
       </c>
       <c r="N22">
-        <v>1.1565676</v>
+        <v>1.13877098</v>
       </c>
       <c r="O22">
-        <v>0.370101632</v>
+        <v>0.3644067135999999</v>
       </c>
       <c r="P22">
-        <v>0.7864659679999999</v>
+        <v>0.7743642663999998</v>
       </c>
       <c r="Q22">
-        <v>1.336465968</v>
+        <v>1.324364266399999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1055212755528389</v>
+        <v>0.1060704812676491</v>
       </c>
       <c r="T22">
-        <v>0.7783684241728381</v>
+        <v>0.7855264157399366</v>
       </c>
       <c r="U22">
         <v>0.0578</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.249402414615808</v>
+        <v>4.047049918681721</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09204952020144283</v>
+        <v>0.09234481996061454</v>
       </c>
       <c r="C23">
-        <v>22.93189507076894</v>
+        <v>22.4376354582987</v>
       </c>
       <c r="D23">
-        <v>29.37379507076894</v>
+        <v>29.1874354582987</v>
       </c>
       <c r="E23">
-        <v>-14.6341</v>
+        <v>-14.3262</v>
       </c>
       <c r="F23">
-        <v>6.4659</v>
+        <v>6.7738</v>
       </c>
       <c r="G23">
         <v>0.024</v>
@@ -3161,45 +3161,45 @@
         <v>1.5125</v>
       </c>
       <c r="M23">
-        <v>0.37372902</v>
+        <v>0.41523394</v>
       </c>
       <c r="N23">
-        <v>1.13877098</v>
+        <v>1.09726606</v>
       </c>
       <c r="O23">
-        <v>0.3644067135999999</v>
+        <v>0.3511251391999999</v>
       </c>
       <c r="P23">
-        <v>0.7743642663999998</v>
+        <v>0.7461409207999998</v>
       </c>
       <c r="Q23">
-        <v>1.324364266399999</v>
+        <v>1.2961409208</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1060704812676491</v>
+        <v>0.1066337691802751</v>
       </c>
       <c r="T23">
-        <v>0.7855264157399366</v>
+        <v>0.7928679455523454</v>
       </c>
       <c r="U23">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V23">
         <v>0.32</v>
       </c>
       <c r="W23">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.047049918681722</v>
+        <v>3.642524982423161</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09234481996061454</v>
+        <v>0.09257823971978628</v>
       </c>
       <c r="C24">
-        <v>22.4376354582987</v>
+        <v>21.9840924371776</v>
       </c>
       <c r="D24">
-        <v>29.1874354582987</v>
+        <v>29.0417924371776</v>
       </c>
       <c r="E24">
-        <v>-14.3262</v>
+        <v>-14.0183</v>
       </c>
       <c r="F24">
-        <v>6.7738</v>
+        <v>7.081700000000001</v>
       </c>
       <c r="G24">
         <v>0.024</v>
@@ -3243,45 +3243,45 @@
         <v>1.5125</v>
       </c>
       <c r="M24">
-        <v>0.41523394</v>
+        <v>0.4539369700000001</v>
       </c>
       <c r="N24">
-        <v>1.09726606</v>
+        <v>1.05856303</v>
       </c>
       <c r="O24">
-        <v>0.3511251391999999</v>
+        <v>0.3387401695999999</v>
       </c>
       <c r="P24">
-        <v>0.7461409207999998</v>
+        <v>0.7198228603999999</v>
       </c>
       <c r="Q24">
-        <v>1.2961409208</v>
+        <v>1.2698228604</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1066337691802751</v>
+        <v>0.1072116879477744</v>
       </c>
       <c r="T24">
-        <v>0.7928679455523454</v>
+        <v>0.8004001644507905</v>
       </c>
       <c r="U24">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V24">
         <v>0.32</v>
       </c>
       <c r="W24">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.642524982423161</v>
+        <v>3.331960382076832</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09257823971978628</v>
+        <v>0.09239277947895799</v>
       </c>
       <c r="C25">
-        <v>21.9840924371776</v>
+        <v>21.79179184720886</v>
       </c>
       <c r="D25">
-        <v>29.0417924371776</v>
+        <v>29.15739184720886</v>
       </c>
       <c r="E25">
-        <v>-14.0183</v>
+        <v>-13.7104</v>
       </c>
       <c r="F25">
-        <v>7.081700000000001</v>
+        <v>7.389600000000001</v>
       </c>
       <c r="G25">
         <v>0.024</v>
@@ -3325,28 +3325,28 @@
         <v>1.5125</v>
       </c>
       <c r="M25">
-        <v>0.4539369700000001</v>
+        <v>0.47367336</v>
       </c>
       <c r="N25">
-        <v>1.05856303</v>
+        <v>1.03882664</v>
       </c>
       <c r="O25">
-        <v>0.3387401695999999</v>
+        <v>0.3324245247999999</v>
       </c>
       <c r="P25">
-        <v>0.7198228603999999</v>
+        <v>0.7064021151999997</v>
       </c>
       <c r="Q25">
-        <v>1.2698228604</v>
+        <v>1.2564021152</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1072116879477744</v>
+        <v>0.1078048151038921</v>
       </c>
       <c r="T25">
-        <v>0.8004001644507905</v>
+        <v>0.8081305996360371</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.331960382076832</v>
+        <v>3.193128699490298</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09239277947895799</v>
+        <v>0.09220731923812973</v>
       </c>
       <c r="C26">
-        <v>21.79179184720886</v>
+        <v>21.60041521039128</v>
       </c>
       <c r="D26">
-        <v>29.15739184720886</v>
+        <v>29.27391521039128</v>
       </c>
       <c r="E26">
-        <v>-13.7104</v>
+        <v>-13.4025</v>
       </c>
       <c r="F26">
-        <v>7.3896</v>
+        <v>7.6975</v>
       </c>
       <c r="G26">
         <v>0.024</v>
@@ -3407,28 +3407,28 @@
         <v>1.5125</v>
       </c>
       <c r="M26">
-        <v>0.47367336</v>
+        <v>0.49340975</v>
       </c>
       <c r="N26">
-        <v>1.03882664</v>
+        <v>1.01909025</v>
       </c>
       <c r="O26">
-        <v>0.3324245247999999</v>
+        <v>0.3261088799999999</v>
       </c>
       <c r="P26">
-        <v>0.7064021151999997</v>
+        <v>0.6929813699999998</v>
       </c>
       <c r="Q26">
-        <v>1.2564021152</v>
+        <v>1.24298137</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1078048151038921</v>
+        <v>0.108413758984173</v>
       </c>
       <c r="T26">
-        <v>0.8081305996360371</v>
+        <v>0.8160671797595568</v>
       </c>
       <c r="U26">
         <v>0.0641</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.193128699490298</v>
+        <v>3.065403551510686</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09220731923812973</v>
+        <v>0.09340089899730145</v>
       </c>
       <c r="C27">
-        <v>21.60041521039128</v>
+        <v>20.55847964797863</v>
       </c>
       <c r="D27">
-        <v>29.27391521039128</v>
+        <v>28.53987964797863</v>
       </c>
       <c r="E27">
-        <v>-13.4025</v>
+        <v>-13.0946</v>
       </c>
       <c r="F27">
-        <v>7.6975</v>
+        <v>8.0054</v>
       </c>
       <c r="G27">
         <v>0.024</v>
@@ -3489,45 +3489,45 @@
         <v>1.5125</v>
       </c>
       <c r="M27">
-        <v>0.49340975</v>
+        <v>0.5755882600000001</v>
       </c>
       <c r="N27">
-        <v>1.01909025</v>
+        <v>0.9369117399999997</v>
       </c>
       <c r="O27">
-        <v>0.3261088799999999</v>
+        <v>0.2998117567999999</v>
       </c>
       <c r="P27">
-        <v>0.6929813699999998</v>
+        <v>0.6370999831999997</v>
       </c>
       <c r="Q27">
-        <v>1.24298137</v>
+        <v>1.1870999832</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.108413758984173</v>
+        <v>0.1090391608071641</v>
       </c>
       <c r="T27">
-        <v>0.8160671797595568</v>
+        <v>0.8242182620485771</v>
       </c>
       <c r="U27">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V27">
         <v>0.32</v>
       </c>
       <c r="W27">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.065403551510686</v>
+        <v>2.627746438052784</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09340089899730145</v>
+        <v>0.09326847875647316</v>
       </c>
       <c r="C28">
-        <v>20.55847964797863</v>
+        <v>20.33019580242892</v>
       </c>
       <c r="D28">
-        <v>28.53987964797863</v>
+        <v>28.61949580242891</v>
       </c>
       <c r="E28">
-        <v>-13.0946</v>
+        <v>-12.7867</v>
       </c>
       <c r="F28">
-        <v>8.0054</v>
+        <v>8.3133</v>
       </c>
       <c r="G28">
         <v>0.024</v>
@@ -3571,28 +3571,28 @@
         <v>1.5125</v>
       </c>
       <c r="M28">
-        <v>0.5755882600000001</v>
+        <v>0.59772627</v>
       </c>
       <c r="N28">
-        <v>0.9369117399999997</v>
+        <v>0.9147737299999997</v>
       </c>
       <c r="O28">
-        <v>0.2998117567999999</v>
+        <v>0.2927275935999999</v>
       </c>
       <c r="P28">
-        <v>0.6370999831999997</v>
+        <v>0.6220461363999998</v>
       </c>
       <c r="Q28">
-        <v>1.1870999832</v>
+        <v>1.1720461364</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1090391608071641</v>
+        <v>0.1096816969266756</v>
       </c>
       <c r="T28">
-        <v>0.8242182620485771</v>
+        <v>0.8325926616605842</v>
       </c>
       <c r="U28">
         <v>0.07190000000000001</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.627746438052784</v>
+        <v>2.530422495902681</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09326847875647316</v>
+        <v>0.09387861851564488</v>
       </c>
       <c r="C29">
-        <v>20.33019580242892</v>
+        <v>19.6591012511789</v>
       </c>
       <c r="D29">
-        <v>28.61949580242891</v>
+        <v>28.2563012511789</v>
       </c>
       <c r="E29">
-        <v>-12.7867</v>
+        <v>-12.4788</v>
       </c>
       <c r="F29">
-        <v>8.3133</v>
+        <v>8.6212</v>
       </c>
       <c r="G29">
         <v>0.024</v>
@@ -3653,45 +3653,45 @@
         <v>1.5125</v>
       </c>
       <c r="M29">
-        <v>0.59772627</v>
+        <v>0.6534869600000001</v>
       </c>
       <c r="N29">
-        <v>0.9147737299999997</v>
+        <v>0.8590130399999997</v>
       </c>
       <c r="O29">
-        <v>0.2927275935999999</v>
+        <v>0.2748841727999999</v>
       </c>
       <c r="P29">
-        <v>0.6220461363999998</v>
+        <v>0.5841288671999998</v>
       </c>
       <c r="Q29">
-        <v>1.1720461364</v>
+        <v>1.1341288672</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1096816969266756</v>
+        <v>0.110342081271729</v>
       </c>
       <c r="T29">
-        <v>0.8325926616605842</v>
+        <v>0.841199683484036</v>
       </c>
       <c r="U29">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V29">
         <v>0.32</v>
       </c>
       <c r="W29">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.530422495902681</v>
+        <v>2.314506780670879</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09387861851564488</v>
+        <v>0.0937727182748166</v>
       </c>
       <c r="C30">
-        <v>19.6591012511789</v>
+        <v>19.41357731021885</v>
       </c>
       <c r="D30">
-        <v>28.2563012511789</v>
+        <v>28.31867731021885</v>
       </c>
       <c r="E30">
-        <v>-12.4788</v>
+        <v>-12.1709</v>
       </c>
       <c r="F30">
-        <v>8.6212</v>
+        <v>8.9291</v>
       </c>
       <c r="G30">
         <v>0.024</v>
@@ -3735,28 +3735,28 @@
         <v>1.5125</v>
       </c>
       <c r="M30">
-        <v>0.6534869600000001</v>
+        <v>0.67682578</v>
       </c>
       <c r="N30">
-        <v>0.8590130399999997</v>
+        <v>0.8356742199999997</v>
       </c>
       <c r="O30">
-        <v>0.2748841727999999</v>
+        <v>0.2674157503999999</v>
       </c>
       <c r="P30">
-        <v>0.5841288671999998</v>
+        <v>0.5682584695999997</v>
       </c>
       <c r="Q30">
-        <v>1.1341288672</v>
+        <v>1.1182584696</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.110342081271729</v>
+        <v>0.1110210679926995</v>
       </c>
       <c r="T30">
-        <v>0.841199683484036</v>
+        <v>0.8500491566264581</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.314506780670879</v>
+        <v>2.234696202027056</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0937727182748166</v>
+        <v>0.09366681803398831</v>
       </c>
       <c r="C31">
-        <v>19.41357731021885</v>
+        <v>19.1683293700437</v>
       </c>
       <c r="D31">
-        <v>28.31867731021885</v>
+        <v>28.3813293700437</v>
       </c>
       <c r="E31">
-        <v>-12.1709</v>
+        <v>-11.863</v>
       </c>
       <c r="F31">
-        <v>8.929099999999998</v>
+        <v>9.237</v>
       </c>
       <c r="G31">
         <v>0.024</v>
@@ -3817,28 +3817,28 @@
         <v>1.5125</v>
       </c>
       <c r="M31">
-        <v>0.6768257799999999</v>
+        <v>0.7001646</v>
       </c>
       <c r="N31">
-        <v>0.8356742199999998</v>
+        <v>0.8123353999999997</v>
       </c>
       <c r="O31">
-        <v>0.2674157503999999</v>
+        <v>0.2599473279999999</v>
       </c>
       <c r="P31">
-        <v>0.5682584695999999</v>
+        <v>0.5523880719999998</v>
       </c>
       <c r="Q31">
-        <v>1.1182584696</v>
+        <v>1.102388072</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1110210679926995</v>
+        <v>0.111719454334269</v>
       </c>
       <c r="T31">
-        <v>0.8500491566264581</v>
+        <v>0.8591514718586638</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.234696202027056</v>
+        <v>2.160206328626154</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09366681803398831</v>
+        <v>0.09356091779316004</v>
       </c>
       <c r="C32">
-        <v>19.1683293700437</v>
+        <v>18.92335926658234</v>
       </c>
       <c r="D32">
-        <v>28.3813293700437</v>
+        <v>28.44425926658234</v>
       </c>
       <c r="E32">
-        <v>-11.863</v>
+        <v>-11.5551</v>
       </c>
       <c r="F32">
-        <v>9.237</v>
+        <v>9.5449</v>
       </c>
       <c r="G32">
         <v>0.024</v>
@@ -3899,28 +3899,28 @@
         <v>1.5125</v>
       </c>
       <c r="M32">
-        <v>0.7001646</v>
+        <v>0.7235034200000001</v>
       </c>
       <c r="N32">
-        <v>0.8123353999999997</v>
+        <v>0.7889965799999996</v>
       </c>
       <c r="O32">
-        <v>0.2599473279999999</v>
+        <v>0.2524789055999999</v>
       </c>
       <c r="P32">
-        <v>0.5523880719999998</v>
+        <v>0.5365176743999998</v>
       </c>
       <c r="Q32">
-        <v>1.102388072</v>
+        <v>1.0865176744</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.111719454334269</v>
+        <v>0.112438083758203</v>
       </c>
       <c r="T32">
-        <v>0.8591514718586638</v>
+        <v>0.8685176223149915</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.160206328626154</v>
+        <v>2.090522253509181</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09356091779316004</v>
+        <v>0.09345501755233176</v>
       </c>
       <c r="C33">
-        <v>18.92335926658234</v>
+        <v>18.67866885208307</v>
       </c>
       <c r="D33">
-        <v>28.44425926658234</v>
+        <v>28.50746885208307</v>
       </c>
       <c r="E33">
-        <v>-11.5551</v>
+        <v>-11.2472</v>
       </c>
       <c r="F33">
-        <v>9.5449</v>
+        <v>9.8528</v>
       </c>
       <c r="G33">
         <v>0.024</v>
@@ -3981,28 +3981,28 @@
         <v>1.5125</v>
       </c>
       <c r="M33">
-        <v>0.7235034200000001</v>
+        <v>0.7468422400000001</v>
       </c>
       <c r="N33">
-        <v>0.7889965799999996</v>
+        <v>0.7656577599999996</v>
       </c>
       <c r="O33">
-        <v>0.2524789055999999</v>
+        <v>0.2450104831999999</v>
       </c>
       <c r="P33">
-        <v>0.5365176743999998</v>
+        <v>0.5206472767999998</v>
       </c>
       <c r="Q33">
-        <v>1.0865176744</v>
+        <v>1.070647276799999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.112438083758203</v>
+        <v>0.1131778493416644</v>
       </c>
       <c r="T33">
-        <v>0.8685176223149915</v>
+        <v>0.8781592477847405</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.090522253509181</v>
+        <v>2.025193433087019</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09345501755233176</v>
+        <v>0.09653559731150349</v>
       </c>
       <c r="C34">
-        <v>18.67866885208307</v>
+        <v>16.63984350214078</v>
       </c>
       <c r="D34">
-        <v>28.50746885208307</v>
+        <v>26.77654350214078</v>
       </c>
       <c r="E34">
-        <v>-11.2472</v>
+        <v>-10.9393</v>
       </c>
       <c r="F34">
-        <v>9.8528</v>
+        <v>10.1607</v>
       </c>
       <c r="G34">
         <v>0.024</v>
@@ -4063,45 +4063,45 @@
         <v>1.5125</v>
       </c>
       <c r="M34">
-        <v>0.7468422400000001</v>
+        <v>0.914463</v>
       </c>
       <c r="N34">
-        <v>0.7656577599999996</v>
+        <v>0.5980369999999997</v>
       </c>
       <c r="O34">
-        <v>0.2450104831999999</v>
+        <v>0.1913718399999999</v>
       </c>
       <c r="P34">
-        <v>0.5206472767999998</v>
+        <v>0.4066651599999998</v>
       </c>
       <c r="Q34">
-        <v>1.070647276799999</v>
+        <v>0.9566651599999996</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1131778493416644</v>
+        <v>0.113939697479856</v>
       </c>
       <c r="T34">
-        <v>0.8781592477847405</v>
+        <v>0.8880886829700044</v>
       </c>
       <c r="U34">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V34">
         <v>0.32</v>
       </c>
       <c r="W34">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.025193433087019</v>
+        <v>1.65397615868548</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09653559731150349</v>
+        <v>0.09652625707067521</v>
       </c>
       <c r="C35">
-        <v>16.63984350214078</v>
+        <v>16.33687387507388</v>
       </c>
       <c r="D35">
-        <v>26.77654350214078</v>
+        <v>26.78147387507388</v>
       </c>
       <c r="E35">
-        <v>-10.9393</v>
+        <v>-10.6314</v>
       </c>
       <c r="F35">
-        <v>10.1607</v>
+        <v>10.4686</v>
       </c>
       <c r="G35">
         <v>0.024</v>
@@ -4145,28 +4145,28 @@
         <v>1.5125</v>
       </c>
       <c r="M35">
-        <v>0.914463</v>
+        <v>0.942174</v>
       </c>
       <c r="N35">
-        <v>0.5980369999999997</v>
+        <v>0.5703259999999998</v>
       </c>
       <c r="O35">
-        <v>0.1913718399999999</v>
+        <v>0.1825043199999999</v>
       </c>
       <c r="P35">
-        <v>0.4066651599999998</v>
+        <v>0.3878216799999998</v>
       </c>
       <c r="Q35">
-        <v>0.9566651599999996</v>
+        <v>0.9378216799999997</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.113939697479856</v>
+        <v>0.1147246319252655</v>
       </c>
       <c r="T35">
-        <v>0.8880886829700044</v>
+        <v>0.8983190101305794</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.65397615868548</v>
+        <v>1.605329801077083</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09652625707067521</v>
+        <v>0.09651691682984694</v>
       </c>
       <c r="C36">
-        <v>16.33687387507388</v>
+        <v>16.03390606400344</v>
       </c>
       <c r="D36">
-        <v>26.78147387507388</v>
+        <v>26.78640606400344</v>
       </c>
       <c r="E36">
-        <v>-10.6314</v>
+        <v>-10.3235</v>
       </c>
       <c r="F36">
-        <v>10.4686</v>
+        <v>10.7765</v>
       </c>
       <c r="G36">
         <v>0.024</v>
@@ -4227,28 +4227,28 @@
         <v>1.5125</v>
       </c>
       <c r="M36">
-        <v>0.942174</v>
+        <v>0.969885</v>
       </c>
       <c r="N36">
-        <v>0.5703259999999998</v>
+        <v>0.5426149999999997</v>
       </c>
       <c r="O36">
-        <v>0.1825043199999999</v>
+        <v>0.1736367999999999</v>
       </c>
       <c r="P36">
-        <v>0.3878216799999998</v>
+        <v>0.3689781999999998</v>
       </c>
       <c r="Q36">
-        <v>0.9378216799999997</v>
+        <v>0.9189781999999996</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1147246319252655</v>
+        <v>0.1155337181997645</v>
       </c>
       <c r="T36">
-        <v>0.8983190101305794</v>
+        <v>0.9088641165884028</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.605329801077083</v>
+        <v>1.559463235332024</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09651691682984694</v>
+        <v>0.09650757658901865</v>
       </c>
       <c r="C37">
-        <v>16.03390606400344</v>
+        <v>15.73094006993296</v>
       </c>
       <c r="D37">
-        <v>26.78640606400344</v>
+        <v>26.79134006993296</v>
       </c>
       <c r="E37">
-        <v>-10.3235</v>
+        <v>-10.0156</v>
       </c>
       <c r="F37">
-        <v>10.7765</v>
+        <v>11.0844</v>
       </c>
       <c r="G37">
         <v>0.024</v>
@@ -4309,28 +4309,28 @@
         <v>1.5125</v>
       </c>
       <c r="M37">
-        <v>0.969885</v>
+        <v>0.997596</v>
       </c>
       <c r="N37">
-        <v>0.5426149999999997</v>
+        <v>0.5149039999999997</v>
       </c>
       <c r="O37">
-        <v>0.1736367999999999</v>
+        <v>0.1647692799999999</v>
       </c>
       <c r="P37">
-        <v>0.3689781999999998</v>
+        <v>0.3501347199999998</v>
       </c>
       <c r="Q37">
-        <v>0.9189781999999996</v>
+        <v>0.9001347199999996</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1155337181997645</v>
+        <v>0.1163680884203417</v>
       </c>
       <c r="T37">
-        <v>0.9088641165884028</v>
+        <v>0.9197387576230331</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.559463235332024</v>
+        <v>1.516144812128356</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09650757658901866</v>
+        <v>0.1130286472477169</v>
       </c>
       <c r="C38">
-        <v>15.73094006993296</v>
+        <v>8.839215458593518</v>
       </c>
       <c r="D38">
-        <v>26.79134006993295</v>
+        <v>20.20751545859352</v>
       </c>
       <c r="E38">
-        <v>-10.0156</v>
+        <v>-9.707700000000003</v>
       </c>
       <c r="F38">
-        <v>11.0844</v>
+        <v>11.3923</v>
       </c>
       <c r="G38">
         <v>0.024</v>
@@ -4391,45 +4391,45 @@
         <v>1.5125</v>
       </c>
       <c r="M38">
-        <v>0.9975959999999998</v>
+        <v>1.67238964</v>
       </c>
       <c r="N38">
-        <v>0.5149039999999999</v>
+        <v>-0.1598896400000003</v>
       </c>
       <c r="O38">
-        <v>0.16476928</v>
+        <v>-0.05116468480000009</v>
       </c>
       <c r="P38">
-        <v>0.3501347199999999</v>
+        <v>-0.1087249552000002</v>
       </c>
       <c r="Q38">
-        <v>0.9001347199999997</v>
+        <v>0.4412750447999996</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1163680884203417</v>
+        <v>0.1181460899362916</v>
       </c>
       <c r="T38">
-        <v>0.919738757623033</v>
+        <v>0.9429120777729421</v>
       </c>
       <c r="U38">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.32</v>
+        <v>0.2894062414785109</v>
       </c>
       <c r="W38">
-        <v>0.06119999999999999</v>
+        <v>0.1043151637509546</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>1.516144812128357</v>
+        <v>0.9043945046203465</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1130286472477169</v>
+        <v>0.1140386472477169</v>
       </c>
       <c r="C39">
-        <v>8.839215458593518</v>
+        <v>8.232224086821597</v>
       </c>
       <c r="D39">
-        <v>20.20751545859352</v>
+        <v>19.9084240868216</v>
       </c>
       <c r="E39">
-        <v>-9.707700000000003</v>
+        <v>-9.399800000000001</v>
       </c>
       <c r="F39">
-        <v>11.3923</v>
+        <v>11.7002</v>
       </c>
       <c r="G39">
         <v>0.024</v>
@@ -4473,37 +4473,37 @@
         <v>1.5125</v>
       </c>
       <c r="M39">
-        <v>1.67238964</v>
+        <v>1.71758936</v>
       </c>
       <c r="N39">
-        <v>-0.1598896400000003</v>
+        <v>-0.2050893600000006</v>
       </c>
       <c r="O39">
-        <v>-0.05116468480000009</v>
+        <v>-0.06562859520000018</v>
       </c>
       <c r="P39">
-        <v>-0.1087249552000002</v>
+        <v>-0.1394607648000004</v>
       </c>
       <c r="Q39">
-        <v>0.4412750447999996</v>
+        <v>0.4105392351999995</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1181460899362916</v>
+        <v>0.1193129623546189</v>
       </c>
       <c r="T39">
-        <v>0.9429120777729421</v>
+        <v>0.9581203370918605</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.2894062414785109</v>
+        <v>0.2817902877553922</v>
       </c>
       <c r="W39">
-        <v>0.1043151637509546</v>
+        <v>0.1054331857575084</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.9043945046203465</v>
+        <v>0.8805946492356005</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1140386472477169</v>
+        <v>0.1150486472477169</v>
       </c>
       <c r="C40">
-        <v>8.232224086821597</v>
+        <v>7.633957283615162</v>
       </c>
       <c r="D40">
-        <v>19.9084240868216</v>
+        <v>19.61805728361516</v>
       </c>
       <c r="E40">
-        <v>-9.399800000000001</v>
+        <v>-9.091900000000001</v>
       </c>
       <c r="F40">
-        <v>11.7002</v>
+        <v>12.0081</v>
       </c>
       <c r="G40">
         <v>0.024</v>
@@ -4555,37 +4555,37 @@
         <v>1.5125</v>
       </c>
       <c r="M40">
-        <v>1.71758936</v>
+        <v>1.76278908</v>
       </c>
       <c r="N40">
-        <v>-0.2050893600000006</v>
+        <v>-0.2502890800000006</v>
       </c>
       <c r="O40">
-        <v>-0.06562859520000018</v>
+        <v>-0.0800925056000002</v>
       </c>
       <c r="P40">
-        <v>-0.1394607648000004</v>
+        <v>-0.1701965744000004</v>
       </c>
       <c r="Q40">
-        <v>0.4105392351999995</v>
+        <v>0.3798034255999994</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1193129623546189</v>
+        <v>0.1205180928850225</v>
       </c>
       <c r="T40">
-        <v>0.9581203370918605</v>
+        <v>0.9738272278638582</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.2817902877553922</v>
+        <v>0.2745648957616642</v>
       </c>
       <c r="W40">
-        <v>0.1054331857575084</v>
+        <v>0.1064938733021877</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8805946492356005</v>
+        <v>0.8580152992552004</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1150486472477169</v>
+        <v>0.1160586472477169</v>
       </c>
       <c r="C41">
-        <v>7.633957283615162</v>
+        <v>7.044038790053927</v>
       </c>
       <c r="D41">
-        <v>19.61805728361516</v>
+        <v>19.33603879005393</v>
       </c>
       <c r="E41">
-        <v>-9.091900000000001</v>
+        <v>-8.784000000000001</v>
       </c>
       <c r="F41">
-        <v>12.0081</v>
+        <v>12.316</v>
       </c>
       <c r="G41">
         <v>0.024</v>
@@ -4637,37 +4637,37 @@
         <v>1.5125</v>
       </c>
       <c r="M41">
-        <v>1.76278908</v>
+        <v>1.8079888</v>
       </c>
       <c r="N41">
-        <v>-0.2502890800000006</v>
+        <v>-0.2954888000000004</v>
       </c>
       <c r="O41">
-        <v>-0.0800925056000002</v>
+        <v>-0.09455641600000014</v>
       </c>
       <c r="P41">
-        <v>-0.1701965744000004</v>
+        <v>-0.2009323840000003</v>
       </c>
       <c r="Q41">
-        <v>0.3798034255999994</v>
+        <v>0.3490676159999995</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1205180928850225</v>
+        <v>0.1217633944331062</v>
       </c>
       <c r="T41">
-        <v>0.9738272278638582</v>
+        <v>0.9900576816615891</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.2745648957616642</v>
+        <v>0.2677007733676225</v>
       </c>
       <c r="W41">
-        <v>0.1064938733021877</v>
+        <v>0.107501526469633</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8580152992552004</v>
+        <v>0.8365649167738205</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1160586472477169</v>
+        <v>0.1170686472477169</v>
       </c>
       <c r="C42">
-        <v>7.044038790053927</v>
+        <v>6.462113676176374</v>
       </c>
       <c r="D42">
-        <v>19.33603879005393</v>
+        <v>19.06201367617637</v>
       </c>
       <c r="E42">
-        <v>-8.784000000000001</v>
+        <v>-8.476100000000001</v>
       </c>
       <c r="F42">
-        <v>12.316</v>
+        <v>12.6239</v>
       </c>
       <c r="G42">
         <v>0.024</v>
@@ -4719,37 +4719,37 @@
         <v>1.5125</v>
       </c>
       <c r="M42">
-        <v>1.8079888</v>
+        <v>1.85318852</v>
       </c>
       <c r="N42">
-        <v>-0.2954888000000004</v>
+        <v>-0.3406885200000005</v>
       </c>
       <c r="O42">
-        <v>-0.09455641600000014</v>
+        <v>-0.1090203264000002</v>
       </c>
       <c r="P42">
-        <v>-0.2009323840000003</v>
+        <v>-0.2316681936000003</v>
       </c>
       <c r="Q42">
-        <v>0.3490676159999995</v>
+        <v>0.3183318063999995</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1217633944331062</v>
+        <v>0.1230509095929893</v>
       </c>
       <c r="T42">
-        <v>0.9900576816615891</v>
+        <v>1.00683832033382</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.2677007733676225</v>
+        <v>0.2611714862123147</v>
       </c>
       <c r="W42">
-        <v>0.107501526469633</v>
+        <v>0.1084600258240322</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8365649167738205</v>
+        <v>0.8161608944134834</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1170686472477169</v>
+        <v>0.1422285306358869</v>
       </c>
       <c r="C43">
-        <v>6.462113676176374</v>
+        <v>1.180602255638853</v>
       </c>
       <c r="D43">
-        <v>19.06201367617637</v>
+        <v>14.08840225563885</v>
       </c>
       <c r="E43">
-        <v>-8.476100000000001</v>
+        <v>-8.168200000000001</v>
       </c>
       <c r="F43">
-        <v>12.6239</v>
+        <v>12.9318</v>
       </c>
       <c r="G43">
         <v>0.024</v>
@@ -4801,45 +4801,45 @@
         <v>1.5125</v>
       </c>
       <c r="M43">
-        <v>1.85318852</v>
+        <v>2.59670544</v>
       </c>
       <c r="N43">
-        <v>-0.3406885200000005</v>
+        <v>-1.08420544</v>
       </c>
       <c r="O43">
-        <v>-0.1090203264000002</v>
+        <v>-0.3469457408000001</v>
       </c>
       <c r="P43">
-        <v>-0.2316681936000003</v>
+        <v>-0.7372596992000002</v>
       </c>
       <c r="Q43">
-        <v>0.3183318063999995</v>
+        <v>-0.1872596992000004</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1230509095929893</v>
+        <v>0.1269171035310926</v>
       </c>
       <c r="T43">
-        <v>1.00683832033382</v>
+        <v>1.057227787994896</v>
       </c>
       <c r="U43">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.2611714862123147</v>
+        <v>0.1863900281273335</v>
       </c>
       <c r="W43">
-        <v>0.1084600258240322</v>
+        <v>0.1633728823520314</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.8161608944134834</v>
+        <v>0.5824688378979173</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1422285306358869</v>
+        <v>0.1437785306358869</v>
       </c>
       <c r="C44">
-        <v>1.180602255638854</v>
+        <v>0.6498266587655745</v>
       </c>
       <c r="D44">
-        <v>14.08840225563885</v>
+        <v>13.86552665876557</v>
       </c>
       <c r="E44">
-        <v>-8.168200000000002</v>
+        <v>-7.860300000000002</v>
       </c>
       <c r="F44">
-        <v>12.9318</v>
+        <v>13.2397</v>
       </c>
       <c r="G44">
         <v>0.024</v>
@@ -4883,37 +4883,37 @@
         <v>1.5125</v>
       </c>
       <c r="M44">
-        <v>2.59670544</v>
+        <v>2.65853176</v>
       </c>
       <c r="N44">
-        <v>-1.08420544</v>
+        <v>-1.14603176</v>
       </c>
       <c r="O44">
-        <v>-0.3469457408000001</v>
+        <v>-0.3667301632</v>
       </c>
       <c r="P44">
-        <v>-0.7372596992000002</v>
+        <v>-0.7793015968000001</v>
       </c>
       <c r="Q44">
-        <v>-0.1872596992000004</v>
+        <v>-0.2293015968000003</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1269171035310926</v>
+        <v>0.1283402106105855</v>
       </c>
       <c r="T44">
-        <v>1.057227787994896</v>
+        <v>1.075775643924631</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1863900281273335</v>
+        <v>0.1820553763104188</v>
       </c>
       <c r="W44">
-        <v>0.1633728823520314</v>
+        <v>0.1642432804368679</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5824688378979173</v>
+        <v>0.5689230509700587</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1437785306358869</v>
+        <v>0.1453285306358869</v>
       </c>
       <c r="C45">
-        <v>0.6498266587655745</v>
+        <v>0.125992934196578</v>
       </c>
       <c r="D45">
-        <v>13.86552665876557</v>
+        <v>13.64959293419658</v>
       </c>
       <c r="E45">
-        <v>-7.860300000000002</v>
+        <v>-7.552400000000002</v>
       </c>
       <c r="F45">
-        <v>13.2397</v>
+        <v>13.5476</v>
       </c>
       <c r="G45">
         <v>0.024</v>
@@ -4965,37 +4965,37 @@
         <v>1.5125</v>
       </c>
       <c r="M45">
-        <v>2.65853176</v>
+        <v>2.72035808</v>
       </c>
       <c r="N45">
-        <v>-1.14603176</v>
+        <v>-1.20785808</v>
       </c>
       <c r="O45">
-        <v>-0.3667301632</v>
+        <v>-0.3865145856000001</v>
       </c>
       <c r="P45">
-        <v>-0.7793015968000001</v>
+        <v>-0.8213434944000002</v>
       </c>
       <c r="Q45">
-        <v>-0.2293015968000003</v>
+        <v>-0.2713434944000004</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1283402106105855</v>
+        <v>0.1298141429429173</v>
       </c>
       <c r="T45">
-        <v>1.075775643924631</v>
+        <v>1.094985923280428</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1820553763104188</v>
+        <v>0.1779177541215456</v>
       </c>
       <c r="W45">
-        <v>0.1642432804368679</v>
+        <v>0.1650741149723936</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5689230509700587</v>
+        <v>0.55599298162983</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1453285306358869</v>
+        <v>0.1468785306358869</v>
       </c>
       <c r="C46">
-        <v>0.125992934196578</v>
+        <v>-0.3912182708130967</v>
       </c>
       <c r="D46">
-        <v>13.64959293419658</v>
+        <v>13.4402817291869</v>
       </c>
       <c r="E46">
-        <v>-7.552400000000002</v>
+        <v>-7.244500000000002</v>
       </c>
       <c r="F46">
-        <v>13.5476</v>
+        <v>13.8555</v>
       </c>
       <c r="G46">
         <v>0.024</v>
@@ -5047,37 +5047,37 @@
         <v>1.5125</v>
       </c>
       <c r="M46">
-        <v>2.72035808</v>
+        <v>2.7821844</v>
       </c>
       <c r="N46">
-        <v>-1.20785808</v>
+        <v>-1.2696844</v>
       </c>
       <c r="O46">
-        <v>-0.3865145856000001</v>
+        <v>-0.406299008</v>
       </c>
       <c r="P46">
-        <v>-0.8213434944000002</v>
+        <v>-0.8633853920000001</v>
       </c>
       <c r="Q46">
-        <v>-0.2713434944000004</v>
+        <v>-0.3133853920000003</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1298141429429173</v>
+        <v>0.1313416728146068</v>
       </c>
       <c r="T46">
-        <v>1.094985923280428</v>
+        <v>1.114894758249163</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1779177541215456</v>
+        <v>0.173964026252178</v>
       </c>
       <c r="W46">
-        <v>0.1650741149723936</v>
+        <v>0.1658680235285627</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.55599298162983</v>
+        <v>0.5436375820380561</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1468785306358869</v>
+        <v>0.1484285306358869</v>
       </c>
       <c r="C47">
-        <v>-0.3912182708130967</v>
+        <v>-0.9021070162541722</v>
       </c>
       <c r="D47">
-        <v>13.4402817291869</v>
+        <v>13.23729298374583</v>
       </c>
       <c r="E47">
-        <v>-7.244500000000002</v>
+        <v>-6.9366</v>
       </c>
       <c r="F47">
-        <v>13.8555</v>
+        <v>14.1634</v>
       </c>
       <c r="G47">
         <v>0.024</v>
@@ -5129,37 +5129,37 @@
         <v>1.5125</v>
       </c>
       <c r="M47">
-        <v>2.7821844</v>
+        <v>2.84401072</v>
       </c>
       <c r="N47">
-        <v>-1.2696844</v>
+        <v>-1.331510720000001</v>
       </c>
       <c r="O47">
-        <v>-0.406299008</v>
+        <v>-0.4260834304000002</v>
       </c>
       <c r="P47">
-        <v>-0.8633853920000001</v>
+        <v>-0.9054272896000004</v>
       </c>
       <c r="Q47">
-        <v>-0.3133853920000003</v>
+        <v>-0.3554272896000006</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1313416728146068</v>
+        <v>0.1329257778667291</v>
       </c>
       <c r="T47">
-        <v>1.114894758249163</v>
+        <v>1.135540957476</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.173964026252178</v>
+        <v>0.1701821995945219</v>
       </c>
       <c r="W47">
-        <v>0.1658680235285627</v>
+        <v>0.16662741432142</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5436375820380561</v>
+        <v>0.5318193737328809</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1484285306358869</v>
+        <v>0.149978530635887</v>
       </c>
       <c r="C48">
-        <v>-0.9021070162541722</v>
+        <v>-1.406955504580603</v>
       </c>
       <c r="D48">
-        <v>13.23729298374583</v>
+        <v>13.0403444954194</v>
       </c>
       <c r="E48">
-        <v>-6.9366</v>
+        <v>-6.6287</v>
       </c>
       <c r="F48">
-        <v>14.1634</v>
+        <v>14.4713</v>
       </c>
       <c r="G48">
         <v>0.024</v>
@@ -5211,37 +5211,37 @@
         <v>1.5125</v>
       </c>
       <c r="M48">
-        <v>2.84401072</v>
+        <v>2.90583704</v>
       </c>
       <c r="N48">
-        <v>-1.331510720000001</v>
+        <v>-1.39333704</v>
       </c>
       <c r="O48">
-        <v>-0.4260834304000002</v>
+        <v>-0.4458678528000002</v>
       </c>
       <c r="P48">
-        <v>-0.9054272896000004</v>
+        <v>-0.9474691872000003</v>
       </c>
       <c r="Q48">
-        <v>-0.3554272896000006</v>
+        <v>-0.3974691872000005</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1329257778667291</v>
+        <v>0.1345696604679882</v>
       </c>
       <c r="T48">
-        <v>1.135540957476</v>
+        <v>1.156966258560453</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1701821995945219</v>
+        <v>0.1665613017308087</v>
       </c>
       <c r="W48">
-        <v>0.16662741432142</v>
+        <v>0.1673544906124536</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5318193737328809</v>
+        <v>0.520504067908777</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.149978530635887</v>
+        <v>0.1515285306358869</v>
       </c>
       <c r="C49">
-        <v>-1.406955504580603</v>
+        <v>-1.906029389683658</v>
       </c>
       <c r="D49">
-        <v>13.0403444954194</v>
+        <v>12.84917061031634</v>
       </c>
       <c r="E49">
-        <v>-6.6287</v>
+        <v>-6.3208</v>
       </c>
       <c r="F49">
-        <v>14.4713</v>
+        <v>14.7792</v>
       </c>
       <c r="G49">
         <v>0.024</v>
@@ -5293,37 +5293,37 @@
         <v>1.5125</v>
       </c>
       <c r="M49">
-        <v>2.90583704</v>
+        <v>2.96766336</v>
       </c>
       <c r="N49">
-        <v>-1.39333704</v>
+        <v>-1.455163360000001</v>
       </c>
       <c r="O49">
-        <v>-0.4458678528000002</v>
+        <v>-0.4656522752000002</v>
       </c>
       <c r="P49">
-        <v>-0.9474691872000003</v>
+        <v>-0.9895110848000004</v>
       </c>
       <c r="Q49">
-        <v>-0.3974691872000005</v>
+        <v>-0.4395110848000006</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1345696604679882</v>
+        <v>0.1362767693231418</v>
       </c>
       <c r="T49">
-        <v>1.156966258560453</v>
+        <v>1.179215609686615</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1665613017308087</v>
+        <v>0.1630912746114168</v>
       </c>
       <c r="W49">
-        <v>0.1673544906124536</v>
+        <v>0.1680512720580275</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.520504067908777</v>
+        <v>0.5096602331606774</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1515285306358869</v>
+        <v>0.170821646337236</v>
       </c>
       <c r="C50">
-        <v>-1.906029389683653</v>
+        <v>-4.196790298285951</v>
       </c>
       <c r="D50">
-        <v>12.84917061031635</v>
+        <v>10.86630970171405</v>
       </c>
       <c r="E50">
-        <v>-6.320800000000002</v>
+        <v>-6.012900000000002</v>
       </c>
       <c r="F50">
-        <v>14.7792</v>
+        <v>15.0871</v>
       </c>
       <c r="G50">
         <v>0.024</v>
@@ -5375,45 +5375,45 @@
         <v>1.5125</v>
       </c>
       <c r="M50">
-        <v>2.96766336</v>
+        <v>3.55753818</v>
       </c>
       <c r="N50">
-        <v>-1.45516336</v>
+        <v>-2.04503818</v>
       </c>
       <c r="O50">
-        <v>-0.4656522752000001</v>
+        <v>-0.6544122176</v>
       </c>
       <c r="P50">
-        <v>-0.9895110848000002</v>
+        <v>-1.3906259624</v>
       </c>
       <c r="Q50">
-        <v>-0.4395110848000003</v>
+        <v>-0.8406259624000003</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1362767693231418</v>
+        <v>0.139213795587025</v>
       </c>
       <c r="T50">
-        <v>1.179215609686615</v>
+        <v>1.217494907702452</v>
       </c>
       <c r="U50">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1630912746114168</v>
+        <v>0.1360491372154437</v>
       </c>
       <c r="W50">
-        <v>0.1680512720580275</v>
+        <v>0.2037196134445984</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.5096602331606775</v>
+        <v>0.4251535537982616</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.170821646337236</v>
+        <v>0.172721646337236</v>
       </c>
       <c r="C51">
-        <v>-4.196790298285951</v>
+        <v>-4.6673574951674</v>
       </c>
       <c r="D51">
-        <v>10.86630970171405</v>
+        <v>10.7036425048326</v>
       </c>
       <c r="E51">
-        <v>-6.012900000000002</v>
+        <v>-5.705000000000002</v>
       </c>
       <c r="F51">
-        <v>15.0871</v>
+        <v>15.395</v>
       </c>
       <c r="G51">
         <v>0.024</v>
@@ -5457,37 +5457,37 @@
         <v>1.5125</v>
       </c>
       <c r="M51">
-        <v>3.55753818</v>
+        <v>3.630141</v>
       </c>
       <c r="N51">
-        <v>-2.04503818</v>
+        <v>-2.117641</v>
       </c>
       <c r="O51">
-        <v>-0.6544122176</v>
+        <v>-0.6776451200000001</v>
       </c>
       <c r="P51">
-        <v>-1.3906259624</v>
+        <v>-1.43999588</v>
       </c>
       <c r="Q51">
-        <v>-0.8406259624000003</v>
+        <v>-0.8899958800000003</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.139213795587025</v>
+        <v>0.1410820714987655</v>
       </c>
       <c r="T51">
-        <v>1.217494907702452</v>
+        <v>1.241844805856501</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1360491372154437</v>
+        <v>0.1333281544711348</v>
       </c>
       <c r="W51">
-        <v>0.2037196134445984</v>
+        <v>0.2043612211757064</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4251535537982616</v>
+        <v>0.4166504827222964</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.172721646337236</v>
+        <v>0.174621646337236</v>
       </c>
       <c r="C52">
-        <v>-4.6673574951674</v>
+        <v>-5.133126310986931</v>
       </c>
       <c r="D52">
-        <v>10.7036425048326</v>
+        <v>10.54577368901307</v>
       </c>
       <c r="E52">
-        <v>-5.705000000000002</v>
+        <v>-5.397100000000002</v>
       </c>
       <c r="F52">
-        <v>15.395</v>
+        <v>15.7029</v>
       </c>
       <c r="G52">
         <v>0.024</v>
@@ -5539,37 +5539,37 @@
         <v>1.5125</v>
       </c>
       <c r="M52">
-        <v>3.630141</v>
+        <v>3.70274382</v>
       </c>
       <c r="N52">
-        <v>-2.117641</v>
+        <v>-2.190243820000001</v>
       </c>
       <c r="O52">
-        <v>-0.6776451200000001</v>
+        <v>-0.7008780224000002</v>
       </c>
       <c r="P52">
-        <v>-1.43999588</v>
+        <v>-1.4893657976</v>
       </c>
       <c r="Q52">
-        <v>-0.8899958800000003</v>
+        <v>-0.9393657976000005</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1410820714987655</v>
+        <v>0.1430266035701689</v>
       </c>
       <c r="T52">
-        <v>1.241844805856501</v>
+        <v>1.267188577404593</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1333281544711348</v>
+        <v>0.1307138769324851</v>
       </c>
       <c r="W52">
-        <v>0.2043612211757064</v>
+        <v>0.20497766781932</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4166504827222964</v>
+        <v>0.4084808654140161</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.174621646337236</v>
+        <v>0.176521646337236</v>
       </c>
       <c r="C53">
-        <v>-5.133126310986931</v>
+        <v>-5.594305974841788</v>
       </c>
       <c r="D53">
-        <v>10.54577368901307</v>
+        <v>10.39249402515821</v>
       </c>
       <c r="E53">
-        <v>-5.397100000000002</v>
+        <v>-5.089200000000002</v>
       </c>
       <c r="F53">
-        <v>15.7029</v>
+        <v>16.0108</v>
       </c>
       <c r="G53">
         <v>0.024</v>
@@ -5621,37 +5621,37 @@
         <v>1.5125</v>
       </c>
       <c r="M53">
-        <v>3.70274382</v>
+        <v>3.77534664</v>
       </c>
       <c r="N53">
-        <v>-2.190243820000001</v>
+        <v>-2.26284664</v>
       </c>
       <c r="O53">
-        <v>-0.7008780224000002</v>
+        <v>-0.7241109248000001</v>
       </c>
       <c r="P53">
-        <v>-1.4893657976</v>
+        <v>-1.5387357152</v>
       </c>
       <c r="Q53">
-        <v>-0.9393657976000005</v>
+        <v>-0.9887357152000003</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1430266035701689</v>
+        <v>0.1450521578112141</v>
       </c>
       <c r="T53">
-        <v>1.267188577404593</v>
+        <v>1.293588339433855</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1307138769324851</v>
+        <v>0.1282001485299374</v>
       </c>
       <c r="W53">
-        <v>0.20497766781932</v>
+        <v>0.2055704049766408</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4084808654140161</v>
+        <v>0.4006254641560543</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.176521646337236</v>
+        <v>0.178421646337236</v>
       </c>
       <c r="C54">
-        <v>-5.594305974841788</v>
+        <v>-6.051093725771905</v>
       </c>
       <c r="D54">
-        <v>10.39249402515821</v>
+        <v>10.2436062742281</v>
       </c>
       <c r="E54">
-        <v>-5.089200000000002</v>
+        <v>-4.781300000000002</v>
       </c>
       <c r="F54">
-        <v>16.0108</v>
+        <v>16.3187</v>
       </c>
       <c r="G54">
         <v>0.024</v>
@@ -5703,37 +5703,37 @@
         <v>1.5125</v>
       </c>
       <c r="M54">
-        <v>3.77534664</v>
+        <v>3.84794946</v>
       </c>
       <c r="N54">
-        <v>-2.26284664</v>
+        <v>-2.33544946</v>
       </c>
       <c r="O54">
-        <v>-0.7241109248000001</v>
+        <v>-0.7473438272000001</v>
       </c>
       <c r="P54">
-        <v>-1.5387357152</v>
+        <v>-1.5881056328</v>
       </c>
       <c r="Q54">
-        <v>-0.9887357152000003</v>
+        <v>-1.0381056328</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1450521578112141</v>
+        <v>0.1471639058497505</v>
       </c>
       <c r="T54">
-        <v>1.293588339433855</v>
+        <v>1.321111495592022</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1282001485299374</v>
+        <v>0.1257812778029574</v>
       </c>
       <c r="W54">
-        <v>0.2055704049766408</v>
+        <v>0.2061407746940626</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4006254641560543</v>
+        <v>0.3930664931342419</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.178421646337236</v>
+        <v>0.180321646337236</v>
       </c>
       <c r="C55">
-        <v>-6.051093725771905</v>
+        <v>-6.503675659505021</v>
       </c>
       <c r="D55">
-        <v>10.2436062742281</v>
+        <v>10.09892434049498</v>
       </c>
       <c r="E55">
-        <v>-4.781300000000002</v>
+        <v>-4.473400000000002</v>
       </c>
       <c r="F55">
-        <v>16.3187</v>
+        <v>16.6266</v>
       </c>
       <c r="G55">
         <v>0.024</v>
@@ -5785,37 +5785,37 @@
         <v>1.5125</v>
       </c>
       <c r="M55">
-        <v>3.84794946</v>
+        <v>3.92055228</v>
       </c>
       <c r="N55">
-        <v>-2.33544946</v>
+        <v>-2.408052280000001</v>
       </c>
       <c r="O55">
-        <v>-0.7473438272000001</v>
+        <v>-0.7705767296000002</v>
       </c>
       <c r="P55">
-        <v>-1.5881056328</v>
+        <v>-1.6374755504</v>
       </c>
       <c r="Q55">
-        <v>-1.0381056328</v>
+        <v>-1.087475550400001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1471639058497505</v>
+        <v>0.1493674690203973</v>
       </c>
       <c r="T55">
-        <v>1.321111495592022</v>
+        <v>1.349831310713588</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1257812778029574</v>
+        <v>0.1234519948806804</v>
       </c>
       <c r="W55">
-        <v>0.2061407746940626</v>
+        <v>0.2066900196071356</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3930664931342419</v>
+        <v>0.3857874840021263</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.180321646337236</v>
+        <v>0.1822216463372359</v>
       </c>
       <c r="C56">
-        <v>-6.503675659505021</v>
+        <v>-6.952227504443963</v>
       </c>
       <c r="D56">
-        <v>10.09892434049498</v>
+        <v>9.958272495556038</v>
       </c>
       <c r="E56">
-        <v>-4.473400000000002</v>
+        <v>-4.165500000000002</v>
       </c>
       <c r="F56">
-        <v>16.6266</v>
+        <v>16.9345</v>
       </c>
       <c r="G56">
         <v>0.024</v>
@@ -5867,37 +5867,37 @@
         <v>1.5125</v>
       </c>
       <c r="M56">
-        <v>3.92055228</v>
+        <v>3.9931551</v>
       </c>
       <c r="N56">
-        <v>-2.408052280000001</v>
+        <v>-2.4806551</v>
       </c>
       <c r="O56">
-        <v>-0.7705767296000002</v>
+        <v>-0.7938096320000001</v>
       </c>
       <c r="P56">
-        <v>-1.6374755504</v>
+        <v>-1.686845468</v>
       </c>
       <c r="Q56">
-        <v>-1.087475550400001</v>
+        <v>-1.136845468</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1493674690203973</v>
+        <v>0.1516689683319617</v>
       </c>
       <c r="T56">
-        <v>1.349831310713588</v>
+        <v>1.379827562062779</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1234519948806804</v>
+        <v>0.1212074131555771</v>
       </c>
       <c r="W56">
-        <v>0.2066900196071356</v>
+        <v>0.2072192919779149</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3857874840021263</v>
+        <v>0.3787731661111785</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1822216463372359</v>
+        <v>0.184121646337236</v>
       </c>
       <c r="C57">
-        <v>-6.952227504443963</v>
+        <v>-7.396915333699747</v>
       </c>
       <c r="D57">
-        <v>9.958272495556038</v>
+        <v>9.821484666300254</v>
       </c>
       <c r="E57">
-        <v>-4.165500000000002</v>
+        <v>-3.857600000000001</v>
       </c>
       <c r="F57">
-        <v>16.9345</v>
+        <v>17.2424</v>
       </c>
       <c r="G57">
         <v>0.024</v>
@@ -5949,37 +5949,37 @@
         <v>1.5125</v>
       </c>
       <c r="M57">
-        <v>3.9931551</v>
+        <v>4.06575792</v>
       </c>
       <c r="N57">
-        <v>-2.4806551</v>
+        <v>-2.553257920000001</v>
       </c>
       <c r="O57">
-        <v>-0.7938096320000001</v>
+        <v>-0.8170425344000002</v>
       </c>
       <c r="P57">
-        <v>-1.686845468</v>
+        <v>-1.7362153856</v>
       </c>
       <c r="Q57">
-        <v>-1.136845468</v>
+        <v>-1.186215385600001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1516689683319617</v>
+        <v>0.1540750812485972</v>
       </c>
       <c r="T57">
-        <v>1.379827562062779</v>
+        <v>1.411187279382388</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1212074131555771</v>
+        <v>0.1190429950635132</v>
       </c>
       <c r="W57">
-        <v>0.2072192919779149</v>
+        <v>0.2077296617640236</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3787731661111785</v>
+        <v>0.3720093595734789</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.184121646337236</v>
+        <v>0.186021646337236</v>
       </c>
       <c r="C58">
-        <v>-7.396915333699747</v>
+        <v>-7.837896219236427</v>
       </c>
       <c r="D58">
-        <v>9.821484666300254</v>
+        <v>9.688403780763574</v>
       </c>
       <c r="E58">
-        <v>-3.857600000000001</v>
+        <v>-3.549700000000001</v>
       </c>
       <c r="F58">
-        <v>17.2424</v>
+        <v>17.5503</v>
       </c>
       <c r="G58">
         <v>0.024</v>
@@ -6031,37 +6031,37 @@
         <v>1.5125</v>
       </c>
       <c r="M58">
-        <v>4.06575792</v>
+        <v>4.13836074</v>
       </c>
       <c r="N58">
-        <v>-2.553257920000001</v>
+        <v>-2.625860740000001</v>
       </c>
       <c r="O58">
-        <v>-0.8170425344000002</v>
+        <v>-0.8402754368000003</v>
       </c>
       <c r="P58">
-        <v>-1.7362153856</v>
+        <v>-1.7855853032</v>
       </c>
       <c r="Q58">
-        <v>-1.186215385600001</v>
+        <v>-1.235585303200001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1540750812485972</v>
+        <v>0.1565931063939134</v>
       </c>
       <c r="T58">
-        <v>1.411187279382388</v>
+        <v>1.444005588205234</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1190429950635132</v>
+        <v>0.1169545214659077</v>
       </c>
       <c r="W58">
-        <v>0.2077296617640236</v>
+        <v>0.208222123838339</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3720093595734789</v>
+        <v>0.3654828795809617</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.186021646337236</v>
+        <v>0.187921646337236</v>
       </c>
       <c r="C59">
-        <v>-7.837896219236427</v>
+        <v>-8.275318833545095</v>
       </c>
       <c r="D59">
-        <v>9.688403780763574</v>
+        <v>9.558881166454906</v>
       </c>
       <c r="E59">
-        <v>-3.549700000000001</v>
+        <v>-3.241800000000001</v>
       </c>
       <c r="F59">
-        <v>17.5503</v>
+        <v>17.8582</v>
       </c>
       <c r="G59">
         <v>0.024</v>
@@ -6113,37 +6113,37 @@
         <v>1.5125</v>
       </c>
       <c r="M59">
-        <v>4.13836074</v>
+        <v>4.210963560000001</v>
       </c>
       <c r="N59">
-        <v>-2.625860740000001</v>
+        <v>-2.698463560000001</v>
       </c>
       <c r="O59">
-        <v>-0.8402754368000003</v>
+        <v>-0.8635083392000003</v>
       </c>
       <c r="P59">
-        <v>-1.7855853032</v>
+        <v>-1.834955220800001</v>
       </c>
       <c r="Q59">
-        <v>-1.235585303200001</v>
+        <v>-1.284955220800001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1565931063939134</v>
+        <v>0.1592310374985304</v>
       </c>
       <c r="T59">
-        <v>1.444005588205234</v>
+        <v>1.478386673638692</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1169545214659077</v>
+        <v>0.1149380641992542</v>
       </c>
       <c r="W59">
-        <v>0.208222123838339</v>
+        <v>0.2086976044618159</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3654828795809617</v>
+        <v>0.3591814506226693</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.187921646337236</v>
+        <v>0.189821646337236</v>
       </c>
       <c r="C60">
-        <v>-8.275318833545091</v>
+        <v>-8.709324003692485</v>
       </c>
       <c r="D60">
-        <v>9.558881166454906</v>
+        <v>9.432775996307516</v>
       </c>
       <c r="E60">
-        <v>-3.241800000000005</v>
+        <v>-2.933900000000001</v>
       </c>
       <c r="F60">
-        <v>17.8582</v>
+        <v>18.1661</v>
       </c>
       <c r="G60">
         <v>0.024</v>
@@ -6195,37 +6195,37 @@
         <v>1.5125</v>
       </c>
       <c r="M60">
-        <v>4.21096356</v>
+        <v>4.28356638</v>
       </c>
       <c r="N60">
-        <v>-2.69846356</v>
+        <v>-2.77106638</v>
       </c>
       <c r="O60">
-        <v>-0.8635083392</v>
+        <v>-0.8867412416000001</v>
       </c>
       <c r="P60">
-        <v>-1.8349552208</v>
+        <v>-1.8843251384</v>
       </c>
       <c r="Q60">
-        <v>-1.2849552208</v>
+        <v>-1.3343251384</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1592310374985303</v>
+        <v>0.1619976481692262</v>
       </c>
       <c r="T60">
-        <v>1.478386673638692</v>
+        <v>1.514444885190855</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1149380641992542</v>
+        <v>0.112989961416216</v>
       </c>
       <c r="W60">
-        <v>0.2086976044618159</v>
+        <v>0.2091569670980563</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3591814506226694</v>
+        <v>0.3530936294256749</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.189821646337236</v>
+        <v>0.191721646337236</v>
       </c>
       <c r="C61">
-        <v>-8.709324003692485</v>
+        <v>-9.140045222085025</v>
       </c>
       <c r="D61">
-        <v>9.432775996307516</v>
+        <v>9.309954777914976</v>
       </c>
       <c r="E61">
-        <v>-2.933900000000001</v>
+        <v>-2.626000000000001</v>
       </c>
       <c r="F61">
-        <v>18.1661</v>
+        <v>18.474</v>
       </c>
       <c r="G61">
         <v>0.024</v>
@@ -6277,37 +6277,37 @@
         <v>1.5125</v>
       </c>
       <c r="M61">
-        <v>4.28356638</v>
+        <v>4.3561692</v>
       </c>
       <c r="N61">
-        <v>-2.77106638</v>
+        <v>-2.8436692</v>
       </c>
       <c r="O61">
-        <v>-0.8867412416000001</v>
+        <v>-0.9099741440000001</v>
       </c>
       <c r="P61">
-        <v>-1.8843251384</v>
+        <v>-1.933695056</v>
       </c>
       <c r="Q61">
-        <v>-1.3343251384</v>
+        <v>-1.383695056000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1619976481692262</v>
+        <v>0.1649025893734569</v>
       </c>
       <c r="T61">
-        <v>1.514444885190855</v>
+        <v>1.552306007320627</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.112989961416216</v>
+        <v>0.1111067953926124</v>
       </c>
       <c r="W61">
-        <v>0.2091569670980563</v>
+        <v>0.209601017646422</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3530936294256749</v>
+        <v>0.3472087356019137</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.191721646337236</v>
+        <v>0.193621646337236</v>
       </c>
       <c r="C62">
-        <v>-9.140045222085025</v>
+        <v>-9.567609117842776</v>
       </c>
       <c r="D62">
-        <v>9.309954777914976</v>
+        <v>9.190290882157225</v>
       </c>
       <c r="E62">
-        <v>-2.626000000000001</v>
+        <v>-2.318100000000001</v>
       </c>
       <c r="F62">
-        <v>18.474</v>
+        <v>18.7819</v>
       </c>
       <c r="G62">
         <v>0.024</v>
@@ -6359,37 +6359,37 @@
         <v>1.5125</v>
       </c>
       <c r="M62">
-        <v>4.3561692</v>
+        <v>4.42877202</v>
       </c>
       <c r="N62">
-        <v>-2.8436692</v>
+        <v>-2.916272020000001</v>
       </c>
       <c r="O62">
-        <v>-0.9099741440000001</v>
+        <v>-0.9332070464000002</v>
       </c>
       <c r="P62">
-        <v>-1.933695056</v>
+        <v>-1.9830649736</v>
       </c>
       <c r="Q62">
-        <v>-1.383695056000001</v>
+        <v>-1.433064973600001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1649025893734569</v>
+        <v>0.1679565019214943</v>
       </c>
       <c r="T62">
-        <v>1.552306007320627</v>
+        <v>1.592108725457053</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1111067953926124</v>
+        <v>0.1092853725173236</v>
       </c>
       <c r="W62">
-        <v>0.209601017646422</v>
+        <v>0.2100305091604151</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3472087356019137</v>
+        <v>0.3415167891166364</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.193621646337236</v>
+        <v>0.195521646337236</v>
       </c>
       <c r="C63">
-        <v>-9.567609117842776</v>
+        <v>-9.992135892282377</v>
       </c>
       <c r="D63">
-        <v>9.190290882157225</v>
+        <v>9.073664107717624</v>
       </c>
       <c r="E63">
-        <v>-2.318100000000001</v>
+        <v>-2.010200000000001</v>
       </c>
       <c r="F63">
-        <v>18.7819</v>
+        <v>19.0898</v>
       </c>
       <c r="G63">
         <v>0.024</v>
@@ -6441,37 +6441,37 @@
         <v>1.5125</v>
       </c>
       <c r="M63">
-        <v>4.42877202</v>
+        <v>4.50137484</v>
       </c>
       <c r="N63">
-        <v>-2.916272020000001</v>
+        <v>-2.988874840000001</v>
       </c>
       <c r="O63">
-        <v>-0.9332070464000002</v>
+        <v>-0.9564399488000003</v>
       </c>
       <c r="P63">
-        <v>-1.9830649736</v>
+        <v>-2.0324348912</v>
       </c>
       <c r="Q63">
-        <v>-1.433064973600001</v>
+        <v>-1.4824348912</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1679565019214943</v>
+        <v>0.171171146708902</v>
       </c>
       <c r="T63">
-        <v>1.592108725457053</v>
+        <v>1.634006323495396</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1092853725173236</v>
+        <v>0.1075227052186571</v>
       </c>
       <c r="W63">
-        <v>0.2100305091604151</v>
+        <v>0.2104461461094407</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3415167891166364</v>
+        <v>0.3360084538083035</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.195521646337236</v>
+        <v>0.197421646337236</v>
       </c>
       <c r="C64">
-        <v>-9.992135892282377</v>
+        <v>-10.41373972165723</v>
       </c>
       <c r="D64">
-        <v>9.073664107717624</v>
+        <v>8.959960278342772</v>
       </c>
       <c r="E64">
-        <v>-2.010200000000001</v>
+        <v>-1.702300000000001</v>
       </c>
       <c r="F64">
-        <v>19.0898</v>
+        <v>19.3977</v>
       </c>
       <c r="G64">
         <v>0.024</v>
@@ -6523,37 +6523,37 @@
         <v>1.5125</v>
       </c>
       <c r="M64">
-        <v>4.50137484</v>
+        <v>4.573977660000001</v>
       </c>
       <c r="N64">
-        <v>-2.988874840000001</v>
+        <v>-3.061477660000001</v>
       </c>
       <c r="O64">
-        <v>-0.9564399488000003</v>
+        <v>-0.9796728512000002</v>
       </c>
       <c r="P64">
-        <v>-2.0324348912</v>
+        <v>-2.081804808800001</v>
       </c>
       <c r="Q64">
-        <v>-1.4824348912</v>
+        <v>-1.531804808800001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.171171146708902</v>
+        <v>0.1745595560794129</v>
       </c>
       <c r="T64">
-        <v>1.634006323495396</v>
+        <v>1.67816865656284</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1075227052186571</v>
+        <v>0.1058159956120118</v>
       </c>
       <c r="W64">
-        <v>0.2104461461094407</v>
+        <v>0.2108485882346876</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3360084538083035</v>
+        <v>0.3306749862875368</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.197421646337236</v>
+        <v>0.199321646337236</v>
       </c>
       <c r="C65">
-        <v>-10.41373972165723</v>
+        <v>-10.83252912999158</v>
       </c>
       <c r="D65">
-        <v>8.959960278342772</v>
+        <v>8.84907087000842</v>
       </c>
       <c r="E65">
-        <v>-1.702300000000001</v>
+        <v>-1.394400000000001</v>
       </c>
       <c r="F65">
-        <v>19.3977</v>
+        <v>19.7056</v>
       </c>
       <c r="G65">
         <v>0.024</v>
@@ -6605,37 +6605,37 @@
         <v>1.5125</v>
       </c>
       <c r="M65">
-        <v>4.573977660000001</v>
+        <v>4.64658048</v>
       </c>
       <c r="N65">
-        <v>-3.061477660000001</v>
+        <v>-3.13408048</v>
       </c>
       <c r="O65">
-        <v>-0.9796728512000002</v>
+        <v>-1.0029057536</v>
       </c>
       <c r="P65">
-        <v>-2.081804808800001</v>
+        <v>-2.1311747264</v>
       </c>
       <c r="Q65">
-        <v>-1.531804808800001</v>
+        <v>-1.5811747264</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1745595560794129</v>
+        <v>0.1781362104149521</v>
       </c>
       <c r="T65">
-        <v>1.67816865656284</v>
+        <v>1.724784452578474</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1058159956120118</v>
+        <v>0.1041626206805741</v>
       </c>
       <c r="W65">
-        <v>0.2108485882346876</v>
+        <v>0.2112384540435206</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3306749862875368</v>
+        <v>0.3255081896267941</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.199321646337236</v>
+        <v>0.201221646337236</v>
       </c>
       <c r="C66">
-        <v>-10.83252912999158</v>
+        <v>-11.24860733456763</v>
       </c>
       <c r="D66">
-        <v>8.84907087000842</v>
+        <v>8.740892665432369</v>
       </c>
       <c r="E66">
-        <v>-1.394400000000001</v>
+        <v>-1.086500000000001</v>
       </c>
       <c r="F66">
-        <v>19.7056</v>
+        <v>20.0135</v>
       </c>
       <c r="G66">
         <v>0.024</v>
@@ -6687,37 +6687,37 @@
         <v>1.5125</v>
       </c>
       <c r="M66">
-        <v>4.64658048</v>
+        <v>4.7191833</v>
       </c>
       <c r="N66">
-        <v>-3.13408048</v>
+        <v>-3.2066833</v>
       </c>
       <c r="O66">
-        <v>-1.0029057536</v>
+        <v>-1.026138656</v>
       </c>
       <c r="P66">
-        <v>-2.1311747264</v>
+        <v>-2.180544644</v>
       </c>
       <c r="Q66">
-        <v>-1.5811747264</v>
+        <v>-1.630544644</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1781362104149521</v>
+        <v>0.1819172449982364</v>
       </c>
       <c r="T66">
-        <v>1.724784452578474</v>
+        <v>1.77406400836643</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1041626206805741</v>
+        <v>0.1025601188239499</v>
       </c>
       <c r="W66">
-        <v>0.2112384540435206</v>
+        <v>0.2116163239813126</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3255081896267941</v>
+        <v>0.3205003713248433</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.201221646337236</v>
+        <v>0.203121646337236</v>
       </c>
       <c r="C67">
-        <v>-11.24860733456763</v>
+        <v>-11.66207256637763</v>
       </c>
       <c r="D67">
-        <v>8.740892665432369</v>
+        <v>8.635327433622368</v>
       </c>
       <c r="E67">
-        <v>-1.086500000000001</v>
+        <v>-0.7786000000000008</v>
       </c>
       <c r="F67">
-        <v>20.0135</v>
+        <v>20.3214</v>
       </c>
       <c r="G67">
         <v>0.024</v>
@@ -6769,37 +6769,37 @@
         <v>1.5125</v>
       </c>
       <c r="M67">
-        <v>4.7191833</v>
+        <v>4.79178612</v>
       </c>
       <c r="N67">
-        <v>-3.2066833</v>
+        <v>-3.279286120000001</v>
       </c>
       <c r="O67">
-        <v>-1.026138656</v>
+        <v>-1.0493715584</v>
       </c>
       <c r="P67">
-        <v>-2.180544644</v>
+        <v>-2.2299145616</v>
       </c>
       <c r="Q67">
-        <v>-1.630544644</v>
+        <v>-1.6799145616</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1819172449982364</v>
+        <v>0.1859206933805375</v>
       </c>
       <c r="T67">
-        <v>1.77406400836643</v>
+        <v>1.826242361553678</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1025601188239499</v>
+        <v>0.1010061776296476</v>
       </c>
       <c r="W67">
-        <v>0.2116163239813126</v>
+        <v>0.2119827433149291</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3205003713248433</v>
+        <v>0.3156443050926487</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.203121646337236</v>
+        <v>0.205021646337236</v>
       </c>
       <c r="C68">
-        <v>-11.66207256637763</v>
+        <v>-12.07301836763214</v>
       </c>
       <c r="D68">
-        <v>8.635327433622368</v>
+        <v>8.532281632367861</v>
       </c>
       <c r="E68">
-        <v>-0.7786000000000008</v>
+        <v>-0.4707000000000008</v>
       </c>
       <c r="F68">
-        <v>20.3214</v>
+        <v>20.6293</v>
       </c>
       <c r="G68">
         <v>0.024</v>
@@ -6851,37 +6851,37 @@
         <v>1.5125</v>
       </c>
       <c r="M68">
-        <v>4.79178612</v>
+        <v>4.86438894</v>
       </c>
       <c r="N68">
-        <v>-3.279286120000001</v>
+        <v>-3.351888940000001</v>
       </c>
       <c r="O68">
-        <v>-1.0493715584</v>
+        <v>-1.0726044608</v>
       </c>
       <c r="P68">
-        <v>-2.2299145616</v>
+        <v>-2.2792844792</v>
       </c>
       <c r="Q68">
-        <v>-1.6799145616</v>
+        <v>-1.7292844792</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1859206933805375</v>
+        <v>0.1901667749981296</v>
       </c>
       <c r="T68">
-        <v>1.826242361553678</v>
+        <v>1.881583039176517</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1010061776296476</v>
+        <v>0.09949862273965286</v>
       </c>
       <c r="W68">
-        <v>0.2119827433149291</v>
+        <v>0.2123382247579899</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3156443050926487</v>
+        <v>0.3109331960614152</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.205021646337236</v>
+        <v>0.206921646337236</v>
       </c>
       <c r="C69">
-        <v>-12.07301836763214</v>
+        <v>-12.48153386821837</v>
       </c>
       <c r="D69">
-        <v>8.532281632367861</v>
+        <v>8.431666131781627</v>
       </c>
       <c r="E69">
-        <v>-0.4707000000000008</v>
+        <v>-0.1628000000000007</v>
       </c>
       <c r="F69">
-        <v>20.6293</v>
+        <v>20.9372</v>
       </c>
       <c r="G69">
         <v>0.024</v>
@@ -6933,37 +6933,37 @@
         <v>1.5125</v>
       </c>
       <c r="M69">
-        <v>4.86438894</v>
+        <v>4.936991760000001</v>
       </c>
       <c r="N69">
-        <v>-3.351888940000001</v>
+        <v>-3.424491760000001</v>
       </c>
       <c r="O69">
-        <v>-1.0726044608</v>
+        <v>-1.0958373632</v>
       </c>
       <c r="P69">
-        <v>-2.2792844792</v>
+        <v>-2.328654396800001</v>
       </c>
       <c r="Q69">
-        <v>-1.7292844792</v>
+        <v>-1.778654396800001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1901667749981296</v>
+        <v>0.1946782367168212</v>
       </c>
       <c r="T69">
-        <v>1.881583039176517</v>
+        <v>1.940382509150784</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09949862273965286</v>
+        <v>0.09803540769936385</v>
       </c>
       <c r="W69">
-        <v>0.2123382247579899</v>
+        <v>0.21268325086449</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3109331960614152</v>
+        <v>0.306360649060512</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.206921646337236</v>
+        <v>0.208821646337236</v>
       </c>
       <c r="C70">
-        <v>-12.48153386821837</v>
+        <v>-12.88770404282602</v>
       </c>
       <c r="D70">
-        <v>8.431666131781627</v>
+        <v>8.333395957173986</v>
       </c>
       <c r="E70">
-        <v>-0.1628000000000007</v>
+        <v>0.1450999999999993</v>
       </c>
       <c r="F70">
-        <v>20.9372</v>
+        <v>21.2451</v>
       </c>
       <c r="G70">
         <v>0.024</v>
@@ -7015,37 +7015,37 @@
         <v>1.5125</v>
       </c>
       <c r="M70">
-        <v>4.936991760000001</v>
+        <v>5.009594580000001</v>
       </c>
       <c r="N70">
-        <v>-3.424491760000001</v>
+        <v>-3.497094580000001</v>
       </c>
       <c r="O70">
-        <v>-1.0958373632</v>
+        <v>-1.1190702656</v>
       </c>
       <c r="P70">
-        <v>-2.328654396800001</v>
+        <v>-2.378024314400001</v>
       </c>
       <c r="Q70">
-        <v>-1.778654396800001</v>
+        <v>-1.828024314400001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1946782367168212</v>
+        <v>0.1994807604818799</v>
       </c>
       <c r="T70">
-        <v>1.940382509150784</v>
+        <v>2.002975493316938</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09803540769936385</v>
+        <v>0.09661460468922814</v>
       </c>
       <c r="W70">
-        <v>0.21268325086449</v>
+        <v>0.21301827621428</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.306360649060512</v>
+        <v>0.3019206396538379</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.208821646337236</v>
+        <v>0.210721646337236</v>
       </c>
       <c r="C71">
-        <v>-12.88770404282602</v>
+        <v>-13.29160995029952</v>
       </c>
       <c r="D71">
-        <v>8.333395957173986</v>
+        <v>8.237390049700481</v>
       </c>
       <c r="E71">
-        <v>0.1450999999999993</v>
+        <v>0.4529999999999994</v>
       </c>
       <c r="F71">
-        <v>21.2451</v>
+        <v>21.553</v>
       </c>
       <c r="G71">
         <v>0.024</v>
@@ -7097,37 +7097,37 @@
         <v>1.5125</v>
       </c>
       <c r="M71">
-        <v>5.009594580000001</v>
+        <v>5.0821974</v>
       </c>
       <c r="N71">
-        <v>-3.497094580000001</v>
+        <v>-3.5696974</v>
       </c>
       <c r="O71">
-        <v>-1.1190702656</v>
+        <v>-1.142303168</v>
       </c>
       <c r="P71">
-        <v>-2.378024314400001</v>
+        <v>-2.427394232</v>
       </c>
       <c r="Q71">
-        <v>-1.828024314400001</v>
+        <v>-1.877394232</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1994807604818799</v>
+        <v>0.2046034524979426</v>
       </c>
       <c r="T71">
-        <v>2.002975493316938</v>
+        <v>2.069741343094169</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09661460468922814</v>
+        <v>0.0952343960508106</v>
       </c>
       <c r="W71">
-        <v>0.21301827621428</v>
+        <v>0.2133437294112189</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3019206396538379</v>
+        <v>0.2976074876587831</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.210721646337236</v>
+        <v>0.212621646337236</v>
       </c>
       <c r="C72">
-        <v>-13.29160995029952</v>
+        <v>-13.69332895663393</v>
       </c>
       <c r="D72">
-        <v>8.237390049700481</v>
+        <v>8.143571043366068</v>
       </c>
       <c r="E72">
-        <v>0.4529999999999994</v>
+        <v>0.7608999999999995</v>
       </c>
       <c r="F72">
-        <v>21.553</v>
+        <v>21.8609</v>
       </c>
       <c r="G72">
         <v>0.024</v>
@@ -7179,37 +7179,37 @@
         <v>1.5125</v>
       </c>
       <c r="M72">
-        <v>5.0821974</v>
+        <v>5.15480022</v>
       </c>
       <c r="N72">
-        <v>-3.5696974</v>
+        <v>-3.642300220000001</v>
       </c>
       <c r="O72">
-        <v>-1.142303168</v>
+        <v>-1.1655360704</v>
       </c>
       <c r="P72">
-        <v>-2.427394232</v>
+        <v>-2.4767641496</v>
       </c>
       <c r="Q72">
-        <v>-1.877394232</v>
+        <v>-1.9267641496</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2046034524979426</v>
+        <v>0.2100794336185613</v>
       </c>
       <c r="T72">
-        <v>2.069741343094169</v>
+        <v>2.141111734235347</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0952343960508106</v>
+        <v>0.09389306652896819</v>
       </c>
       <c r="W72">
-        <v>0.2133437294112189</v>
+        <v>0.2136600149124693</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2976074876587831</v>
+        <v>0.2934158329030256</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.212621646337236</v>
+        <v>0.214521646337236</v>
       </c>
       <c r="C73">
-        <v>-13.69332895663393</v>
+        <v>-14.09293494290358</v>
       </c>
       <c r="D73">
-        <v>8.143571043366068</v>
+        <v>8.051865057096414</v>
       </c>
       <c r="E73">
-        <v>0.7608999999999959</v>
+        <v>1.068799999999996</v>
       </c>
       <c r="F73">
-        <v>21.8609</v>
+        <v>22.1688</v>
       </c>
       <c r="G73">
         <v>0.024</v>
@@ -7261,37 +7261,37 @@
         <v>1.5125</v>
       </c>
       <c r="M73">
-        <v>5.154800219999999</v>
+        <v>5.22740304</v>
       </c>
       <c r="N73">
-        <v>-3.64230022</v>
+        <v>-3.71490304</v>
       </c>
       <c r="O73">
-        <v>-1.1655360704</v>
+        <v>-1.1887689728</v>
       </c>
       <c r="P73">
-        <v>-2.4767641496</v>
+        <v>-2.5261340672</v>
       </c>
       <c r="Q73">
-        <v>-1.9267641496</v>
+        <v>-1.9761340672</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2100794336185612</v>
+        <v>0.2159465562477955</v>
       </c>
       <c r="T73">
-        <v>2.141111734235347</v>
+        <v>2.217580010458037</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09389306652896821</v>
+        <v>0.09258899616051032</v>
       </c>
       <c r="W73">
-        <v>0.2136600149124693</v>
+        <v>0.2139675147053517</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2934158329030256</v>
+        <v>0.2893406130015947</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.214521646337236</v>
+        <v>0.216421646337236</v>
       </c>
       <c r="C74">
-        <v>-14.09293494290358</v>
+        <v>-14.49049849929809</v>
       </c>
       <c r="D74">
-        <v>8.051865057096414</v>
+        <v>7.962201500701904</v>
       </c>
       <c r="E74">
-        <v>1.068799999999996</v>
+        <v>1.376699999999996</v>
       </c>
       <c r="F74">
-        <v>22.1688</v>
+        <v>22.4767</v>
       </c>
       <c r="G74">
         <v>0.024</v>
@@ -7343,37 +7343,37 @@
         <v>1.5125</v>
       </c>
       <c r="M74">
-        <v>5.22740304</v>
+        <v>5.30000586</v>
       </c>
       <c r="N74">
-        <v>-3.71490304</v>
+        <v>-3.78750586</v>
       </c>
       <c r="O74">
-        <v>-1.1887689728</v>
+        <v>-1.2120018752</v>
       </c>
       <c r="P74">
-        <v>-2.5261340672</v>
+        <v>-2.5755039848</v>
       </c>
       <c r="Q74">
-        <v>-1.9761340672</v>
+        <v>-2.0255039848</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2159465562477955</v>
+        <v>0.2222482805532695</v>
       </c>
       <c r="T74">
-        <v>2.217580010458037</v>
+        <v>2.299712603437965</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09258899616051032</v>
+        <v>0.09132065374735264</v>
       </c>
       <c r="W74">
-        <v>0.2139675147053517</v>
+        <v>0.2142665898463743</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2893406130015947</v>
+        <v>0.2853770429604769</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.216421646337236</v>
+        <v>0.2183216463372359</v>
       </c>
       <c r="C75">
-        <v>-14.49049849929809</v>
+        <v>-14.88608710633678</v>
       </c>
       <c r="D75">
-        <v>7.962201500701904</v>
+        <v>7.874512893663216</v>
       </c>
       <c r="E75">
-        <v>1.376699999999996</v>
+        <v>1.684599999999996</v>
       </c>
       <c r="F75">
-        <v>22.4767</v>
+        <v>22.7846</v>
       </c>
       <c r="G75">
         <v>0.024</v>
@@ -7425,37 +7425,37 @@
         <v>1.5125</v>
       </c>
       <c r="M75">
-        <v>5.30000586</v>
+        <v>5.37260868</v>
       </c>
       <c r="N75">
-        <v>-3.78750586</v>
+        <v>-3.86010868</v>
       </c>
       <c r="O75">
-        <v>-1.2120018752</v>
+        <v>-1.2352347776</v>
       </c>
       <c r="P75">
-        <v>-2.5755039848</v>
+        <v>-2.6248739024</v>
       </c>
       <c r="Q75">
-        <v>-2.0255039848</v>
+        <v>-2.0748739024</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2222482805532695</v>
+        <v>0.2290347528822413</v>
       </c>
       <c r="T75">
-        <v>2.299712603437965</v>
+        <v>2.388163088185579</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09132065374735264</v>
+        <v>0.0900865908588749</v>
       </c>
       <c r="W75">
-        <v>0.2142665898463743</v>
+        <v>0.2145575818754773</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2853770429604769</v>
+        <v>0.2815205964339841</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2183216463372359</v>
+        <v>0.220221646337236</v>
       </c>
       <c r="C76">
-        <v>-14.88608710633678</v>
+        <v>-15.27976530423908</v>
       </c>
       <c r="D76">
-        <v>7.874512893663216</v>
+        <v>7.788734695760917</v>
       </c>
       <c r="E76">
-        <v>1.684599999999996</v>
+        <v>1.9925</v>
       </c>
       <c r="F76">
-        <v>22.7846</v>
+        <v>23.0925</v>
       </c>
       <c r="G76">
         <v>0.024</v>
@@ -7507,37 +7507,37 @@
         <v>1.5125</v>
       </c>
       <c r="M76">
-        <v>5.37260868</v>
+        <v>5.4452115</v>
       </c>
       <c r="N76">
-        <v>-3.86010868</v>
+        <v>-3.9327115</v>
       </c>
       <c r="O76">
-        <v>-1.2352347776</v>
+        <v>-1.25846768</v>
       </c>
       <c r="P76">
-        <v>-2.6248739024</v>
+        <v>-2.67424382</v>
       </c>
       <c r="Q76">
-        <v>-2.0748739024</v>
+        <v>-2.12424382</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2290347528822413</v>
+        <v>0.236364142997531</v>
       </c>
       <c r="T76">
-        <v>2.388163088185579</v>
+        <v>2.483689611713003</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0900865908588749</v>
+        <v>0.08888543631408989</v>
       </c>
       <c r="W76">
-        <v>0.2145575818754773</v>
+        <v>0.2148408141171376</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2815205964339841</v>
+        <v>0.2777669884815309</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.220221646337236</v>
+        <v>0.222121646337236</v>
       </c>
       <c r="C77">
-        <v>-15.27976530423908</v>
+        <v>-15.67159485134439</v>
       </c>
       <c r="D77">
-        <v>7.788734695760917</v>
+        <v>7.704805148655614</v>
       </c>
       <c r="E77">
-        <v>1.9925</v>
+        <v>2.3004</v>
       </c>
       <c r="F77">
-        <v>23.0925</v>
+        <v>23.4004</v>
       </c>
       <c r="G77">
         <v>0.024</v>
@@ -7589,37 +7589,37 @@
         <v>1.5125</v>
       </c>
       <c r="M77">
-        <v>5.4452115</v>
+        <v>5.51781432</v>
       </c>
       <c r="N77">
-        <v>-3.9327115</v>
+        <v>-4.00531432</v>
       </c>
       <c r="O77">
-        <v>-1.25846768</v>
+        <v>-1.2817005824</v>
       </c>
       <c r="P77">
-        <v>-2.67424382</v>
+        <v>-2.7236137376</v>
       </c>
       <c r="Q77">
-        <v>-2.12424382</v>
+        <v>-2.1736137376</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.236364142997531</v>
+        <v>0.2443043156224282</v>
       </c>
       <c r="T77">
-        <v>2.483689611713003</v>
+        <v>2.587176678867711</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08888543631408989</v>
+        <v>0.08771589109943081</v>
       </c>
       <c r="W77">
-        <v>0.2148408141171376</v>
+        <v>0.2151165928787542</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2777669884815309</v>
+        <v>0.2741121596857213</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.222121646337236</v>
+        <v>0.224021646337236</v>
       </c>
       <c r="C78">
-        <v>-15.67159485134439</v>
+        <v>-16.06163487239854</v>
       </c>
       <c r="D78">
-        <v>7.704805148655614</v>
+        <v>7.622665127601463</v>
       </c>
       <c r="E78">
-        <v>2.3004</v>
+        <v>2.6083</v>
       </c>
       <c r="F78">
-        <v>23.4004</v>
+        <v>23.7083</v>
       </c>
       <c r="G78">
         <v>0.024</v>
@@ -7671,37 +7671,37 @@
         <v>1.5125</v>
       </c>
       <c r="M78">
-        <v>5.51781432</v>
+        <v>5.59041714</v>
       </c>
       <c r="N78">
-        <v>-4.00531432</v>
+        <v>-4.07791714</v>
       </c>
       <c r="O78">
-        <v>-1.2817005824</v>
+        <v>-1.3049334848</v>
       </c>
       <c r="P78">
-        <v>-2.7236137376</v>
+        <v>-2.7729836552</v>
       </c>
       <c r="Q78">
-        <v>-2.1736137376</v>
+        <v>-2.2229836552</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2443043156224282</v>
+        <v>0.2529349380407946</v>
       </c>
       <c r="T78">
-        <v>2.587176678867711</v>
+        <v>2.699662621427177</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08771589109943081</v>
+        <v>0.08657672368255509</v>
       </c>
       <c r="W78">
-        <v>0.2151165928787542</v>
+        <v>0.2153852085556535</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2741121596857213</v>
+        <v>0.2705522615079847</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.224021646337236</v>
+        <v>0.225921646337236</v>
       </c>
       <c r="C79">
-        <v>-16.06163487239854</v>
+        <v>-16.44994199745516</v>
       </c>
       <c r="D79">
-        <v>7.622665127601463</v>
+        <v>7.542258002544843</v>
       </c>
       <c r="E79">
-        <v>2.6083</v>
+        <v>2.9162</v>
       </c>
       <c r="F79">
-        <v>23.7083</v>
+        <v>24.0162</v>
       </c>
       <c r="G79">
         <v>0.024</v>
@@ -7753,37 +7753,37 @@
         <v>1.5125</v>
       </c>
       <c r="M79">
-        <v>5.59041714</v>
+        <v>5.663019960000001</v>
       </c>
       <c r="N79">
-        <v>-4.07791714</v>
+        <v>-4.15051996</v>
       </c>
       <c r="O79">
-        <v>-1.3049334848</v>
+        <v>-1.3281663872</v>
       </c>
       <c r="P79">
-        <v>-2.7729836552</v>
+        <v>-2.8223535728</v>
       </c>
       <c r="Q79">
-        <v>-2.2229836552</v>
+        <v>-2.2723535728</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2529349380407946</v>
+        <v>0.2623501624971943</v>
       </c>
       <c r="T79">
-        <v>2.699662621427177</v>
+        <v>2.822374558764776</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08657672368255509</v>
+        <v>0.0854667656866249</v>
       </c>
       <c r="W79">
-        <v>0.2153852085556535</v>
+        <v>0.2156469366510939</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2705522615079847</v>
+        <v>0.2670836427707028</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.225921646337236</v>
+        <v>0.2278216463372359</v>
       </c>
       <c r="C80">
-        <v>-16.44994199745516</v>
+        <v>-16.83657049207763</v>
       </c>
       <c r="D80">
-        <v>7.542258002544843</v>
+        <v>7.463529507922369</v>
       </c>
       <c r="E80">
-        <v>2.9162</v>
+        <v>3.2241</v>
       </c>
       <c r="F80">
-        <v>24.0162</v>
+        <v>24.3241</v>
       </c>
       <c r="G80">
         <v>0.024</v>
@@ -7835,37 +7835,37 @@
         <v>1.5125</v>
       </c>
       <c r="M80">
-        <v>5.663019960000001</v>
+        <v>5.735622780000001</v>
       </c>
       <c r="N80">
-        <v>-4.15051996</v>
+        <v>-4.223122780000001</v>
       </c>
       <c r="O80">
-        <v>-1.3281663872</v>
+        <v>-1.3513992896</v>
       </c>
       <c r="P80">
-        <v>-2.8223535728</v>
+        <v>-2.8717234904</v>
       </c>
       <c r="Q80">
-        <v>-2.2723535728</v>
+        <v>-2.321723490400001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2623501624971943</v>
+        <v>0.2726620749970607</v>
       </c>
       <c r="T80">
-        <v>2.822374558764776</v>
+        <v>2.956773347277384</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0854667656866249</v>
+        <v>0.08438490789312331</v>
       </c>
       <c r="W80">
-        <v>0.2156469366510939</v>
+        <v>0.2159020387188015</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2670836427707028</v>
+        <v>0.2637028371660104</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2278216463372359</v>
+        <v>0.229721646337236</v>
       </c>
       <c r="C81">
-        <v>-16.83657049207763</v>
+        <v>-17.22157237947076</v>
       </c>
       <c r="D81">
-        <v>7.463529507922369</v>
+        <v>7.386427620529236</v>
       </c>
       <c r="E81">
-        <v>3.2241</v>
+        <v>3.532</v>
       </c>
       <c r="F81">
-        <v>24.3241</v>
+        <v>24.632</v>
       </c>
       <c r="G81">
         <v>0.024</v>
@@ -7917,37 +7917,37 @@
         <v>1.5125</v>
       </c>
       <c r="M81">
-        <v>5.735622780000001</v>
+        <v>5.808225600000001</v>
       </c>
       <c r="N81">
-        <v>-4.223122780000001</v>
+        <v>-4.295725600000001</v>
       </c>
       <c r="O81">
-        <v>-1.3513992896</v>
+        <v>-1.374632192</v>
       </c>
       <c r="P81">
-        <v>-2.8717234904</v>
+        <v>-2.921093408000001</v>
       </c>
       <c r="Q81">
-        <v>-2.321723490400001</v>
+        <v>-2.371093408000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2726620749970607</v>
+        <v>0.2840051787469138</v>
       </c>
       <c r="T81">
-        <v>2.956773347277384</v>
+        <v>3.104612014641253</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08438490789312331</v>
+        <v>0.08333009654445926</v>
       </c>
       <c r="W81">
-        <v>0.2159020387188015</v>
+        <v>0.2161507632348165</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2637028371660104</v>
+        <v>0.2604065517014352</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.229721646337236</v>
+        <v>0.231621646337236</v>
       </c>
       <c r="C82">
-        <v>-17.22157237947076</v>
+        <v>-17.60499755511976</v>
       </c>
       <c r="D82">
-        <v>7.386427620529236</v>
+        <v>7.310902444880239</v>
       </c>
       <c r="E82">
-        <v>3.532</v>
+        <v>3.8399</v>
       </c>
       <c r="F82">
-        <v>24.632</v>
+        <v>24.9399</v>
       </c>
       <c r="G82">
         <v>0.024</v>
@@ -7999,37 +7999,37 @@
         <v>1.5125</v>
       </c>
       <c r="M82">
-        <v>5.808225600000001</v>
+        <v>5.88082842</v>
       </c>
       <c r="N82">
-        <v>-4.295725600000001</v>
+        <v>-4.368328420000001</v>
       </c>
       <c r="O82">
-        <v>-1.374632192</v>
+        <v>-1.3978650944</v>
       </c>
       <c r="P82">
-        <v>-2.921093408000001</v>
+        <v>-2.970463325600001</v>
       </c>
       <c r="Q82">
-        <v>-2.371093408000001</v>
+        <v>-2.420463325600001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2840051787469138</v>
+        <v>0.2965422934178041</v>
       </c>
       <c r="T82">
-        <v>3.104612014641253</v>
+        <v>3.268012646990794</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08333009654445926</v>
+        <v>0.08230132992045361</v>
       </c>
       <c r="W82">
-        <v>0.2161507632348165</v>
+        <v>0.216393346404757</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2604065517014352</v>
+        <v>0.2571916560014175</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.231621646337236</v>
+        <v>0.233521646337236</v>
       </c>
       <c r="C83">
-        <v>-17.60499755511976</v>
+        <v>-17.98689389446742</v>
       </c>
       <c r="D83">
-        <v>7.310902444880239</v>
+        <v>7.236906105532576</v>
       </c>
       <c r="E83">
-        <v>3.8399</v>
+        <v>4.1478</v>
       </c>
       <c r="F83">
-        <v>24.9399</v>
+        <v>25.2478</v>
       </c>
       <c r="G83">
         <v>0.024</v>
@@ -8081,37 +8081,37 @@
         <v>1.5125</v>
       </c>
       <c r="M83">
-        <v>5.88082842</v>
+        <v>5.95343124</v>
       </c>
       <c r="N83">
-        <v>-4.368328420000001</v>
+        <v>-4.440931240000001</v>
       </c>
       <c r="O83">
-        <v>-1.3978650944</v>
+        <v>-1.4210979968</v>
       </c>
       <c r="P83">
-        <v>-2.970463325600001</v>
+        <v>-3.019833243200001</v>
       </c>
       <c r="Q83">
-        <v>-2.420463325600001</v>
+        <v>-2.469833243200001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2965422934178041</v>
+        <v>0.3104724208299042</v>
       </c>
       <c r="T83">
-        <v>3.268012646990794</v>
+        <v>3.449568905156948</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08230132992045361</v>
+        <v>0.08129765516532611</v>
       </c>
       <c r="W83">
-        <v>0.216393346404757</v>
+        <v>0.2166300129120161</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2571916560014175</v>
+        <v>0.254055172391644</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.233521646337236</v>
+        <v>0.235421646337236</v>
       </c>
       <c r="C84">
-        <v>-17.98689389446742</v>
+        <v>-18.3673073541178</v>
       </c>
       <c r="D84">
-        <v>7.236906105532576</v>
+        <v>7.164392645882204</v>
       </c>
       <c r="E84">
-        <v>4.1478</v>
+        <v>4.4557</v>
       </c>
       <c r="F84">
-        <v>25.2478</v>
+        <v>25.5557</v>
       </c>
       <c r="G84">
         <v>0.024</v>
@@ -8163,37 +8163,37 @@
         <v>1.5125</v>
       </c>
       <c r="M84">
-        <v>5.95343124</v>
+        <v>6.026034060000001</v>
       </c>
       <c r="N84">
-        <v>-4.440931240000001</v>
+        <v>-4.513534060000001</v>
       </c>
       <c r="O84">
-        <v>-1.4210979968</v>
+        <v>-1.4443308992</v>
       </c>
       <c r="P84">
-        <v>-3.019833243200001</v>
+        <v>-3.069203160800001</v>
       </c>
       <c r="Q84">
-        <v>-2.469833243200001</v>
+        <v>-2.519203160800001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3104724208299042</v>
+        <v>0.3260413867610751</v>
       </c>
       <c r="T84">
-        <v>3.449568905156948</v>
+        <v>3.652484723107358</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08129765516532611</v>
+        <v>0.08031816534405714</v>
       </c>
       <c r="W84">
-        <v>0.2166300129120161</v>
+        <v>0.2168609766118713</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.254055172391644</v>
+        <v>0.2509942667001784</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.235421646337236</v>
+        <v>0.237321646337236</v>
       </c>
       <c r="C85">
-        <v>-18.3673073541178</v>
+        <v>-18.74628206701582</v>
       </c>
       <c r="D85">
-        <v>7.164392645882204</v>
+        <v>7.093317932984178</v>
       </c>
       <c r="E85">
-        <v>4.4557</v>
+        <v>4.7636</v>
       </c>
       <c r="F85">
-        <v>25.5557</v>
+        <v>25.8636</v>
       </c>
       <c r="G85">
         <v>0.024</v>
@@ -8245,37 +8245,37 @@
         <v>1.5125</v>
       </c>
       <c r="M85">
-        <v>6.026034060000001</v>
+        <v>6.098636880000001</v>
       </c>
       <c r="N85">
-        <v>-4.513534060000001</v>
+        <v>-4.586136880000002</v>
       </c>
       <c r="O85">
-        <v>-1.4443308992</v>
+        <v>-1.467563801600001</v>
       </c>
       <c r="P85">
-        <v>-3.069203160800001</v>
+        <v>-3.118573078400001</v>
       </c>
       <c r="Q85">
-        <v>-2.519203160800001</v>
+        <v>-2.568573078400001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3260413867610751</v>
+        <v>0.3435564734336424</v>
       </c>
       <c r="T85">
-        <v>3.652484723107358</v>
+        <v>3.880765018301569</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08031816534405714</v>
+        <v>0.07936199670900883</v>
       </c>
       <c r="W85">
-        <v>0.2168609766118713</v>
+        <v>0.2170864411760157</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2509942667001784</v>
+        <v>0.2480062397156525</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.237321646337236</v>
+        <v>0.2392216463372359</v>
       </c>
       <c r="C86">
-        <v>-18.74628206701582</v>
+        <v>-19.12386043201728</v>
       </c>
       <c r="D86">
-        <v>7.093317932984181</v>
+        <v>7.023639567982717</v>
       </c>
       <c r="E86">
-        <v>4.763599999999997</v>
+        <v>5.071499999999997</v>
       </c>
       <c r="F86">
-        <v>25.8636</v>
+        <v>26.1715</v>
       </c>
       <c r="G86">
         <v>0.024</v>
@@ -8327,37 +8327,37 @@
         <v>1.5125</v>
       </c>
       <c r="M86">
-        <v>6.09863688</v>
+        <v>6.1712397</v>
       </c>
       <c r="N86">
-        <v>-4.58613688</v>
+        <v>-4.6587397</v>
       </c>
       <c r="O86">
-        <v>-1.4675638016</v>
+        <v>-1.490796704</v>
       </c>
       <c r="P86">
-        <v>-3.1185730784</v>
+        <v>-3.167942996</v>
       </c>
       <c r="Q86">
-        <v>-2.5685730784</v>
+        <v>-2.617942996</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3435564734336422</v>
+        <v>0.363406904995885</v>
       </c>
       <c r="T86">
-        <v>3.880765018301565</v>
+        <v>4.139482686188336</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07936199670900884</v>
+        <v>0.07842832615949108</v>
       </c>
       <c r="W86">
-        <v>0.2170864411760157</v>
+        <v>0.217306600691592</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2480062397156527</v>
+        <v>0.2450885192484097</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2392216463372359</v>
+        <v>0.241121646337236</v>
       </c>
       <c r="C87">
-        <v>-19.12386043201728</v>
+        <v>-19.50008319823095</v>
       </c>
       <c r="D87">
-        <v>7.023639567982717</v>
+        <v>6.95531680176905</v>
       </c>
       <c r="E87">
-        <v>5.071499999999997</v>
+        <v>5.379399999999997</v>
       </c>
       <c r="F87">
-        <v>26.1715</v>
+        <v>26.4794</v>
       </c>
       <c r="G87">
         <v>0.024</v>
@@ -8409,37 +8409,37 @@
         <v>1.5125</v>
       </c>
       <c r="M87">
-        <v>6.1712397</v>
+        <v>6.24384252</v>
       </c>
       <c r="N87">
-        <v>-4.6587397</v>
+        <v>-4.73134252</v>
       </c>
       <c r="O87">
-        <v>-1.490796704</v>
+        <v>-1.5140296064</v>
       </c>
       <c r="P87">
-        <v>-3.167942996</v>
+        <v>-3.2173129136</v>
       </c>
       <c r="Q87">
-        <v>-2.617942996</v>
+        <v>-2.6673129136</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.363406904995885</v>
+        <v>0.386093112495591</v>
       </c>
       <c r="T87">
-        <v>4.139482686188336</v>
+        <v>4.435160020916075</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07842832615949108</v>
+        <v>0.07751636887856676</v>
       </c>
       <c r="W87">
-        <v>0.217306600691592</v>
+        <v>0.217521640218434</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2450885192484097</v>
+        <v>0.2422386527455213</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.241121646337236</v>
+        <v>0.2430216463372359</v>
       </c>
       <c r="C88">
-        <v>-19.50008319823095</v>
+        <v>-19.87498954448548</v>
       </c>
       <c r="D88">
-        <v>6.95531680176905</v>
+        <v>6.888310455514523</v>
       </c>
       <c r="E88">
-        <v>5.379399999999997</v>
+        <v>5.687299999999997</v>
       </c>
       <c r="F88">
-        <v>26.4794</v>
+        <v>26.7873</v>
       </c>
       <c r="G88">
         <v>0.024</v>
@@ -8491,37 +8491,37 @@
         <v>1.5125</v>
       </c>
       <c r="M88">
-        <v>6.24384252</v>
+        <v>6.31644534</v>
       </c>
       <c r="N88">
-        <v>-4.73134252</v>
+        <v>-4.80394534</v>
       </c>
       <c r="O88">
-        <v>-1.5140296064</v>
+        <v>-1.5372625088</v>
       </c>
       <c r="P88">
-        <v>-3.2173129136</v>
+        <v>-3.2666828312</v>
       </c>
       <c r="Q88">
-        <v>-2.6673129136</v>
+        <v>-2.7166828312</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.386093112495591</v>
+        <v>0.4122695057644827</v>
       </c>
       <c r="T88">
-        <v>4.435160020916075</v>
+        <v>4.776326176371158</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07751636887856676</v>
+        <v>0.07662537613283613</v>
       </c>
       <c r="W88">
-        <v>0.217521640218434</v>
+        <v>0.2177317363078772</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2422386527455213</v>
+        <v>0.2394543004151128</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2430216463372359</v>
+        <v>0.244921646337236</v>
       </c>
       <c r="C89">
-        <v>-19.87498954448548</v>
+        <v>-20.24861715424676</v>
       </c>
       <c r="D89">
-        <v>6.888310455514523</v>
+        <v>6.822582845753241</v>
       </c>
       <c r="E89">
-        <v>5.687299999999997</v>
+        <v>5.995199999999997</v>
       </c>
       <c r="F89">
-        <v>26.7873</v>
+        <v>27.0952</v>
       </c>
       <c r="G89">
         <v>0.024</v>
@@ -8573,37 +8573,37 @@
         <v>1.5125</v>
       </c>
       <c r="M89">
-        <v>6.31644534</v>
+        <v>6.38904816</v>
       </c>
       <c r="N89">
-        <v>-4.80394534</v>
+        <v>-4.87654816</v>
       </c>
       <c r="O89">
-        <v>-1.5372625088</v>
+        <v>-1.5604954112</v>
       </c>
       <c r="P89">
-        <v>-3.2666828312</v>
+        <v>-3.3160527488</v>
       </c>
       <c r="Q89">
-        <v>-2.7166828312</v>
+        <v>-2.7660527488</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4122695057644827</v>
+        <v>0.4428086312448563</v>
       </c>
       <c r="T89">
-        <v>4.776326176371158</v>
+        <v>5.174353357735422</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07662537613283613</v>
+        <v>0.0757546332222357</v>
       </c>
       <c r="W89">
-        <v>0.2177317363078772</v>
+        <v>0.2179370574861968</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2394543004151128</v>
+        <v>0.2367332288194866</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.244921646337236</v>
+        <v>0.246821646337236</v>
       </c>
       <c r="C90">
-        <v>-20.24861715424676</v>
+        <v>-20.62100228628664</v>
       </c>
       <c r="D90">
-        <v>6.822582845753241</v>
+        <v>6.758097713713359</v>
       </c>
       <c r="E90">
-        <v>5.995199999999997</v>
+        <v>6.303099999999997</v>
       </c>
       <c r="F90">
-        <v>27.0952</v>
+        <v>27.4031</v>
       </c>
       <c r="G90">
         <v>0.024</v>
@@ -8655,37 +8655,37 @@
         <v>1.5125</v>
       </c>
       <c r="M90">
-        <v>6.38904816</v>
+        <v>6.46165098</v>
       </c>
       <c r="N90">
-        <v>-4.87654816</v>
+        <v>-4.949150980000001</v>
       </c>
       <c r="O90">
-        <v>-1.5604954112</v>
+        <v>-1.5837283136</v>
       </c>
       <c r="P90">
-        <v>-3.3160527488</v>
+        <v>-3.365422666400001</v>
       </c>
       <c r="Q90">
-        <v>-2.7660527488</v>
+        <v>-2.815422666400001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4428086312448563</v>
+        <v>0.4789003249943887</v>
       </c>
       <c r="T90">
-        <v>5.174353357735422</v>
+        <v>5.644749117529551</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0757546332222357</v>
+        <v>0.07490345756805328</v>
       </c>
       <c r="W90">
-        <v>0.2179370574861968</v>
+        <v>0.218137764705453</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2367332288194866</v>
+        <v>0.2340733049001664</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.246821646337236</v>
+        <v>0.248721646337236</v>
       </c>
       <c r="C91">
-        <v>-20.62100228628664</v>
+        <v>-20.99217984138156</v>
       </c>
       <c r="D91">
-        <v>6.758097713713359</v>
+        <v>6.694820158618443</v>
       </c>
       <c r="E91">
-        <v>6.303099999999997</v>
+        <v>6.610999999999997</v>
       </c>
       <c r="F91">
-        <v>27.4031</v>
+        <v>27.711</v>
       </c>
       <c r="G91">
         <v>0.024</v>
@@ -8737,37 +8737,37 @@
         <v>1.5125</v>
       </c>
       <c r="M91">
-        <v>6.46165098</v>
+        <v>6.5342538</v>
       </c>
       <c r="N91">
-        <v>-4.949150980000001</v>
+        <v>-5.021753800000001</v>
       </c>
       <c r="O91">
-        <v>-1.5837283136</v>
+        <v>-1.606961216</v>
       </c>
       <c r="P91">
-        <v>-3.365422666400001</v>
+        <v>-3.414792584000001</v>
       </c>
       <c r="Q91">
-        <v>-2.815422666400001</v>
+        <v>-2.864792584000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4789003249943887</v>
+        <v>0.5222103574938276</v>
       </c>
       <c r="T91">
-        <v>5.644749117529551</v>
+        <v>6.209224029282507</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07490345756805328</v>
+        <v>0.07407119692840824</v>
       </c>
       <c r="W91">
-        <v>0.218137764705453</v>
+        <v>0.2183340117642814</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2340733049001664</v>
+        <v>0.2314724904012757</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.248721646337236</v>
+        <v>0.2506216463372359</v>
       </c>
       <c r="C92">
-        <v>-20.99217984138156</v>
+        <v>-21.36218342529881</v>
       </c>
       <c r="D92">
-        <v>6.694820158618443</v>
+        <v>6.632716574701187</v>
       </c>
       <c r="E92">
-        <v>6.610999999999997</v>
+        <v>6.918899999999997</v>
       </c>
       <c r="F92">
-        <v>27.711</v>
+        <v>28.0189</v>
       </c>
       <c r="G92">
         <v>0.024</v>
@@ -8819,37 +8819,37 @@
         <v>1.5125</v>
       </c>
       <c r="M92">
-        <v>6.5342538</v>
+        <v>6.60685662</v>
       </c>
       <c r="N92">
-        <v>-5.021753800000001</v>
+        <v>-5.094356620000001</v>
       </c>
       <c r="O92">
-        <v>-1.606961216</v>
+        <v>-1.6301941184</v>
       </c>
       <c r="P92">
-        <v>-3.414792584000001</v>
+        <v>-3.464162501600001</v>
       </c>
       <c r="Q92">
-        <v>-2.864792584000001</v>
+        <v>-2.914162501600001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5222103574938276</v>
+        <v>0.5751448416598084</v>
       </c>
       <c r="T92">
-        <v>6.209224029282507</v>
+        <v>6.899137810313897</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07407119692840824</v>
+        <v>0.07325722773139277</v>
       </c>
       <c r="W92">
-        <v>0.2183340117642814</v>
+        <v>0.2185259457009376</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2314724904012757</v>
+        <v>0.2289288366606024</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2506216463372359</v>
+        <v>0.252521646337236</v>
       </c>
       <c r="C93">
-        <v>-21.36218342529881</v>
+        <v>-21.73104540830941</v>
       </c>
       <c r="D93">
-        <v>6.632716574701187</v>
+        <v>6.571754591690593</v>
       </c>
       <c r="E93">
-        <v>6.918899999999997</v>
+        <v>7.226800000000001</v>
       </c>
       <c r="F93">
-        <v>28.0189</v>
+        <v>28.3268</v>
       </c>
       <c r="G93">
         <v>0.024</v>
@@ -8901,37 +8901,37 @@
         <v>1.5125</v>
       </c>
       <c r="M93">
-        <v>6.60685662</v>
+        <v>6.67945944</v>
       </c>
       <c r="N93">
-        <v>-5.094356620000001</v>
+        <v>-5.166959440000001</v>
       </c>
       <c r="O93">
-        <v>-1.6301941184</v>
+        <v>-1.6534270208</v>
       </c>
       <c r="P93">
-        <v>-3.464162501600001</v>
+        <v>-3.513532419200001</v>
       </c>
       <c r="Q93">
-        <v>-2.914162501600001</v>
+        <v>-2.963532419200001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5751448416598084</v>
+        <v>0.6413129468672848</v>
       </c>
       <c r="T93">
-        <v>6.899137810313897</v>
+        <v>7.761530036603137</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07325722773139277</v>
+        <v>0.07246095351692111</v>
       </c>
       <c r="W93">
-        <v>0.2185259457009376</v>
+        <v>0.21871370716071</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2289288366606024</v>
+        <v>0.2264404797403784</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.252521646337236</v>
+        <v>0.254421646337236</v>
       </c>
       <c r="C94">
-        <v>-21.73104540830941</v>
+        <v>-22.09879698144879</v>
       </c>
       <c r="D94">
-        <v>6.571754591690593</v>
+        <v>6.51190301855121</v>
       </c>
       <c r="E94">
-        <v>7.226800000000001</v>
+        <v>7.534700000000001</v>
       </c>
       <c r="F94">
-        <v>28.3268</v>
+        <v>28.6347</v>
       </c>
       <c r="G94">
         <v>0.024</v>
@@ -8983,37 +8983,37 @@
         <v>1.5125</v>
       </c>
       <c r="M94">
-        <v>6.67945944</v>
+        <v>6.752062260000001</v>
       </c>
       <c r="N94">
-        <v>-5.166959440000001</v>
+        <v>-5.239562260000001</v>
       </c>
       <c r="O94">
-        <v>-1.6534270208</v>
+        <v>-1.676659923200001</v>
       </c>
       <c r="P94">
-        <v>-3.513532419200001</v>
+        <v>-3.562902336800001</v>
       </c>
       <c r="Q94">
-        <v>-2.963532419200001</v>
+        <v>-3.012902336800001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6413129468672848</v>
+        <v>0.7263862249911825</v>
       </c>
       <c r="T94">
-        <v>7.761530036603137</v>
+        <v>8.870320041832157</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07246095351692111</v>
+        <v>0.07168180347910476</v>
       </c>
       <c r="W94">
-        <v>0.21871370716071</v>
+        <v>0.2188974307396271</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2264404797403784</v>
+        <v>0.2240056358722022</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.254421646337236</v>
+        <v>0.256321646337236</v>
       </c>
       <c r="C95">
-        <v>-22.09879698144879</v>
+        <v>-22.46546820973107</v>
       </c>
       <c r="D95">
-        <v>6.51190301855121</v>
+        <v>6.453131790268929</v>
       </c>
       <c r="E95">
-        <v>7.534700000000001</v>
+        <v>7.842600000000001</v>
       </c>
       <c r="F95">
-        <v>28.6347</v>
+        <v>28.9426</v>
       </c>
       <c r="G95">
         <v>0.024</v>
@@ -9065,37 +9065,37 @@
         <v>1.5125</v>
       </c>
       <c r="M95">
-        <v>6.752062260000001</v>
+        <v>6.824665080000001</v>
       </c>
       <c r="N95">
-        <v>-5.239562260000001</v>
+        <v>-5.312165080000002</v>
       </c>
       <c r="O95">
-        <v>-1.676659923200001</v>
+        <v>-1.699892825600001</v>
       </c>
       <c r="P95">
-        <v>-3.562902336800001</v>
+        <v>-3.612272254400001</v>
       </c>
       <c r="Q95">
-        <v>-3.012902336800001</v>
+        <v>-3.062272254400001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7263862249911825</v>
+        <v>0.8398172624897132</v>
       </c>
       <c r="T95">
-        <v>8.870320041832157</v>
+        <v>10.34870671547085</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07168180347910476</v>
+        <v>0.07091923110166747</v>
       </c>
       <c r="W95">
-        <v>0.2188974307396271</v>
+        <v>0.2190772453062268</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2240056358722022</v>
+        <v>0.2216225971927107</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.256321646337236</v>
+        <v>0.258221646337236</v>
       </c>
       <c r="C96">
-        <v>-22.46546820973107</v>
+        <v>-22.83108808250734</v>
       </c>
       <c r="D96">
-        <v>6.453131790268929</v>
+        <v>6.395411917492658</v>
       </c>
       <c r="E96">
-        <v>7.842600000000001</v>
+        <v>8.150500000000001</v>
       </c>
       <c r="F96">
-        <v>28.9426</v>
+        <v>29.2505</v>
       </c>
       <c r="G96">
         <v>0.024</v>
@@ -9147,37 +9147,37 @@
         <v>1.5125</v>
       </c>
       <c r="M96">
-        <v>6.824665080000001</v>
+        <v>6.897267900000001</v>
       </c>
       <c r="N96">
-        <v>-5.312165080000002</v>
+        <v>-5.384767900000002</v>
       </c>
       <c r="O96">
-        <v>-1.699892825600001</v>
+        <v>-1.723125728000001</v>
       </c>
       <c r="P96">
-        <v>-3.612272254400001</v>
+        <v>-3.661642172000001</v>
       </c>
       <c r="Q96">
-        <v>-3.062272254400001</v>
+        <v>-3.111642172000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8398172624897132</v>
+        <v>0.9986207149876563</v>
       </c>
       <c r="T96">
-        <v>10.34870671547085</v>
+        <v>12.41844805856503</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07091923110166747</v>
+        <v>0.07017271287954464</v>
       </c>
       <c r="W96">
-        <v>0.2190772453062268</v>
+        <v>0.2192532743030034</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2216225971927107</v>
+        <v>0.2192897277485769</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.258221646337236</v>
+        <v>0.2601216463372359</v>
       </c>
       <c r="C97">
-        <v>-22.83108808250734</v>
+        <v>-23.19568456114542</v>
       </c>
       <c r="D97">
-        <v>6.395411917492658</v>
+        <v>6.338715438854586</v>
       </c>
       <c r="E97">
-        <v>8.150500000000001</v>
+        <v>8.458400000000001</v>
       </c>
       <c r="F97">
-        <v>29.2505</v>
+        <v>29.5584</v>
       </c>
       <c r="G97">
         <v>0.024</v>
@@ -9229,37 +9229,37 @@
         <v>1.5125</v>
       </c>
       <c r="M97">
-        <v>6.897267900000001</v>
+        <v>6.969870720000001</v>
       </c>
       <c r="N97">
-        <v>-5.384767900000002</v>
+        <v>-5.457370720000002</v>
       </c>
       <c r="O97">
-        <v>-1.723125728000001</v>
+        <v>-1.746358630400001</v>
       </c>
       <c r="P97">
-        <v>-3.661642172000001</v>
+        <v>-3.711012089600001</v>
       </c>
       <c r="Q97">
-        <v>-3.111642172000002</v>
+        <v>-3.161012089600002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9986207149876563</v>
+        <v>1.236825893734571</v>
       </c>
       <c r="T97">
-        <v>12.41844805856503</v>
+        <v>15.52306007320629</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07017271287954464</v>
+        <v>0.06944174712038273</v>
       </c>
       <c r="W97">
-        <v>0.2192532743030034</v>
+        <v>0.2194256360290137</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2192897277485769</v>
+        <v>0.2170054597511959</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2601216463372359</v>
+        <v>0.262021646337236</v>
       </c>
       <c r="C98">
-        <v>-23.19568456114541</v>
+        <v>-23.55928462419571</v>
       </c>
       <c r="D98">
-        <v>6.338715438854586</v>
+        <v>6.283015375804286</v>
       </c>
       <c r="E98">
-        <v>8.458399999999997</v>
+        <v>8.766299999999998</v>
       </c>
       <c r="F98">
-        <v>29.5584</v>
+        <v>29.8663</v>
       </c>
       <c r="G98">
         <v>0.024</v>
@@ -9311,37 +9311,37 @@
         <v>1.5125</v>
       </c>
       <c r="M98">
-        <v>6.96987072</v>
+        <v>7.04247354</v>
       </c>
       <c r="N98">
-        <v>-5.45737072</v>
+        <v>-5.52997354</v>
       </c>
       <c r="O98">
-        <v>-1.7463586304</v>
+        <v>-1.7695915328</v>
       </c>
       <c r="P98">
-        <v>-3.7110120896</v>
+        <v>-3.7603820072</v>
       </c>
       <c r="Q98">
-        <v>-3.1610120896</v>
+        <v>-3.210382007200001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.236825893734568</v>
+        <v>1.633834524979424</v>
       </c>
       <c r="T98">
-        <v>15.52306007320625</v>
+        <v>20.69741343094167</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06944174712038273</v>
+        <v>0.0687258528201726</v>
       </c>
       <c r="W98">
-        <v>0.2194256360290137</v>
+        <v>0.2195944439050033</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2170054597511961</v>
+        <v>0.2147682900630394</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.262021646337236</v>
+        <v>0.2639216463372359</v>
       </c>
       <c r="C99">
-        <v>-23.55928462419571</v>
+        <v>-23.92191431019658</v>
       </c>
       <c r="D99">
-        <v>6.283015375804286</v>
+        <v>6.228285689803422</v>
       </c>
       <c r="E99">
-        <v>8.766299999999998</v>
+        <v>9.074199999999998</v>
       </c>
       <c r="F99">
-        <v>29.8663</v>
+        <v>30.1742</v>
       </c>
       <c r="G99">
         <v>0.024</v>
@@ -9393,37 +9393,37 @@
         <v>1.5125</v>
       </c>
       <c r="M99">
-        <v>7.04247354</v>
+        <v>7.11507636</v>
       </c>
       <c r="N99">
-        <v>-5.52997354</v>
+        <v>-5.60257636</v>
       </c>
       <c r="O99">
-        <v>-1.7695915328</v>
+        <v>-1.7928244352</v>
       </c>
       <c r="P99">
-        <v>-3.7603820072</v>
+        <v>-3.8097519248</v>
       </c>
       <c r="Q99">
-        <v>-3.210382007200001</v>
+        <v>-3.259751924800001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.633834524979424</v>
+        <v>2.427851787469135</v>
       </c>
       <c r="T99">
-        <v>20.69741343094167</v>
+        <v>31.0461201464125</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0687258528201726</v>
+        <v>0.06802456860772187</v>
       </c>
       <c r="W99">
-        <v>0.2195944439050033</v>
+        <v>0.2197598067222992</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2147682900630394</v>
+        <v>0.2125767768991308</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2639216463372359</v>
+        <v>0.2658216463372359</v>
       </c>
       <c r="C100">
-        <v>-23.92191431019658</v>
+        <v>-24.28359875826169</v>
       </c>
       <c r="D100">
-        <v>6.228285689803422</v>
+        <v>6.174501241738306</v>
       </c>
       <c r="E100">
-        <v>9.074199999999998</v>
+        <v>9.382099999999998</v>
       </c>
       <c r="F100">
-        <v>30.1742</v>
+        <v>30.4821</v>
       </c>
       <c r="G100">
         <v>0.024</v>
@@ -9475,37 +9475,37 @@
         <v>1.5125</v>
       </c>
       <c r="M100">
-        <v>7.11507636</v>
+        <v>7.18767918</v>
       </c>
       <c r="N100">
-        <v>-5.60257636</v>
+        <v>-5.675179180000001</v>
       </c>
       <c r="O100">
-        <v>-1.7928244352</v>
+        <v>-1.8160573376</v>
       </c>
       <c r="P100">
-        <v>-3.8097519248</v>
+        <v>-3.8591218424</v>
       </c>
       <c r="Q100">
-        <v>-3.259751924800001</v>
+        <v>-3.309121842400001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.427851787469135</v>
+        <v>4.809903574938271</v>
       </c>
       <c r="T100">
-        <v>31.0461201464125</v>
+        <v>62.092240292825</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06802456860772187</v>
+        <v>0.06733745175309841</v>
       </c>
       <c r="W100">
-        <v>0.2197598067222992</v>
+        <v>0.2199218288766194</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2125767768991308</v>
+        <v>0.2104295367284325</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2658216463372359</v>
-      </c>
-      <c r="C101">
-        <v>-24.28359875826169</v>
-      </c>
-      <c r="D101">
-        <v>6.174501241738306</v>
-      </c>
-      <c r="E101">
-        <v>9.382099999999998</v>
-      </c>
-      <c r="F101">
-        <v>30.4821</v>
-      </c>
-      <c r="G101">
-        <v>0.024</v>
-      </c>
-      <c r="H101">
-        <v>9.69</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.0625</v>
-      </c>
-      <c r="K101">
-        <v>0.5499999999999998</v>
-      </c>
-      <c r="L101">
-        <v>1.5125</v>
-      </c>
-      <c r="M101">
-        <v>7.18767918</v>
-      </c>
-      <c r="N101">
-        <v>-5.675179180000001</v>
-      </c>
-      <c r="O101">
-        <v>-1.8160573376</v>
-      </c>
-      <c r="P101">
-        <v>-3.8591218424</v>
-      </c>
-      <c r="Q101">
-        <v>-3.309121842400001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.809903574938271</v>
-      </c>
-      <c r="T101">
-        <v>62.092240292825</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06733745175309841</v>
-      </c>
-      <c r="W101">
-        <v>0.2199218288766194</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2104295367284325</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
